--- a/data/dong-source.xlsx
+++ b/data/dong-source.xlsx
@@ -202,8 +202,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">강남구의 남쪽에 있는 동이다.
-양재천 남쪽이자 구룡산 · 대모산 북쪽 기슭에 있다.
+          <t xml:space="preserve">양재천 남쪽이자 구룡산 · 대모산 북쪽 기슭에 있다.
 남쪽은 서초구 내곡동, 동쪽은 일원동, 북쪽은 대치동 · 도곡동, 서쪽은 포이동과 접해 있다.
 1963년 서울특별시 성동구에 편입되어 언주출장소 관할이 되면서 개포동이 되었다가, 1975년 강남구 신설로 이에 속하게 되었다.
 양재천과 탄천이 만나는 곳에 여울이 세차게 형성되어 한여울 · 반포 등의 지명이 유래되어, 여기서 학여울 · 개포 등의 전이된 이름이 생겨났다.
@@ -212,11 +211,12 @@
         </is>
       </c>
       <c r="M2" s="0">
-        <v>342</v>
+        <v>325</v>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">양재대로가 동서로 가로지르고, 선릉로 · 영동대로 등과 지하철 분당선이 통과하여 교통이 매우 편리하다.</t>
+          <t xml:space="preserve">강남구의 남쪽에 있는 동이다.
+양재대로가 동서로 가로지르고, 선릉로 · 영동대로 등과 지하철 분당선이 통과하여 교통이 매우 편리하다.</t>
         </is>
       </c>
     </row>
@@ -278,8 +278,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">강남구 북쪽에 있는 동이다.
-동쪽은 삼성동, 서쪽은 서초구 잠원동 · 반포동, 남쪽은 역삼동, 북쪽은 신사동과 접해 있다.
+          <t xml:space="preserve">동쪽은 삼성동, 서쪽은 서초구 잠원동 · 반포동, 남쪽은 역삼동, 북쪽은 신사동과 접해 있다.
 논밭의 벌판에 논고개가 있던 데서 연유한 이름으로, 강남대로와 도산대로 남동쪽에 해당된다.
 1963년 서울특별시 성동구에 편입되어 언주출장소 관할이 되면서 논현동이 되었다가, 1975년 강남구 신설로 이에 속하게 되었다.
 1982년 종전의 학동(鶴洞)이 논현동에 편입되었다.
@@ -288,11 +287,12 @@
         </is>
       </c>
       <c r="M3" s="0">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">특히 논현사거리에서 영동사거리 일대에 가구단지가 형성되어 전문 가구 시장으로 유명하다.
+          <t xml:space="preserve">강남구 북쪽에 있는 동이다.
+특히 논현사거리에서 영동사거리 일대에 가구단지가 형성되어 전문 가구 시장으로 유명하다.
 강남대로, 봉은사로, 논현로, 도산대로, 언주로 등 도로가 바둑판 식으로 나 있고 지하철 7호선이 지나 교통이 매우 편리하다.</t>
         </is>
       </c>
@@ -355,8 +355,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">강남구의 중앙 동쪽에 있는 동이다.
-동쪽은 탄천을 경계로 송파구 잠실동과 접하고, 서쪽은 도곡동, 남쪽은 양재천, 북쪽은 삼성동과 접해 있다.
+          <t xml:space="preserve">동쪽은 탄천을 경계로 송파구 잠실동과 접하고, 서쪽은 도곡동, 남쪽은 양재천, 북쪽은 삼성동과 접해 있다.
 자연마을인 한티마을을 한자로 표기하면서 동명이 유래되었다.
 1963년 서울특별시 성동구에 편입되어 언주출장소 관할이 되었으며 1975년 강남구 신설로 이에 속하게 되었다.
 이 지역은 하천부지로 습지(濕地)였으나 1970년대부터 개발이 시작되어 크고 작은 빌딩과 고층아파트가 속속 들어서 서울 남부의 중심지로 탈바꿈하였다.
@@ -364,11 +363,12 @@
         </is>
       </c>
       <c r="M4" s="0">
-        <v>332</v>
+        <v>312</v>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동서로 남부순환로가 지나며, 도곡동길, 역삼로, 테헤란로, 선릉로가에는 상가와 업무용 빌딩들이 많이 들어서 있고, 특히 벤처산업의 요람으로 이름 높다.</t>
+          <t xml:space="preserve">강남구의 중앙 동쪽에 있는 동이다.
+동서로 남부순환로가 지나며, 도곡동길, 역삼로, 테헤란로, 선릉로가에는 상가와 업무용 빌딩들이 많이 들어서 있고, 특히 벤처산업의 요람으로 이름 높다.</t>
         </is>
       </c>
     </row>
@@ -430,8 +430,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">강남구의 중앙 서쪽에 있는 동이다.
-뒤쪽에 매봉산이 있으며, 동쪽은 대치동, 서쪽은 역삼동, 남쪽은 양재동 · 포이동, 북쪽은 삼성동과 접해 있다.
+          <t xml:space="preserve">뒤쪽에 매봉산이 있으며, 동쪽은 대치동, 서쪽은 역삼동, 남쪽은 양재동 · 포이동, 북쪽은 삼성동과 접해 있다.
 양재천 북쪽 매봉산 아래 산부리에 돌이 많이 박혀 있어 독부리라고 하던 것이 변하여 독구리, 독골이 되어 도곡이라고 지명이 유래되었다.
 1963년 서울특별시 성동구에 편입되면서 옛 이름 독골을 되찾아 도곡동이 되었다.
 1975년 신설된 강남구에 속하였다가 1988년 서초구를 거쳐 1989년 다시 강남구에 편입되었다.
@@ -440,11 +439,12 @@
         </is>
       </c>
       <c r="M5" s="0">
-        <v>369</v>
+        <v>349</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동서로 남부순환로가 지나며, 역삼로, 선릉로, 논현로, 언주로와 매봉터널 등 도로망이 잘 되어 있으며 지하철 3호선과 분당선이 지나 교통이 편리하다.</t>
+          <t xml:space="preserve">강남구의 중앙 서쪽에 있는 동이다.
+동서로 남부순환로가 지나며, 역삼로, 선릉로, 논현로, 언주로와 매봉터널 등 도로망이 잘 되어 있으며 지하철 3호선과 분당선이 지나 교통이 편리하다.</t>
         </is>
       </c>
     </row>
@@ -506,8 +506,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">강남구 북동쪽 영동대로와 테헤란로 서북쪽에 있는 동이다.
-탄천 하구 서쪽에 있으며, 동쪽은 송파구 잠실동, 서쪽은 논현동 · 역삼동과 접해 있고, 남쪽은 대치동 · 도곡동, 북쪽은 청담동과 접해 있다.
+          <t xml:space="preserve">탄천 하구 서쪽에 있으며, 동쪽은 송파구 잠실동, 서쪽은 논현동 · 역삼동과 접해 있고, 남쪽은 대치동 · 도곡동, 북쪽은 청담동과 접해 있다.
 닥점, 봉은사(奉恩寺), 무동도(舞童島)와 부리도(浮里島) 등의 세 마을을 합하여 삼성리(三成里)라고 한 데서 지명이 유래되었다.
 1963년 서울특별시 성동구에 편입되어 언주출장소 관할이 되면서 삼성동이 되었다가, 1975년 강남구 신설로 이에 속하게 되었다.
 영동대로 변에는 경기고등학교, 한국종합전시장, 무역센터 등이 있으며, 탄천변에는 강남소방서, 강남병원 등이 자리 잡고 있다.
@@ -515,11 +514,11 @@
         </is>
       </c>
       <c r="M6" s="0">
-        <v>399</v>
+        <v>367</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">강남구 북동쪽 영동대로와 테헤란로 서북쪽에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -580,8 +579,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">강남구의 남동 끝에 있는 동이다.
-대모산 서쪽 기슭에 위치하여, 동쪽은 송파구 장지동, 서쪽은 서초구 내곡동, 남쪽은 경기도 성남시 신촌동, 북쪽은 율현동 · 자곡동과 접해 있다.
+          <t xml:space="preserve">대모산 서쪽 기슭에 위치하여, 동쪽은 송파구 장지동, 서쪽은 서초구 내곡동, 남쪽은 경기도 성남시 신촌동, 북쪽은 율현동 · 자곡동과 접해 있다.
 자연마을인 세천리와 은곡동이 합해져 세곡동이 되었다.
 1963년 서울특별시 성동구에 편입되면서 송파출장소 관할의 세곡동으로 되었고, 1975년 강남구에 속하게 되었다.
 동의 많은 지역이 그린벨트로 지정되어 있어 한적한 전원 모습을 지니고 있으며, 점차 고급 주택지로 변하고 있다.
@@ -590,11 +588,11 @@
         </is>
       </c>
       <c r="M7" s="0">
-        <v>330</v>
+        <v>311</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">강남구의 남동 끝에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -654,19 +652,19 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">강남구의 남동쪽 끝에 있는 동이다.
-대모산 북쪽 기슭의 탄천 서쪽에 위치하여, 동쪽은 탄천을 경계로 송파구 문정동, 서쪽과 북쪽은 일원동, 남쪽은 자곡동과 접해 있다.
+          <t xml:space="preserve">대모산 북쪽 기슭의 탄천 서쪽에 위치하여, 동쪽은 탄천을 경계로 송파구 문정동, 서쪽과 북쪽은 일원동, 남쪽은 자곡동과 접해 있다.
 마을 서쪽에 강물이 흐른다 하여 동명이 유래되었다.
 1963년 서울특별시 성동구에 편입되면서 송파출장소 관할의 수서동이 되었고, 1975년 강남구가 신설되면서 이에 속하게 되었다.
 이 지역은 세종의 5남인 광평대군과 그 자손들의 묘소 등 700여 기 묘소 · 재실 및 종택인 전통한옥이 있어 궁말이라 부른다.</t>
         </is>
       </c>
       <c r="M8" s="0">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">택지개발사업에 의해 고밀도 아파트 지역으로 변모하였으며, 광평로 · 양재대로와 밤고개길이 만나는 곳에 수서입체교차로가 있고, 지하철 3호선 종점인 수서역이 분당선과 이어져 있으며, 강남구와 평택시를 연결하는 수서평택고속선의 수서역이 있어 교통이 편리하다.</t>
+          <t xml:space="preserve">강남구의 남동쪽 끝에 있는 동이다.
+택지개발사업에 의해 고밀도 아파트 지역으로 변모하였으며, 광평로 · 양재대로와 밤고개길이 만나는 곳에 수서입체교차로가 있고, 지하철 3호선 종점인 수서역이 분당선과 이어져 있으며, 강남구와 평택시를 연결하는 수서평택고속선의 수서역이 있어 교통이 편리하다.</t>
         </is>
       </c>
     </row>
@@ -728,8 +726,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">강남구의 북쪽 한강변에 있는 동이다.
-동쪽은 청담동, 북쪽은 압구정동, 서쪽은 잠원동, 남쪽은 논현동과 서초구 반포동과 접해 있다.
+          <t xml:space="preserve">동쪽은 청담동, 북쪽은 압구정동, 서쪽은 잠원동, 남쪽은 논현동과 서초구 반포동과 접해 있다.
 1963년 서울특별시 성동구에 편입되어 언주출장소 관할이 되면서 신사동이 되었다가, 1975년 강남구 신설로 이에 속하게 되었다.
 한남대교가 놓이기 전에는 새말나루터가 있어 강북으로 이어졌다.
 또 조선시대 이후 사평원이 있었고, 나루를 중심으로 시장이 서서 상업활동이 이루어지고 있었다.
@@ -737,11 +734,12 @@
         </is>
       </c>
       <c r="M9" s="0">
-        <v>336</v>
+        <v>315</v>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">신사동사무소와 압구정1·2동사무소에서 행정을 담당하고 있다.
+          <t xml:space="preserve">강남구의 북쪽 한강변에 있는 동이다.
+신사동사무소와 압구정1·2동사무소에서 행정을 담당하고 있다.
 유흥업소와 상가건물이 밀집해 있다.</t>
         </is>
       </c>
@@ -805,8 +803,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">강남구 북쪽 한강변에 있는 동이다.
-동쪽은 청담동, 서쪽은 신사동과 접해 있고, 북쪽은 한강을 넘어 성동구의 옥수동 · 금호동과 마주보고 있으며, 남쪽은 논현동과 접해 있다.
+          <t xml:space="preserve">동쪽은 청담동, 서쪽은 신사동과 접해 있고, 북쪽은 한강을 넘어 성동구의 옥수동 · 금호동과 마주보고 있으며, 남쪽은 논현동과 접해 있다.
 조선시대 세조 때의 권신 한명회(韓明會)가 지은 압구정이라는 정자가 있어 붙은 이름이다.
 1963년 서울특별시 성동구에 편입되어 언주출장소 관할이 되면서 압구정동이 되었다가, 1975년 강남구 신설로 이에 속하게 되었다.
 옛 압구정이 있던 곳은 한강 너머 멀리 삼각산 봉우리들까지 한눈에 들어오는 명승지였다.
@@ -815,11 +812,12 @@
         </is>
       </c>
       <c r="M10" s="0">
-        <v>419</v>
+        <v>399</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">이를 바탕으로 대형백화점 등이 조성되면서 고급 상업지역으로 발전하기에 이르렀다.
+          <t xml:space="preserve">강남구 북쪽 한강변에 있는 동이다.
+이를 바탕으로 대형백화점 등이 조성되면서 고급 상업지역으로 발전하기에 이르렀다.
 압구정로 등 많은 도로와 지하철 3호선이 지나 교통이 편리하며, 로데오거리로 불리는 젊은이들이 많이 찾는 유흥거리로 유명하다.</t>
         </is>
       </c>
@@ -882,18 +880,18 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">강남구의 중앙 서쪽에 있는 동이다.
-동쪽은 도곡동 · 삼성동, 서쪽은 서초구 서초동, 남쪽은 서초구 양재동, 북쪽은 논현동과 접해 있다.
+          <t xml:space="preserve">동쪽은 도곡동 · 삼성동, 서쪽은 서초구 서초동, 남쪽은 서초구 양재동, 북쪽은 논현동과 접해 있다.
 조선시대 한강을 건너기 전의 마지막 역마을이었던 말죽거리, 상방하교, 하방하교 등 세 마을을 합친 데서 동명이 유래되었다.
 1963년 서울특별시 성동구에 편입되면서 역삼동이 되었으며, 1975년 강남구에 속하게 되었다.</t>
         </is>
       </c>
       <c r="M11" s="0">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">강남대로 중앙에서 지하철 2호선 강남역을 만나 서울에서 사람이 가장 많이 모이는 곳으로 유명하며 봉은사로, 선릉로, 논현로, 언주로, 역삼로, 테헤란로 등이 바둑판식으로 교차하여 교통이 매우 편리하다.</t>
+          <t xml:space="preserve">강남구의 중앙 서쪽에 있는 동이다.
+강남대로 중앙에서 지하철 2호선 강남역을 만나 서울에서 사람이 가장 많이 모이는 곳으로 유명하며 봉은사로, 선릉로, 논현로, 언주로, 역삼로, 테헤란로 등이 바둑판식으로 교차하여 교통이 매우 편리하다.</t>
         </is>
       </c>
     </row>
@@ -954,19 +952,18 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">강남구의 남동쪽 끝에 있는 동이다.
-북쪽은 자곡동, 남쪽과 서쪽은 세곡동, 동쪽은 탄천을 건너 송파구 가락동과 접해 있다.
+          <t xml:space="preserve">북쪽은 자곡동, 남쪽과 서쪽은 세곡동, 동쪽은 탄천을 건너 송파구 가락동과 접해 있다.
 1963년 서울특별시 성동구에 편입되어 송파출장소 관할이 되었으며, 1975년 강남구가 신설되어 이에 속하게 되었다.
 율현이란 지명은 조선 숙종 때 영의정을 지낸 유상운(柳尙運)이 심은 밤나무가 많았다는 데서 유래되었다.
 동 가운데로 밤고개길이 지나는데, 방죽말에는 방죽 제1·2공원이 있으며, 탄천 쪽에는 덕암사가 있다.</t>
         </is>
       </c>
       <c r="M12" s="0">
-        <v>249</v>
+        <v>229</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">강남구의 남동쪽 끝에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -1028,8 +1025,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">강남구의 남동쪽에 있는 동이다.
-대모산 북쪽 기슭에 있으며, 동쪽은 수서동, 서쪽은 개포동, 남쪽은 서초구 내곡동, 북쪽은 탄천을 경계로 송파구 삼전동 · 석촌동과 접해 있다.
+          <t xml:space="preserve">대모산 북쪽 기슭에 있으며, 동쪽은 수서동, 서쪽은 개포동, 남쪽은 서초구 내곡동, 북쪽은 탄천을 경계로 송파구 삼전동 · 석촌동과 접해 있다.
 옛날 이 마을에 일원(逸院)이라는 서원이 있어 동명이 유래되었다.
 1963년 서울특별시 성동구에 편입되어 송파출장소의 관할이 되었으며, 1975년 강남구 신설에 따라 이에 속하였다.
 이 지역은 양재천 변의 기름진 농토가 많았으며, 도시화가 이루어지면서 단독주택 지역과 고밀도 아파트 혼합지역이 되었다.
@@ -1037,11 +1033,11 @@
         </is>
       </c>
       <c r="M13" s="0">
-        <v>296</v>
+        <v>278</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">강남구의 남동쪽에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -1103,8 +1099,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">강남구의 남동쪽 끝에 있는 동이다.
-동쪽은 송파구 가락동, 북쪽은 수서동, 서쪽은 서초구 내곡동, 남쪽은 율현동과 접해 있다.
+          <t xml:space="preserve">동쪽은 송파구 가락동, 북쪽은 수서동, 서쪽은 서초구 내곡동, 남쪽은 율현동과 접해 있다.
 1963년 서울특별시 성동구에 편입되어 송파출장소 관할구역이 되었다가, 1975년 강남구가 신설되어 이에 속하게 되었다.
 자곡이란 지명은 자연마을인 자양동(紫陽洞)과 지곡동(池谷洞)의 이름에서 유래되었다.
 1987년 취락구조 개선사업 실시로 옛집은 거의 헐리고 현대식 주택으로 탈바꿈하였다.
@@ -1112,11 +1107,11 @@
         </is>
       </c>
       <c r="M14" s="0">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">강남구의 남동쪽 끝에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -1178,8 +1173,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">강남구 북동쪽 영동대교 남단의 한강변에 있는 동이다.
-서쪽은 압구정동 · 논현동, 남쪽은 삼성동, 북쪽은 한강을 경계로 성동구 성수동 · 자양동, 동쪽은 한강과 접하고 있다.
+          <t xml:space="preserve">서쪽은 압구정동 · 논현동, 남쪽은 삼성동, 북쪽은 한강을 경계로 성동구 성수동 · 자양동, 동쪽은 한강과 접하고 있다.
 한강변의 물이 맑아 이 마을을 청숫골이라고 한 데에서 동 이름이 유래되었다.
 1963년 서울특별시 성동구에 편입되어 언주출장소 관할이 되면서 청담동이 되었다가, 1975년 강남구 신설로 이에 속하게 되었다.
 1973년 영동대교가 놓이기 전에는 전형적인 강촌으로 청담도선장을 통하여 강북으로 왕래하였다.
@@ -1187,11 +1181,12 @@
         </is>
       </c>
       <c r="M15" s="0">
-        <v>356</v>
+        <v>326</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">영동대교와 청담대교로 강북과 이어지며 도산대로와 영동대로가 지나고, 청담대교에 지하철 7호선이 놓이고 3개 역이 설치되어 있어 교통이 매우 편리하다.</t>
+          <t xml:space="preserve">강남구 북동쪽 영동대교 남단의 한강변에 있는 동이다.
+영동대교와 청담대교로 강북과 이어지며 도산대로와 영동대로가 지나고, 청담대교에 지하철 7호선이 놓이고 3개 역이 설치되어 있어 교통이 매우 편리하다.</t>
         </is>
       </c>
     </row>
@@ -1318,8 +1313,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 동북쪽에 있는 동이다.
-동쪽은 하일동, 북쪽은 한강 건너 경기도 구리시, 남쪽은 상일동 · 명일동, 서쪽은 암사동과 접해 있다.
+          <t xml:space="preserve">동쪽은 하일동, 북쪽은 한강 건너 경기도 구리시, 남쪽은 상일동 · 명일동, 서쪽은 암사동과 접해 있다.
 고려 말기 형조참의를 지낸 이양중이 조선 건국을 반대하여 이곳에 숨어 살아 덕이 높은 인물로 추앙받은 데에서 동명이 유래되었다.
 1963년 서울특별시 성동구에 편입되어 천호출장소 관할이 되었으며, 1975년 강남구를 거쳐 1979년 강동구가 신설되면서 이에 속하였다.
 1982년 고덕지구 택지개발사업에 의하여 대단위 주거지역으로 발전하였으며, 고덕주공아파트단지가 들어섰다.
@@ -1328,11 +1322,11 @@
         </is>
       </c>
       <c r="M17" s="0">
-        <v>436</v>
+        <v>420</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 동북쪽에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -1394,8 +1388,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 중앙 동남쪽에 있는 동이다.
-북쪽은 명일동, 서쪽은 천호동, 남쪽은 둔촌동, 동쪽의 경기도 하남시와 접해 있다.
+          <t xml:space="preserve">북쪽은 명일동, 서쪽은 천호동, 남쪽은 둔촌동, 동쪽의 경기도 하남시와 접해 있다.
 천재지변이 없는 살기 좋고 길(吉)한 곳이라는 데서 동명이 유래되었다.
 1963년 서울특별시 성동구에 편입되어 천호출장소 관할이 되었으며, 1975년 강남구를 거쳐 1979년 강동구가 신설되면서 이에 속하였다.
 1972년 천호토지구획정리사업지구에 둔촌로 일대가 개발되면서 인구가 급증하였다.
@@ -1404,11 +1397,11 @@
         </is>
       </c>
       <c r="M18" s="0">
-        <v>326</v>
+        <v>307</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 중앙 동남쪽에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -1468,8 +1461,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 남쪽 끝에 있는 동이다.
-북쪽은 길동, 서쪽은 성내동, 남쪽은 송파구 방이동, 동쪽은 일자산을 경계로 경기도 하남시와 접해 있다.
+          <t xml:space="preserve">북쪽은 길동, 서쪽은 성내동, 남쪽은 송파구 방이동, 동쪽은 일자산을 경계로 경기도 하남시와 접해 있다.
 광주이씨(廣州李氏)의 시조인 둔촌 이집(李集)이 한때 거주한 데서 동명이 유래되었다.
 1963년 서울특별시 성동구에 편입되어 천호출장소 관할이 되었으며, 1975년 강남구를 거쳐 1979년 강동구가 신설되면서 이에 속하였다.
 주택지구로 개발되기 시작하여 1980년 이후 대단위 주거 전용지구가 되었으며, 주공아파트단지가 형성되어 있다.
@@ -1478,11 +1470,12 @@
         </is>
       </c>
       <c r="M19" s="0">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">둔촌로와 지하철 5호선이 지나 교통이 편리하다.</t>
+          <t xml:space="preserve">구의 남쪽 끝에 있는 동이다.
+둔촌로와 지하철 5호선이 지나 교통이 편리하다.</t>
         </is>
       </c>
     </row>
@@ -1543,8 +1536,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 동남쪽 끝에 있는 동이다.
-북쪽은 고덕동, 동쪽은 상일동, 남쪽은 길동, 서쪽은 천호동 · 암사동과 접해 있다.
+          <t xml:space="preserve">북쪽은 고덕동, 동쪽은 상일동, 남쪽은 길동, 서쪽은 천호동 · 암사동과 접해 있다.
 고려시대 명일원(明逸院)이라는 숙박소가 있었던 데서 동명이 유래되었다.
 1963년 서울특별시 성동구에 편입되어 천호출장소 관할이 되었으며, 1975년 강남구를 거쳐 1979년 강동구가 신설되면서 이에 속하였다.
 고덕지구 택지개발사업에 포함되면서 주요 주거지역으로 발전하였으며 고층아파트가 들어섰다.
@@ -1552,11 +1544,11 @@
         </is>
       </c>
       <c r="M20" s="0">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 동남쪽 끝에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -1617,8 +1609,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 동쪽 끝에 있는 동이다.
-동쪽은 경기도 하남시 풍산동, 서쪽은 명일동, 남쪽은 하남시 초이동, 북쪽은 고덕동 · 하일동과 접해 있다.
+          <t xml:space="preserve">동쪽은 경기도 하남시 풍산동, 서쪽은 명일동, 남쪽은 하남시 초이동, 북쪽은 고덕동 · 하일동과 접해 있다.
 계 내의 위쪽에 있어 동명이 유래되었다.
 1963년 서울특별시 성동구에 편입되어 천호출장소 관할이 되었으며, 1975년 강남구를 거쳐 1979년 강동구가 신설되면서 이에 속하였다.
 임씨(任氏)와 조씨(趙氏)의 집성촌이 남아 있으며, 이곳에서는 매년 치성제를 올린다.
@@ -1627,11 +1618,12 @@
         </is>
       </c>
       <c r="M21" s="0">
-        <v>337</v>
+        <v>320</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">고덕지구 택지개발사업에 포함되면서 본격적으로 개발되어, 주공아파트단지를 형성하고 있다.</t>
+          <t xml:space="preserve">구의 동쪽 끝에 있는 동이다.
+고덕지구 택지개발사업에 포함되면서 본격적으로 개발되어, 주공아파트단지를 형성하고 있다.</t>
         </is>
       </c>
     </row>
@@ -1693,8 +1685,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 서남쪽에 있는 동이다.
-동쪽은 둔촌동, 남쪽과 서쪽은 송파구 방이동, 북쪽은 천호동과 접해 있다.
+          <t xml:space="preserve">동쪽은 둔촌동, 남쪽과 서쪽은 송파구 방이동, 북쪽은 천호동과 접해 있다.
 백제의 고성인 몽촌토성과 풍납토성이 각각 남쪽과 서쪽에 있다.
 풍납동 토성 안쪽에 위치하여 성안말 · 안말 등으로 불린 데서 동명이 유래되었다.
 1963년 서울특별시 성동구에 편입되어 천호출장소 관할이 되었으며, 1975년 강남구를 거쳐 1979년 강동구가 신설되면서 이에 속하였다.
@@ -1702,11 +1693,12 @@
         </is>
       </c>
       <c r="M22" s="0">
-        <v>338</v>
+        <v>322</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 후 인구 증가에 따른 아파트 건설과 구청 · 경찰서 등 공공시설이 들어서면서 공장들은 외곽으로 밀려나고 주택지역으로 바뀌었다.</t>
+          <t xml:space="preserve">구의 서남쪽에 있는 동이다.
+그 후 인구 증가에 따른 아파트 건설과 구청 · 경찰서 등 공공시설이 들어서면서 공장들은 외곽으로 밀려나고 주택지역으로 바뀌었다.</t>
         </is>
       </c>
     </row>
@@ -1768,19 +1760,18 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 북쪽에 위치한 동이다.
-동쪽은 고덕동 · 명일동, 남쪽은 천호동 · 북쪽은 한강을 경계로 경기도 구리시, 서쪽은 한강을 경계로 광진구 광장동과 접해 있다.
+          <t xml:space="preserve">동쪽은 고덕동 · 명일동, 남쪽은 천호동 · 북쪽은 한강을 경계로 경기도 구리시, 서쪽은 한강을 경계로 광진구 광장동과 접해 있다.
 신라시대 절이 9개 있어 구암사(九岩寺), 속칭 ‘바위절’이라고 하였던 데서 동명이 유래되었다.
 1963년 서울특별시 성동구에 편입되어 천호출장소 관할이 되었으며, 1975년 강남구를 거쳐 1979년 강동구가 신설되면서 이에 속하였다.
 주로 농업에 종사하던 마을이었는데 1970년대 중반부터 개발되었다.</t>
         </is>
       </c>
       <c r="M23" s="0">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 북쪽에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -1841,8 +1832,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 중앙 서쪽에 있는 동이다.
-동쪽은 명일동과 길동, 남쪽은 성내동, 북쪽은 암사동, 서쪽은 풍납동과 한강을 사이에 두고 광진구 광장동과 접해 있다.
+          <t xml:space="preserve">동쪽은 명일동과 길동, 남쪽은 성내동, 북쪽은 암사동, 서쪽은 풍납동과 한강을 사이에 두고 광진구 광장동과 접해 있다.
 옛날부터 수천 호가 살만한 지역이 될 것이라는 데서 동명이 유래되었다.
 원래 광주군 구천면 곡교리였으나 1963년 서울특별시 성동구에 편입되어 천호출장소 관할이 되면서 천호동이 되었으며, 1975년 강남구를 거쳐 1979년 강동구가 신설되면서 이에 속하였다.
 광나루로 인해 형성되기 시작한 도진촌락(渡津村落)으로 1936년 광진교가 놓이면서 마을이 커지기 시작하였다.
@@ -1850,11 +1840,12 @@
         </is>
       </c>
       <c r="M24" s="0">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">길이 육로로 바뀌면서 상업과 교통의 요충지로 성장하기 시작하였고, 천호시장과 주택단지가 들어섰다.
+          <t xml:space="preserve">구의 중앙 서쪽에 있는 동이다.
+길이 육로로 바뀌면서 상업과 교통의 요충지로 성장하기 시작하였고, 천호시장과 주택단지가 들어섰다.
 지하철 8호선이 지나 교통이 더욱 편리해졌다.</t>
         </is>
       </c>
@@ -1919,8 +1910,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">강북구의 남쪽에 있는 동이다.
-북쪽은 수유동, 동쪽은 번동, 그리고 산 능선을 경계로 성북구의 정릉동과 인접해 있으며, 남쪽은 성북구의 길음동 · 하월곡동과 도봉로를 경계로 하고 있다.
+          <t xml:space="preserve">북쪽은 수유동, 동쪽은 번동, 그리고 산 능선을 경계로 성북구의 정릉동과 인접해 있으며, 남쪽은 성북구의 길음동 · 하월곡동과 도봉로를 경계로 하고 있다.
 미아동이란 이름은 조선 말 고종 초의 공식기록에 처음 나타나는데 그 유래는 확실하지 않다.
 일제 때 이곳 일대에는 한국인 전용 공동묘지가 조성되었으므로 시내에서 사람이 죽으면 그 상여(喪輿)가 이 고개를 넘어가게 되어 있었다.
 그러나 이 고개를 넘어 미아리공동묘지에 묻히면 다시 돌아오지 못하므로 이때부터 사람들이 미아리고개라고 칭하게 되었다 한다.
@@ -1931,11 +1921,11 @@
         </is>
       </c>
       <c r="M25" s="0">
-        <v>621</v>
+        <v>604</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">강북구의 남쪽에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -1997,8 +1987,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">강북구의 동쪽에 있는 동이다.
-북쪽과 동쪽은 우이천을 사이로 창동 · 월계동과 마주하고, 서쪽은 오동공원(오패산) 능선을 경계로 미아동 · 수유동과 접하며, 남쪽은 장위동 · 하월곡동과 이웃하고 있다.
+          <t xml:space="preserve">북쪽과 동쪽은 우이천을 사이로 창동 · 월계동과 마주하고, 서쪽은 오동공원(오패산) 능선을 경계로 미아동 · 수유동과 접하며, 남쪽은 장위동 · 하월곡동과 이웃하고 있다.
 번동의 동명 유래는 “이(李)씨가 한양에 도읍하리라”는 설이 퍼지자, 한양 삼각산 아래 오얏나무가 무성하다는 말을 듣고 이씨가 흥할 징조라 여겨 오얏나무를 베기 위해 벌리사(伐李使)를 보냈다는 데서 이곳을 “벌리(伐李)”라 칭하다가 “번리(樊里)”가 되었다 한다.
 1949년 경기도 고양군에서 성북구로 편입되었고, 1950년 번동으로 바뀌었다.
 1973년 성북구에서 도봉구가 분리, 신설되자 도봉구 관할로 있다가 1995년 강북구에 속하게 되었다.
@@ -2007,11 +1996,12 @@
         </is>
       </c>
       <c r="M26" s="0">
-        <v>459</v>
+        <v>442</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">번2동은 오동근린공원이 전체 면적의 반 이상을 차지하며 공동주택이 밀집되어 있다.</t>
+          <t xml:space="preserve">강북구의 동쪽에 있는 동이다.
+번2동은 오동근린공원이 전체 면적의 반 이상을 차지하며 공동주택이 밀집되어 있다.</t>
         </is>
       </c>
     </row>
@@ -2073,8 +2063,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">강북구의 북쪽에 있는 동이다.
-동쪽은 번동 · 쌍문동, 서쪽은 경기도 신도읍(新道邑), 남쪽은 미아동, 북쪽은 경기도 고양시와 이웃하고 있다.
+          <t xml:space="preserve">동쪽은 번동 · 쌍문동, 서쪽은 경기도 신도읍(新道邑), 남쪽은 미아동, 북쪽은 경기도 고양시와 이웃하고 있다.
 수유동 동명의 유래는 북한산 골짜기에서 흘러내리는 물이 이 마을에 넘쳤기 때문에 물 ‘수(水)’ 자와 넘칠 ‘유(踰)’ 자를 써서 붙여졌다 한다.
 그래서 물이 넘친다 하여 ‘무너미’라고 부르게 되었다고도 한다.
 또 다른 하나는 예전 수유리와 인접해 있는 삼양동(三陽洞)이라는 마을에 삼형제가 살았는데 맏형은 바보이고 둘째는 개구쟁이며 셋째는 두 형보다는 머리가 좋은 편이었다고 한다.
@@ -2085,11 +2074,11 @@
         </is>
       </c>
       <c r="M27" s="0">
-        <v>610</v>
+        <v>593</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">강북구의 북쪽에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -2223,8 +2212,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">강서구의 동쪽에 위치한 동이다.
-북쪽은 올림픽대로를 끝으로 한강에 접해 있고, 서쪽은 궁산(宮山)의 능선을 경계로 마곡동과 이웃하며, 남쪽은 공항로가 경계가 되어 내발산동 · 외발산동 · 등촌동, 동쪽은 염창동과 접해 있다.
+          <t xml:space="preserve">북쪽은 올림픽대로를 끝으로 한강에 접해 있고, 서쪽은 궁산(宮山)의 능선을 경계로 마곡동과 이웃하며, 남쪽은 공항로가 경계가 되어 내발산동 · 외발산동 · 등촌동, 동쪽은 염창동과 접해 있다.
 가마동(加麻洞)과 고양리(古陽里)가 합쳐지면서 가마동의 ‘가(加)’자와 고양리의 ‘양(陽)’자를 따서 동명이 유래되었다.
 1963년 영등포구에 편입되면서 가양동이 되었고, 1977년 강서구의 신설로 이에 속하게 되었다.
 이 동은 가양1∼3동으로 이루어져 있으며, 마곡동도 관할하고 있다.
@@ -2235,11 +2223,11 @@
         </is>
       </c>
       <c r="M29" s="0">
-        <v>551</v>
+        <v>533</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">강서구의 동쪽에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -2374,8 +2362,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">강서구의 중앙에 위치한 동이다.
-동쪽은 외발산동, 서쪽은 과해동, 남쪽은 오곡동 · 오쇠동 · 방화동과 접해 있다.
+          <t xml:space="preserve">동쪽은 외발산동, 서쪽은 과해동, 남쪽은 오곡동 · 오쇠동 · 방화동과 접해 있다.
 이 마을에 김포비행장이 있는 데서 동명이 유래되었다.
 1963년 영등포구에 속하면서 공항동으로 개칭되었으며, 1977년 강서구가 분리 신설되자 공항동은 강서구 소속이 되었다.
 공항이 건설되기 이전까지는 넓은 김포평야의 한가운데 비교적 습지가 적은 밭 지역으로 형성되어 주거지역으로 안성맞춤이었다.
@@ -2384,11 +2371,11 @@
         </is>
       </c>
       <c r="M31" s="0">
-        <v>338</v>
+        <v>320</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">강서구의 중앙에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -2524,8 +2511,7 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">강서구의 중앙에 위치한 동이다.
-내발산동의 동쪽은 화곡동, 서쪽은 외발산동, 남쪽은 화곡동, 북쪽은 가양동과 접해 있다.
+          <t xml:space="preserve">내발산동의 동쪽은 화곡동, 서쪽은 외발산동, 남쪽은 화곡동, 북쪽은 가양동과 접해 있다.
 이 마을의 주산(主山)인 수명산(壽命山)의 모습이 주발처럼 생겼으므로 ‘발산(鉢山)’이라는 데서 동명이 유래하였다.
 발산의 안쪽이 내발산동이다.
 1963년 서울특별시 영등포구에 편입되었고, 1977년 강서구 신설로 이에 속하게 되었다.
@@ -2533,11 +2519,11 @@
         </is>
       </c>
       <c r="M33" s="0">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">강서구의 중앙에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -2598,8 +2584,7 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">강서구의 동쪽에 위치한 동이다.
-동쪽은 염창동, 서쪽은 내발산동, 남쪽은 화곡동, 북쪽은 가양동과 접해 있다.
+          <t xml:space="preserve">동쪽은 염창동, 서쪽은 내발산동, 남쪽은 화곡동, 북쪽은 가양동과 접해 있다.
 1963년 영등포구 양동출장소 관할아래 있다가, 1968년 영등포구로 직할되었다.
 1977년 강서구를 분구 신설하자 강서구에 편입되었다.
 우장산 북쪽 공항로 건너의 드넓은 농경지로 얼마 전까지 김포공항에서 서울 시내로 들어가는 길 양쪽에 누런 벼이삭이 황금바다를 이루던 곳이었으나 1990년대 이후 택지 개발로 오늘날에는 고층빌딩과 고층아파트가 들어선 주상복합단지로 탈바꿈하였다.
@@ -2608,11 +2593,11 @@
         </is>
       </c>
       <c r="M34" s="0">
-        <v>400</v>
+        <v>382</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">강서구의 동쪽에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -2745,8 +2730,7 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">강서구의 북쪽에 위치한 동이다.
-동쪽은 마곡동, 서쪽은 과해동과 경기도 고촌면과 연해 있고, 남쪽은 공항동, 북쪽은 개화동 · 한강과 접해 있다.
+          <t xml:space="preserve">동쪽은 마곡동, 서쪽은 과해동과 경기도 고촌면과 연해 있고, 남쪽은 공항동, 북쪽은 개화동 · 한강과 접해 있다.
 꽃이 피는 모습과 같이 생긴 개화산(開花山) 옆에 위치해 있어서 붙여진 데서 동명이 유래하였다.
 1963년 서울특별시 영등포구에 편입되었고, 1977년 강서구가 분리, 신설되면서 이에 속하게 되었다.
 1970년대 이후 단독주택이 들어서다가 1992년 방화지구 택지개발계획에 의거 대단위 아파트 단지가 들어서면서 시가지로 형성되었다.
@@ -2755,11 +2739,12 @@
         </is>
       </c>
       <c r="M36" s="0">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">주거와 상업지구가 혼합된 지역이며, 방화동길을 중심으로 상권이 형성되어 있다.</t>
+          <t xml:space="preserve">강서구의 북쪽에 위치한 동이다.
+주거와 상업지구가 혼합된 지역이며, 방화동길을 중심으로 상권이 형성되어 있다.</t>
         </is>
       </c>
     </row>
@@ -2820,8 +2805,7 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">강서구의 동쪽에 위치한 동이다.
-동쪽은 목동과 안양천을 경계로 영등포구와 마주하고, 서쪽은 등촌동 · 가양동, 남쪽은 목동 · 화곡동, 북쪽은 한강과 접해 있다.
+          <t xml:space="preserve">동쪽은 목동과 안양천을 경계로 영등포구와 마주하고, 서쪽은 등촌동 · 가양동, 남쪽은 목동 · 화곡동, 북쪽은 한강과 접해 있다.
 조선시대 말 서해안 염전(鹽田)으로부터 채취해 온 소금을 보관하기 위해 이곳에 소금 보관창고를 지은 데서 동명이 유래하였다.
 1963년 영등포구에 편입되었고, 1977년 강서구 신설로 이에 속하게 되었다.
 양천길이 동서로 관통하고 있으며 북쪽에 올림픽대로 · 한강과 연접한 지역으로 자연부락에서 공장지대로 발전하였고, 중소공장 · 노후건물 부지의 활발한 재건축사업으로 급속한 인구 유입, 주민 구성 및 생활수준이 다양화되고 공동주택이 계속 건축되고 있다.
@@ -2832,11 +2816,11 @@
         </is>
       </c>
       <c r="M37" s="0">
-        <v>588</v>
+        <v>570</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">강서구의 동쪽에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -3043,19 +3027,18 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">강서구의 남쪽에 위치한 동이다.
-발산동은 동쪽은 발산을 경계로 내발산동, 서쪽은 공항동, 남쪽은 신월동과 경기도 부천시, 북쪽은 가양동과 접해 있다.
+          <t xml:space="preserve">발산동은 동쪽은 발산을 경계로 내발산동, 서쪽은 공항동, 남쪽은 신월동과 경기도 부천시, 북쪽은 가양동과 접해 있다.
 이 마을의 주산(主山)인 수명산(壽命山)의 모습이 주발처럼 생겼으므로 ‘발산(鉢山)’이라는 데서 동명이 유래하였다.
 바깥쪽에 형성된 마을은 외발산동이다.
 1963년 서울특별시 영등포구에 편입되었고, 1977년 강서구 신설로 이에 속하게 되었다.</t>
         </is>
       </c>
       <c r="M40" s="0">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">강서구의 남쪽에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -3116,18 +3099,18 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">강서구의 남쪽에 위치한 동이다.
-동쪽은 등촌로를 경계로 양천구와 접해 있고, 서쪽은 우장산 능선을 경계로 발산 2동과 강서로를 경계로 발산 1동과 연해 있으며, 남쪽은 신월2동과 신정2동에 접해 있고, 북쪽은 공항로를 경계로 등촌로와 접해 있다.
+          <t xml:space="preserve">동쪽은 등촌로를 경계로 양천구와 접해 있고, 서쪽은 우장산 능선을 경계로 발산 2동과 강서로를 경계로 발산 1동과 연해 있으며, 남쪽은 신월2동과 신정2동에 접해 있고, 북쪽은 공항로를 경계로 등촌로와 접해 있다.
 땅이 기름져 벼가 잘되는 마을인 데서 동명이 유래하였다.
 1963년 서울특별시 영등포구에 편입되었고, 1977년 강서구 신설로 이에 속하게 되었다.</t>
         </is>
       </c>
       <c r="M41" s="0">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">한국전쟁 이전에는 호랑이와 여우, 늑대 등 맹수들이 출몰하는 한적한 농촌이었으나, 늘어나는 강북 인구를 강남으로 분산 유치시키기 위해 산 전체에 국민주택들이 들어서고 화곡시범아파트가 세워지면서부터 오늘날 거대한 빌딩숲으로 변하였으며 강서구의 중심지가 되었다.</t>
+          <t xml:space="preserve">강서구의 남쪽에 위치한 동이다.
+한국전쟁 이전에는 호랑이와 여우, 늑대 등 맹수들이 출몰하는 한적한 농촌이었으나, 늘어나는 강북 인구를 강남으로 분산 유치시키기 위해 산 전체에 국민주택들이 들어서고 화곡시범아파트가 세워지면서부터 오늘날 거대한 빌딩숲으로 변하였으며 강서구의 중심지가 되었다.</t>
         </is>
       </c>
     </row>
@@ -3387,8 +3370,7 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">광진구의 동쪽에 있는 동이다.
-남동쪽은 한강을 사이에 두고 강동구 천호동 · 풍납동과 마주하며, 서쪽은 구의동과 접하고, 북쪽은 아차산의 능선을 경계로 경기도 구리시와 이웃한다.
+          <t xml:space="preserve">남동쪽은 한강을 사이에 두고 강동구 천호동 · 풍납동과 마주하며, 서쪽은 구의동과 접하고, 북쪽은 아차산의 능선을 경계로 경기도 구리시와 이웃한다.
 조선시대 자연마을인 광진리(廣津里)의 ‘광’자와 장의동(壯義洞)의 ‘장’자를 따서 동 이름을 만들었다.
 조선시대에는 경기도 양주군 고양주면(古楊州面) 장의동이었다.
 1949년 성동구 광진리로 되었으며, 1950년 광장동으로 바뀌었고, 1995년 광진구가 신설되면서 이에 편입되었다.
@@ -3398,11 +3380,12 @@
         </is>
       </c>
       <c r="M45" s="0">
-        <v>489</v>
+        <v>472</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">강변도로변에는 많은 아파트가 건립되어 있고, 천호대로와 구의로가 만나는 광장동 사거리는 교통 체증이 심한 곳이나, 지하철 5호선이 개통되어 교통이 편리하다.</t>
+          <t xml:space="preserve">광진구의 동쪽에 있는 동이다.
+강변도로변에는 많은 아파트가 건립되어 있고, 천호대로와 구의로가 만나는 광장동 사거리는 교통 체증이 심한 곳이나, 지하철 5호선이 개통되어 교통이 편리하다.</t>
         </is>
       </c>
     </row>
@@ -3463,8 +3446,7 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">광진구의 동쪽에 있는 동이다.
-동쪽은 광장동과 접하고 서쪽은 능동 · 화양동과 연해 있고 남쪽은 자양동과 이웃하면서 한강으로 뻗어 있으며 북쪽은 아차산과 중곡동에 접해있다.
+          <t xml:space="preserve">동쪽은 광장동과 접하고 서쪽은 능동 · 화양동과 연해 있고 남쪽은 자양동과 이웃하면서 한강으로 뻗어 있으며 북쪽은 아차산과 중곡동에 접해있다.
 아차산 기슭에서 한강변에 이르는 긴 지형을 지닌 동의 이름은 자연마을인 양주군 고양주면(古楊州面)의 구정동(九井洞)의 ‘구’자와 산의동(山宜洞)의 ‘의’자를 따서 붙인 이름이다.
 조선시대에는 경기도 양주군 고양주면의 구정동 · 산의동 · 율동이었다.
 1949년 성동구 구의리가 되었으며, 1950년 구의동으로 바뀌었고, 1995년 광진구가 신설되면서 이에 편입되었다.
@@ -3475,11 +3457,11 @@
         </is>
       </c>
       <c r="M46" s="0">
-        <v>521</v>
+        <v>504</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">광진구의 동쪽에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -3542,8 +3524,7 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">광진구의 서쪽에 있는 동이다.
-동쪽은 능동과 접해 있고, 서쪽은 용답동과 연해 있으며 남쪽은 송정동 · 화양동과 이웃해 있고 북쪽은 천호대로를 사이에 두고 중곡동과 동대문구 장안동, 중랑구 면목동과 이웃하여 있다.
+          <t xml:space="preserve">동쪽은 능동과 접해 있고, 서쪽은 용답동과 연해 있으며 남쪽은 송정동 · 화양동과 이웃해 있고 북쪽은 천호대로를 사이에 두고 중곡동과 동대문구 장안동, 중랑구 면목동과 이웃하여 있다.
 동명의 유래는 다음과 같다.
 옛날 어느 임금님 일행이 거동하다가 마침 이곳 동이로변(東二路邊: 남일농장터)에 묵게 되었는데, 그날 밤 동행했던 왕비가 옥동자를 낳았다고 한다.
 그래서 임금의 아들을 낳은 곳이라 하여 이곳을 군자동이라 하였으며 지금도 이곳을 ‘명려궁터’라 부른다.
@@ -3553,11 +3534,12 @@
         </is>
       </c>
       <c r="M47" s="0">
-        <v>478</v>
+        <v>461</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">중랑천 건너편에는 서울 중고 자동차 시장과 자동차 정비 단지가 있다.</t>
+          <t xml:space="preserve">광진구의 서쪽에 있는 동이다.
+중랑천 건너편에는 서울 중고 자동차 시장과 자동차 정비 단지가 있다.</t>
         </is>
       </c>
     </row>
@@ -3619,8 +3601,7 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">광진구의 중앙에 있는 동이다.
-동쪽은 구의동, 남쪽은 화양동, 서쪽은 군자동, 북쪽은 중곡동과 접하고 있다.
+          <t xml:space="preserve">동쪽은 구의동, 남쪽은 화양동, 서쪽은 군자동, 북쪽은 중곡동과 접하고 있다.
 1904년(광무 8) 순명황후(純明皇后) 민씨(閔氏)의 유릉(裕陵)을 모셨으므로 능말 · 능리(陵里)라 하였으며, 마장(馬場)의 안쪽에 있다 하여 ‘장안말’, ‘안말’, 한자로 ‘장내리(場內里)’, ‘내리(內里)’라고 하였다.
 1949년 성동구 능리로 바뀌었으며, 1950년 능동으로 되었다.
 1995년 광진구가 신설되면서 이에 편입되었다.
@@ -3630,11 +3611,12 @@
         </is>
       </c>
       <c r="M48" s="0">
-        <v>472</v>
+        <v>455</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동의 북쪽에는 천호대로, 남쪽에는 광나룻길, 서쪽의 군자동 사이에는 능동로가 있고, 지하철 5·7호선이 지나고 있어 교통이 편리하다.</t>
+          <t xml:space="preserve">광진구의 중앙에 있는 동이다.
+동의 북쪽에는 천호대로, 남쪽에는 광나룻길, 서쪽의 군자동 사이에는 능동로가 있고, 지하철 5·7호선이 지나고 있어 교통이 편리하다.</t>
         </is>
       </c>
     </row>
@@ -3696,8 +3678,7 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">광진구의 남쪽 끝에 있는 동이다.
-동쪽은 구의동, 서쪽은 성수동과 접하고 남쪽은 한강과 연해 있으며 북쪽은 화양동과 이웃하고 있다.
+          <t xml:space="preserve">동쪽은 구의동, 서쪽은 성수동과 접하고 남쪽은 한강과 연해 있으며 북쪽은 화양동과 이웃하고 있다.
 조선시대 이곳에서 암말을 길렀기 때문에 자마장리(雌馬場里)라 한 것이 전음(轉音)이 되어 자양동이 되었다.
 조선시대에는 경기도 양주군 고양주면(古楊州面) 자마장리 율동(栗洞)의 일부였던 것이, 1936년 자양리로 이름이 바뀌었고, 1949년 성동구 자양리로 편입되었다가, 1950년 자양동으로 바뀌었다.
 1995년 광진구가 신설되면서 이에 속하여 오늘에 이른다.
@@ -3706,11 +3687,11 @@
         </is>
       </c>
       <c r="M49" s="0">
-        <v>400</v>
+        <v>381</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">광진구의 남쪽 끝에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -3771,8 +3752,7 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">광진구의 북쪽에 있는 동이다.
-동쪽은 구의동, 경기도 구리시와 시계를 이루고 있으며, 서쪽은 동대문구 장안동과 구계(區界)를 이루고, 남쪽은 군자동 · 능동 · 구의동과 이웃하고 북쪽은 중랑구 면목동과 구계(區界)를 이루고 있다.
+          <t xml:space="preserve">동쪽은 구의동, 경기도 구리시와 시계를 이루고 있으며, 서쪽은 동대문구 장안동과 구계(區界)를 이루고, 남쪽은 군자동 · 능동 · 구의동과 이웃하고 북쪽은 중랑구 면목동과 구계(區界)를 이루고 있다.
 동명은 능동과 면목동 중간에 있어 ‘가운데말’, ‘간뎃말’ 또는 한자음으로 중곡동(中谷洞)이라 한데서 유래되었다.
 1949년 성동구 중곡리로 되었으며, 1950년 중곡동으로 바뀌었다.
 1973년과 1975년 구청 사이의 경계 조정으로 동 일부가 동대문구 면목동으로 바뀌었고, 면목동의 일부가 중곡동에 속하게 되었다.
@@ -3785,11 +3765,11 @@
         </is>
       </c>
       <c r="M50" s="0">
-        <v>630</v>
+        <v>613</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">광진구의 북쪽에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -3850,19 +3830,19 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">광진구의 서쪽에 있는 동이다.
-동쪽은 구의동, 서쪽은 성동구, 남쪽은 자양동, 북쪽은 군자동 · 능동과 접한다.
+          <t xml:space="preserve">동쪽은 구의동, 서쪽은 성동구, 남쪽은 자양동, 북쪽은 군자동 · 능동과 접한다.
 동의 이름은 조선시대 이곳에 세워진 화양정(華陽亭)에서 유래하였다.
 세조에게 왕위를 내놓은 단종이 노산군으로 강봉(降封)되어 영월로 귀양 갈 때, 이곳에서 부인 송씨와 이별하면서 회행(回行)하기를 기원했다고 하여 회행리(回行里)로도 불렸다.
 1949년 성동구에 편입되어 이듬해 화양동으로 바뀐 뒤, 1995년 광진구가 신설되면서 이에 속하게 되었다.</t>
         </is>
       </c>
       <c r="M51" s="0">
-        <v>258</v>
+        <v>241</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">광나룻길, 구의로, 동이로, 능동로가 동을 지나고, 지하철 2·7호선이 있어 교통이 편리하다.</t>
+          <t xml:space="preserve">광진구의 서쪽에 있는 동이다.
+광나룻길, 구의로, 동이로, 능동로가 동을 지나고, 지하철 2·7호선이 있어 교통이 편리하다.</t>
         </is>
       </c>
     </row>
@@ -3923,8 +3903,7 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구로구의 동남부에 위치한 동이다.
-가리봉동의 동명 유래는 이 마을 주위의 작은 봉우리가 이어져 마을이 되었다고 한 데서 붙여졌다 한다.
+          <t xml:space="preserve">가리봉동의 동명 유래는 이 마을 주위의 작은 봉우리가 이어져 마을이 되었다고 한 데서 붙여졌다 한다.
 또 다른 하나는 골[谷], 즉 고을과 같은 의미를 갖는 ‘갈’ 또는 ‘가리’, ‘갈라졌다’는 뜻에서 유래하였다고 한다.
 조선시대에 금천현이었다가 1795년(정조 19) 시흥현으로 바뀌었고, 1895년 시흥군 동면 가리봉리였다.
 1963년 서울시 영등포구에 편입되어 가리봉동이 된 후 1980년 영등포구에서 구로구가 분리 신설되면서 구로구의 법정동이 되었다.
@@ -3936,11 +3915,11 @@
         </is>
       </c>
       <c r="M52" s="0">
-        <v>561</v>
+        <v>542</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구로구의 동남부에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -4002,8 +3981,7 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구로구의 남부에 위치한 동이다.
-개봉동 동명의 유래는 경인선과 남부순환로가 교차하는 남쪽에 있었던 개웅(開雄)마을의 이름에서 유래하는데, 개웅의 ‘개(開)’자와 양천구 신정동과 경계를 이루는 매봉산의 ‘봉(峰)’자를 합한 것이다.
+          <t xml:space="preserve">개봉동 동명의 유래는 경인선과 남부순환로가 교차하는 남쪽에 있었던 개웅(開雄)마을의 이름에서 유래하는데, 개웅의 ‘개(開)’자와 양천구 신정동과 경계를 이루는 매봉산의 ‘봉(峰)’자를 합한 것이다.
 조선시대 부평도호부(富平都護府) 갈탄(葛灘)이었으며, 1895년 부평군 수탄면(水呑面)이 되었고, 1914년 부천군 계남면(桂南面) 개봉리(開峰里)로 바뀌었다가 1941년 부천군 소사읍 개봉리가 되었다.
 1963년 서울시 영등포구에 편입되어 개봉동이 된 후 1980년 영등포구에서 구로구가 분리 신설되면서 구로구의 법정동이 되었다.
 위치는 동쪽은 고척동 구로동 및 광명시, 서쪽은 오류동, 남쪽은 광명시, 북쪽은 고척동과 양천구 신정동에 접해 있다.
@@ -4011,11 +3989,12 @@
         </is>
       </c>
       <c r="M53" s="0">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">남부순환도로가 중앙을 동서로 관통하고, 1호선 전철의 개봉역이 있어 교통이 편리하다.</t>
+          <t xml:space="preserve">구로구의 남부에 위치한 동이다.
+남부순환도로가 중앙을 동서로 관통하고, 1호선 전철의 개봉역이 있어 교통이 편리하다.</t>
         </is>
       </c>
     </row>
@@ -4076,8 +4055,7 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구로구의 중앙에 위치한 동이다.
-고척동의 동명 유래는 마을인 고좌리(高座里), 즉 높은 곳에 생긴 마을이라는 것에서 연유되었다.
+          <t xml:space="preserve">고척동의 동명 유래는 마을인 고좌리(高座里), 즉 높은 곳에 생긴 마을이라는 것에서 연유되었다.
 조선시대 부평도호부 수탄면이었으며, 1914년 부천군 계남면 고척리(高尺里)로 바뀌었다가 1941년 부천군 소사읍 고척리가 되었다.
 1963년 서울시 영등포구에 편입되어 개봉동이 된 후 1980년 영등포구에서 구로구가 분리 신설되면서 구로구의 법정동이 되었다.
 위치는 동쪽으로 구로동, 서쪽과 북쪽으로는 양천구 신정동, 남쪽으로는 개봉동에 접해 있다.
@@ -4085,11 +4063,11 @@
         </is>
       </c>
       <c r="M54" s="0">
-        <v>291</v>
+        <v>273</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구로구의 중앙에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -4146,13 +4124,12 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">판정보류</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구로구의 동부에 위치한 동이다.
-구로동의 동명은 옛날 이 마을에 아홉 노인이 오랫동안 살았다는 데서 유래되었다는 설과 중국 당나라의 대표적인 시인인 백거이(白居易)가 낙양(洛陽) 용문산(龍門山) 동쪽에 석루(石樓)를 짓고 시인 8명과 함께 시회(詩會)인 ‘향산구로회(香山九老會)’를 만들어 즐긴 것을 아름답게 여긴 데서 유래하였다는 설이 있다.
+          <t xml:space="preserve">구로동의 동명은 옛날 이 마을에 아홉 노인이 오랫동안 살았다는 데서 유래되었다는 설과 중국 당나라의 대표적인 시인인 백거이(白居易)가 낙양(洛陽) 용문산(龍門山) 동쪽에 석루(石樓)를 짓고 시인 8명과 함께 시회(詩會)인 ‘향산구로회(香山九老會)’를 만들어 즐긴 것을 아름답게 여긴 데서 유래하였다는 설이 있다.
 조선시대 금천현이었다가 1795년(정조 19) 시흥현으로 바뀌었고, 1895년 시흥군 상북면(上北面)에 속했으며, 1914년 시흥군 상북면 구로리가 되었다.
 이후 1963년 서울시 영등포구에 편입된 후 1980년 영등포구에서 구로구가 분리 신설되면서 구로구의 법정동이 되었다.
 위치는 동쪽으로 독산동과 영등포구 문래동 및 관악구 신림동, 서쪽으로 고척동, 남쪽으로 가리봉동과 경기도 광명시, 북쪽은 신도림동과 영등포구 문래동과 접해 있다.
@@ -4160,11 +4137,12 @@
         </is>
       </c>
       <c r="M55" s="0">
-        <v>480</v>
+        <v>462</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구로구의 중심동으로서 구로구청과 구로경찰서 등의 행정기관이 밀집되어 있고, 영화관을 갖추고 있는 애경백화점, 평강 성서유물박물관, 구로구민회관, 구로문화원, 구로문화예술회관 등의 문화시설이 집중되어 있다.</t>
+          <t xml:space="preserve">구로구의 동부에 위치한 동이다.
+구로구의 중심동으로서 구로구청과 구로경찰서 등의 행정기관이 밀집되어 있고, 영화관을 갖추고 있는 애경백화점, 평강 성서유물박물관, 구로구민회관, 구로문화원, 구로문화예술회관 등의 문화시설이 집중되어 있다.</t>
         </is>
       </c>
     </row>
@@ -4373,8 +4351,7 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구로구의 서남부에 위치한 동이다.
-오류동의 동명은 예부터 오류동 123번지 일대와 그 서쪽에 오동나무와 버드나무가 많이 심어져 오류꿀이라 부른데서 유래한다.
+          <t xml:space="preserve">오류동의 동명은 예부터 오류동 123번지 일대와 그 서쪽에 오동나무와 버드나무가 많이 심어져 오류꿀이라 부른데서 유래한다.
 조선시대 부평도호부 수탄면 오류동이었으며, 1895년 인천부 부평군 수탄면이 되었고, 1914년 부천군 계남면 오류리로 바뀌었다가 1941년 부천군 소사읍 오류리가 되었다.
 이후 1963년 서울시 영등포구에 편입되어 오류동이 되었고, 1980년 영등포구에서 구로구가 분리 신설되면서 구로구의 법정동이 되었다.
 위치는 동쪽으로 개봉동, 서쪽으로 궁동, 남쪽으로 천왕동 · 항동, 북쪽으로 개봉동이 접해있다.
@@ -4382,11 +4359,11 @@
         </is>
       </c>
       <c r="M58" s="0">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구로구의 서남부에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -4668,19 +4645,19 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">금천구의 북서부에 위치한 동이다.
-가산동의 동명 유래는 가리봉동(加里峰洞)의 ‘가(加)’자와 독산동(禿山洞)의 ‘산(山)’자를 따서 지었다.
+          <t xml:space="preserve">가산동의 동명 유래는 가리봉동(加里峰洞)의 ‘가(加)’자와 독산동(禿山洞)의 ‘산(山)’자를 따서 지었다.
 조선시대 금천현, 시흥현의 동면에 속하였고, 1914년 이후에는 시흥군에 속하였다가 1995년 금천구가 구로구에서 분리 신설되면서 금천구의 법정동이 되었다.
 서쪽으로는 경기도 과천시 철산동과 접하고, 동쪽으로는 독산동, 북쪽으로는 구로구와 접하고 있으며, 안양천변을 따라 서부간선도로가 이어져 서해안고속도로와 연결되고, 남부순환로가 동의 북쪽을 동서로 지나고 있다.
 이 동에는 한국산업디자인진흥원 등 디지털단지가 조성되어 동 전체가 회사들로 들어차 있으며, 학교나 전시관 및 공연장 등 문화시설이 없다.</t>
         </is>
       </c>
       <c r="M62" s="0">
-        <v>360</v>
+        <v>341</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">전철 1호선과 7호선이 만나는 가산디지털단지역이 디지털가산단지에서 합류되어 교통이 편리하다.</t>
+          <t xml:space="preserve">금천구의 북서부에 위치한 동이다.
+전철 1호선과 7호선이 만나는 가산디지털단지역이 디지털가산단지에서 합류되어 교통이 편리하다.</t>
         </is>
       </c>
     </row>
@@ -4741,8 +4718,7 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">금천구의 중앙에 위치한 동이다.
-독산동의 동명은 이 마을 산봉우리에 나무가 없어 벌거숭이 산이어서 대머리, 민둥민둥할 ‘독(禿)’자를 쓴다.
+          <t xml:space="preserve">독산동의 동명은 이 마을 산봉우리에 나무가 없어 벌거숭이 산이어서 대머리, 민둥민둥할 ‘독(禿)’자를 쓴다.
 조선시대 금천현, 시흥현의 동면에 속하였고, 1914년 이후에는 시흥군에 속하였다가 1995년 금천구가 구로구에서 분리 신설되면서 금천구의 법정동이 되었다.
 서쪽으로는 가산동, 동쪽으로는 관악구, 남쪽으로는 시흥동과 접하고 있다.
 동의 중앙을 시흥대로가 관통하고, 간선도로와 연결되어 도로망이 형성되어 있으며, 전철 1호선 독산역이 있다.
@@ -4751,11 +4727,11 @@
         </is>
       </c>
       <c r="M63" s="0">
-        <v>355</v>
+        <v>337</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">금천구의 중앙에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -4814,8 +4790,7 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">금천구의 남부에 위치한 동이다.
-시흥동의 동명은 1795년(정조 19) 금천현의 행정지명을 시흥현으로 개칭하면서 생긴 이름이다.
+          <t xml:space="preserve">시흥동의 동명은 1795년(정조 19) 금천현의 행정지명을 시흥현으로 개칭하면서 생긴 이름이다.
 조선시대 금천현, 시흥현의 동면에 속하였고, 1914년 이후에는 시흥군에 속하였다가 1995년 금천구가 구로구에서 분리 신설되면서 금천구의 법정동이 되었다.
 동의 북쪽에는 독산동, 남쪽에는 경기도 안양시, 서쪽으로는 경기도 광명시, 동쪽으로는 관악구와 접하고 있다.
 동의 중앙을 시흥대로가 관통하고, 간선도로와 연결되어 도로망이 형성되어 있으며, 전철 1호선 금천구청역이 있다.
@@ -4823,11 +4798,11 @@
         </is>
       </c>
       <c r="M64" s="0">
-        <v>353</v>
+        <v>335</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">금천구의 남부에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -4888,8 +4863,7 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">노원구의 동남부에 위치한 동이다.
-공릉동의 동명은 1963년 경기도에서 서울특별시로 편입될 때 양주군(楊州郡) 노해면(蘆海面) 공덕리(孔德里)의 ‘공(孔)’자와 동쪽 태릉의 ‘릉(陵)’자를 따서 지었다.
+          <t xml:space="preserve">공릉동의 동명은 1963년 경기도에서 서울특별시로 편입될 때 양주군(楊州郡) 노해면(蘆海面) 공덕리(孔德里)의 ‘공(孔)’자와 동쪽 태릉의 ‘릉(陵)’자를 따서 지었다.
 조선 초부터 양주목(楊州牧) 노원면(蘆原面)에 속하였고, 1895년 한성부 양주군 노원면이 되었다.
 1914년 해등촌면(海等村面)과 합하여 노해면 공덕리가 되었으며, 1963년 서울시 성북구 공릉동으로 개칭되었다.
 1973년 도봉구에 속했다가 1988년 노원구의 법정동이 되었다.
@@ -4900,11 +4874,11 @@
         </is>
       </c>
       <c r="M65" s="0">
-        <v>494</v>
+        <v>475</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">노원구의 동남부에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -4965,8 +4939,7 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">노원구의 북부에 위치한 동이다.
-상계동 동명은 중랑천의 위쪽에 위치하므로 붙여진 이름이다.
+          <t xml:space="preserve">상계동 동명은 중랑천의 위쪽에 위치하므로 붙여진 이름이다.
 조선 초부터 경기도 양주목(楊州牧) 노원면에 속하였고, 1895년 한성부 양주군 노원면이 되었다.
 1914년 양주군 노해면 상계리가 되었으며, 1963년 서울시 성북구 상계동으로 개칭되었다.
 1973년 도봉구에 속했다가 1988년 노원구의 법정동이 되었다.
@@ -4976,11 +4949,11 @@
         </is>
       </c>
       <c r="M66" s="0">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">노원구의 북부에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -5041,8 +5014,7 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">노원구의 서남부에 위치한 동이다.
-월계동의 동명은 중랑천(中浪川, 漢川이라고도 함)과 우이천(牛耳川)이 이곳에서 만나기 때문에 지형이 반달처럼 생겨 붙여진 이름이다.
+          <t xml:space="preserve">월계동의 동명은 중랑천(中浪川, 漢川이라고도 함)과 우이천(牛耳川)이 이곳에서 만나기 때문에 지형이 반달처럼 생겨 붙여진 이름이다.
 조선 초부터 양주목 노원면에 속하였고, 1895년 한성부 양주군 노원면이 되었다.
 1914년 양주군 노해면 월계리(月溪里)가 되었으며, 1963년 서울시 성북구 월계동으로 개칭되었다.
 1973년 도봉구에 속했다가 1988년 노원구의 법정동이 되었다.
@@ -5052,11 +5024,11 @@
         </is>
       </c>
       <c r="M67" s="0">
-        <v>365</v>
+        <v>346</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">노원구의 서남부에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -5117,8 +5089,7 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">노원구의 중앙에 위치한 동이다.
-중계동 동명은 이 지역이 중랑천의 중간에 위치해서 붙여진 것이다.
+          <t xml:space="preserve">중계동 동명은 이 지역이 중랑천의 중간에 위치해서 붙여진 것이다.
 조선 초부터 경기도 양주목 노원면에 속하였고, 1895년 한성부 양주군 노원면이 되었다.
 1914년 양주군 노해면 중계리(中溪里)가 되었으며, 1963년 서울시 성북구 중계동으로 개칭되었다.
 1973년 도봉구에 속했다가 1988년 노원구의 법정동이 되었다.
@@ -5128,11 +5099,11 @@
         </is>
       </c>
       <c r="M68" s="0">
-        <v>331</v>
+        <v>313</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">노원구의 중앙에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -5191,8 +5162,7 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">노원구의 남부에 위치한 동이다.
-하계동 동명은 이 지역이 중랑천 아래쪽에 위치하므로 붙여진 것이다.
+          <t xml:space="preserve">하계동 동명은 이 지역이 중랑천 아래쪽에 위치하므로 붙여진 것이다.
 조선 초부터 경기도 양주목 노원면에 속하였고, 1895년 한성부 양주군 노원면이 되었다.
 1914년 양주군 노해면 하계리(下溪里)가 되었으며, 1963년 서울시 성북구 하계동으로 개칭되었다.
 1973년 도봉구에 속했다가 1988년 노원구의 법정동이 되었다.
@@ -5202,11 +5172,11 @@
         </is>
       </c>
       <c r="M69" s="0">
-        <v>322</v>
+        <v>304</v>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">노원구의 남부에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -5270,8 +5240,7 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">도봉구 북쪽 끝에 위치하고 있다.
-동쪽은 한천(漢川)을 끼고 상계동과 이웃하고, 서쪽은 우이동과 양주군 장흥면, 남쪽은 방학동, 북쪽은 의정부시와 접해 있다.
+          <t xml:space="preserve">동쪽은 한천(漢川)을 끼고 상계동과 이웃하고, 서쪽은 우이동과 양주군 장흥면, 남쪽은 방학동, 북쪽은 의정부시와 접해 있다.
 동명은 도봉산 아래에 마을이 위치한 데서 유래되었다.
 1963년 성북구에 편입되면서 도봉동이 되었고, 1973년 도봉구 관할로 편입되었다.
 1975년 도봉동에서 방학동이 분동되어 나갔고, 1977년 도봉1·2동으로 분동되었다.
@@ -5281,11 +5250,11 @@
         </is>
       </c>
       <c r="M70" s="0">
-        <v>393</v>
+        <v>374</v>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">도봉구 북쪽 끝에 위치하고 있다.</t>
         </is>
       </c>
     </row>
@@ -5349,8 +5318,7 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">도봉구 중앙에 위치하고 있다.
-동쪽은 한천(漢川)을 사이에 두고 상계동과 이웃하고, 서쪽은 우이동, 남쪽은 창동 · 쌍문동, 북쪽은 도봉동과 접해있다.
+          <t xml:space="preserve">동쪽은 한천(漢川)을 사이에 두고 상계동과 이웃하고, 서쪽은 우이동, 남쪽은 창동 · 쌍문동, 북쪽은 도봉동과 접해있다.
 동명 유래에 관해서는 조선시대에 왕이 도봉서원의 터를 정하기 위해 도봉산 중턱에 앉아 중다리를 내려다보다가 학이 평화롭게 노는 모습을 보고, 이 마을을 ‘방학굴(골)’이라 칭하였다는 설이 있으며, 또 하나는 이곳 지형이 학이 알을 품고 있는 것 같다고 하여 ‘방학(放鶴)’으로 칭하였다는 설이 있다.
 1963년 성북구에 편입되면서 방학동이 되었고, 1973년 도봉구 관할로 편입되었다.
 1975년 도봉동에서 분동하였으며, 1980년 방학1·2동으로 분동, 1988년 2동이 다시 2·3동으로 분동되었다.
@@ -5361,11 +5329,11 @@
         </is>
       </c>
       <c r="M71" s="0">
-        <v>592</v>
+        <v>575</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">도봉구 중앙에 위치하고 있다.</t>
         </is>
       </c>
     </row>
@@ -5428,8 +5396,7 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">도봉구 서쪽에 위치하고 있다.
-동쪽은 창동, 서쪽과 남쪽은 수유동, 북쪽은 방학동과 접해 있다.
+          <t xml:space="preserve">동쪽은 창동, 서쪽과 남쪽은 수유동, 북쪽은 방학동과 접해 있다.
 동명은 이곳에 효자문 2개가 세워진 데서 비롯되었다고 전해진다.
 일설에는 현 창동우체국 부근에 열녀문(烈女門)이 두 개 있었다 하여 붙여진 이름이라는 설과, 쌍갈래 길에 이문(里門)이 있었는데, 이것을 ‘쌍갈무니’라 하던 것이 ‘쌍문’이 되었다는 설도 있다.
 1963년 성북구에 편입되면서 쌍문동이 되었고, 1973년 도봉구 관할로 편입되었다.
@@ -5439,11 +5406,11 @@
         </is>
       </c>
       <c r="M72" s="0">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">도봉구 서쪽에 위치하고 있다.</t>
         </is>
       </c>
     </row>
@@ -5507,8 +5474,7 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">도봉구 남쪽에 위치하고 있다.
-동쪽은 상계동, 서쪽은 쌍문동, 남쪽은 번동, 북쪽은 방학동과 접해 있다.
+          <t xml:space="preserve">동쪽은 상계동, 서쪽은 쌍문동, 남쪽은 번동, 북쪽은 방학동과 접해 있다.
 동명은 조선시대 이곳에 양곡(糧穀) 창고가 있었던 데서 비롯되었다.
 1963년 성북구에 편입되면서 창동이 되었고, 1973년 도봉구 관할이 되었다.
 1988년 노원구로 관할이 바뀌었다가 1989년 다시 도봉구로 편입되었다.
@@ -5521,11 +5487,11 @@
         </is>
       </c>
       <c r="M73" s="0">
-        <v>620</v>
+        <v>603</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">도봉구 남쪽에 위치하고 있다.</t>
         </is>
       </c>
     </row>
@@ -5589,8 +5555,7 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동대문구 남쪽에 위치하고 있다.
-동쪽은 장안동, 서쪽은 마장동 · 제기동, 남쪽은 천호대로를 경계로 한 용답동과 군자동, 북쪽은 전농동 · 청량리동이 접해 있다.
+          <t xml:space="preserve">동쪽은 장안동, 서쪽은 마장동 · 제기동, 남쪽은 천호대로를 경계로 한 용답동과 군자동, 북쪽은 전농동 · 청량리동이 접해 있다.
 조선 초기 무학대사(無學大師)가 왕도를 정하려고 이곳을 밟았다 하여 동명을 ‘답심리(踏尋里)’라 했다는 구전이 있으며, 동대문으로부터 10리 정도 떨어진 거리에 있었기 때문에 왕십리와 같이 답십리라는 동명이 붙여진 것이고도 한다.
 1943년 동대문구에 속하였다가 1946년 답십리동으로 바뀌었다.
 답십리근린공원, 간데메공원, 동대문문화회관 등이 자리하고 있다.
@@ -5598,11 +5563,12 @@
         </is>
       </c>
       <c r="M74" s="0">
-        <v>336</v>
+        <v>318</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">한국전쟁 이후부터 농업은 인구 집중 현상에 따라 점차 사라지고 현재는 도로변에 상가지역이, 그 밖의 지역은 대부분 주택가가 자리잡고 있다.
+          <t xml:space="preserve">동대문구 남쪽에 위치하고 있다.
+한국전쟁 이후부터 농업은 인구 집중 현상에 따라 점차 사라지고 현재는 도로변에 상가지역이, 그 밖의 지역은 대부분 주택가가 자리잡고 있다.
 현재 답십리 지역엔 자동차 부품상가, 고미술상가 등 특화거리가 조성되어 있다.</t>
         </is>
       </c>
@@ -5666,8 +5632,7 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동대문구 서쪽에 위치하고 있다.
-동쪽은 종로구 숭인동, 서쪽은 용두동, 남쪽은 성동구 상왕십리동, 북쪽은 용두동과 성북구 안암동이 접해 있다.
+          <t xml:space="preserve">동쪽은 종로구 숭인동, 서쪽은 용두동, 남쪽은 성동구 상왕십리동, 북쪽은 용두동과 성북구 안암동이 접해 있다.
 조선시대 동부숭신방(東部崇信坊)에 새로 설치한 마을이라 하여 신설계(新設契)라 한 데서 동명이 유래되었다.
 신설동은 새로 마을이 만들어졌다 하여 ‘새말’ 또는 ‘신리(新里)’라고 하였다.
 1943년 동대문구에 속하였고, 1946년 신설동으로 바뀌었다.
@@ -5675,11 +5640,12 @@
         </is>
       </c>
       <c r="M75" s="0">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">공공시설로는 동부교육지원청, 동대문도서관, 동대문우체국, 동대문등기소, 성북수도사업소 등과 우산각 공원이 위치하고 있다.</t>
+          <t xml:space="preserve">동대문구 서쪽에 위치하고 있다.
+공공시설로는 동부교육지원청, 동대문도서관, 동대문우체국, 동대문등기소, 성북수도사업소 등과 우산각 공원이 위치하고 있다.</t>
         </is>
       </c>
     </row>
@@ -5743,8 +5709,7 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동대문구 서쪽에 위치하고 있다.
-동쪽은 신설동, 서쪽은 답십리동, 남쪽은 성동구 마장동 · 상왕십리동, 북쪽은 제기동과 접해 있다.
+          <t xml:space="preserve">동쪽은 신설동, 서쪽은 답십리동, 남쪽은 성동구 마장동 · 상왕십리동, 북쪽은 제기동과 접해 있다.
 동명은 마을을 감싸고 있는 산의 모습이 용(龍)의 머리와 같이 생겼다 하여 붙여진 이름이다.
 1943년 동대문구 관할이었다가 1946년 용두동으로 바뀌었다.
 왕산로 · 하정로 · 청계천로가 시작되는 곳이며, 남북으로 고산자로가 지나고, 지하철 1호선 제기역이 있다.
@@ -5752,11 +5717,12 @@
         </is>
       </c>
       <c r="M76" s="0">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">청량리 청과물시장, 수산업협동조합 서울공판장, 건설자재시험소, 한국직업관리공단, 폐차부품상가, 용두시장 등이 있고, 동대문구청, 한의약 전시관 · 문화관, 용두근린공원이 조성되어 있다.</t>
+          <t xml:space="preserve">동대문구 서쪽에 위치하고 있다.
+청량리 청과물시장, 수산업협동조합 서울공판장, 건설자재시험소, 한국직업관리공단, 폐차부품상가, 용두시장 등이 있고, 동대문구청, 한의약 전시관 · 문화관, 용두근린공원이 조성되어 있다.</t>
         </is>
       </c>
     </row>
@@ -5819,8 +5785,7 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동대문구 북쪽 끝에 위치하고 있다.
-동쪽은 중랑천(中浪川)을 사이에 두고 중랑구 면목동과 이웃하고, 서쪽은 회기동, 남쪽은 휘경동, 북쪽은 성북구 석관동과 접해 있다.
+          <t xml:space="preserve">동쪽은 중랑천(中浪川)을 사이에 두고 중랑구 면목동과 이웃하고, 서쪽은 회기동, 남쪽은 휘경동, 북쪽은 성북구 석관동과 접해 있다.
 마을에 도둑을 지키는 이문(里門)이 있어, 우리말로 ‘이문골’, ‘이문안’이라고 불리던 것을 한자로 ‘이문동(里門洞)’이라 한데서 동명이 유래되었다.
 1943년 동대문구에 속한 뒤, 1946년 이문동으로 바뀌었다.
 1975년 성북구 석관동 일부가 이문2동에 편입되었다.
@@ -5831,11 +5796,11 @@
         </is>
       </c>
       <c r="M77" s="0">
-        <v>512</v>
+        <v>492</v>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">동대문구 북쪽 끝에 위치하고 있다.</t>
         </is>
       </c>
     </row>
@@ -5899,8 +5864,7 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동대문구 동남쪽에 위치하고 있다.
-동쪽은 성동구 중곡동, 서쪽은 답십리동, 남쪽은 성동구 군자동, 북쪽은 전농동과 중랑구 면목동과 접해 있다.
+          <t xml:space="preserve">동쪽은 성동구 중곡동, 서쪽은 답십리동, 남쪽은 성동구 군자동, 북쪽은 전농동과 중랑구 면목동과 접해 있다.
 조선시대 목마장(牧馬場)으로 유명했던 ‘장안벌’, 즉 ‘장안평(長安坪)’에서 동명이 유래되었다.
 1975년 성동구 중곡동과 군자동 일부를 합해 신설된 동으로서 역사가 짧다.
 목마장을 농토로 일구기 시작하면서 농토가 비옥해지자 일제강점기 토지조사사업을 통해 동양척식주식회사에 소속되었다.
@@ -5911,11 +5875,12 @@
         </is>
       </c>
       <c r="M78" s="0">
-        <v>499</v>
+        <v>480</v>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">천호대로, 한천로, 장안로, 사가정 길 외에도 중랑천을 따라 도로를 개설해 교통이 편리하다.
+          <t xml:space="preserve">동대문구 동남쪽에 위치하고 있다.
+천호대로, 한천로, 장안로, 사가정 길 외에도 중랑천을 따라 도로를 개설해 교통이 편리하다.
 장한로변에는 호텔과 유흥업소가 밀집해 있다.</t>
         </is>
       </c>
@@ -5979,19 +5944,18 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동대문구 동쪽에 위치하고 있다.
-동쪽은 답십리, 서쪽은 중구 신당동, 남쪽은 성동구 마장동, 북쪽은 신설동과 접해있다.
+          <t xml:space="preserve">동쪽은 답십리, 서쪽은 중구 신당동, 남쪽은 성동구 마장동, 북쪽은 신설동과 접해있다.
 조선시대 왕의 친경지(親耕地)였던, 전농(典農)이라고도 하는 적전(籍田)이 있었던 데서 동명이 유래되었다.
 1943년 동대문구에 속해 있다가 1946년 전농동으로 바뀌었다.
 서울 동부지역 철도교통의 관문인 청량리역(淸凉里驛)이 있으며, 배봉산(拜峰山) 아래 서울시립대학교와 배봉산근린공원이 위치하고 있다.</t>
         </is>
       </c>
       <c r="M79" s="0">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">동대문구 동쪽에 위치하고 있다.</t>
         </is>
       </c>
     </row>
@@ -6056,8 +6020,7 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동대문구 서쪽에 위치하고 있다.
-동쪽은 청량리동, 서쪽은 안암동, 남쪽은 용두동, 북쪽은 성북구 종암동과 접해 있다.
+          <t xml:space="preserve">동쪽은 청량리동, 서쪽은 안암동, 남쪽은 용두동, 북쪽은 성북구 종암동과 접해 있다.
 조선시대 국왕이 풍년을 기원하기 위해 마을의 친경대(親耕臺), 즉 선농단을 만들어 친히 제사를 지내던 자리로 ‘제터’라고 부르던 데서 동명이 유래되었다.
 1943년 동대문구에 편입된 뒤 1946년 제기동으로 바뀌었다.
 조선시대에는 토지가 비옥하고 야채와 토란 산지로 유명하였다.
@@ -6068,11 +6031,12 @@
         </is>
       </c>
       <c r="M80" s="0">
-        <v>469</v>
+        <v>451</v>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">지금도 경동시장에는 각 지방에서 들어오는 토산품 시장으로 성시를 이룬다.
+          <t xml:space="preserve">동대문구 서쪽에 위치하고 있다.
+지금도 경동시장에는 각 지방에서 들어오는 토산품 시장으로 성시를 이룬다.
 또한 전국 한약재의 70%가 유통되고 있는 경동약령시(京東藥令市)와 그 외 경동시장, 청량리시장, 동서시장 등이 있다.</t>
         </is>
       </c>
@@ -6138,8 +6102,7 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동대문구 서북쪽에 위치하고 있다.
-동쪽은 휘경동, 남쪽은 전농동, 서쪽은 제기동, 북쪽은 회기동과 성북구 종암동에 접해 있다.
+          <t xml:space="preserve">동쪽은 휘경동, 남쪽은 전농동, 서쪽은 제기동, 북쪽은 회기동과 성북구 종암동에 접해 있다.
 청량사(淸凉寺)라는 사찰이 있는 데서 동명이 유래되었다.
 1943년 동대문구에 속한 뒤, 1946년 청량리동으로 바뀌었다.
 청량리1동은 청량리 로터리 부근으로 한림대학교 부속 동산병원, 청량리세무서, 청량리정신병원 등이 있고, 청량리2동에는 산림청, 임업연구원, 동대문경찰서, 세종대왕기념관, 영휘원 등이 있다.
@@ -6149,11 +6112,11 @@
         </is>
       </c>
       <c r="M81" s="0">
-        <v>524</v>
+        <v>505</v>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">동대문구 서북쪽에 위치하고 있다.</t>
         </is>
       </c>
     </row>
@@ -6217,8 +6180,7 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동대문구 북쪽에 위치하고 있다.
-동쪽과 남쪽은 청량리동, 서쪽은 휘경동, 북쪽은 이문동과 접해 있다.
+          <t xml:space="preserve">동쪽과 남쪽은 청량리동, 서쪽은 휘경동, 북쪽은 이문동과 접해 있다.
 조선시대 연산군의 생모 폐비(廢妃) 윤씨(尹氏)의 묘소인 회묘(懷墓: 현 西三陵 경내 이장)가 있어 동명이 유래되었다.
 1943년 동대문구에 속한 뒤, 1946년 회기동으로 바뀌었다.
 남동쪽으로 망우로와 이문로가 지나고, 회기로가 동서로 관통하며, 지하철 1호선인 회기역이 있다.
@@ -6228,11 +6190,11 @@
         </is>
       </c>
       <c r="M82" s="0">
-        <v>344</v>
+        <v>326</v>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">동대문구 북쪽에 위치하고 있다.</t>
         </is>
       </c>
     </row>
@@ -6295,19 +6257,18 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동대문구 북쪽에 위치하고 있다.
-동쪽은 회기동 · 이문동, 서쪽은 중랑구 면목동, 남쪽은 전농동, 북쪽은 이문동과 접해 있다.
+          <t xml:space="preserve">동쪽은 회기동 · 이문동, 서쪽은 중랑구 면목동, 남쪽은 전농동, 북쪽은 이문동과 접해 있다.
 조선시대 순조의 생모인 수빈박씨의 묘소인 휘경원(徽慶園: 西三陵 이장)에서 동명이 유래되었다.
 망우로, 이문로, 한천로, 중랑천 고수부지에 동부고속화도로가 있고, 전철역인 회기역과 휘경역이 있다.
 건설공무원교육원, 국립건설시험소, 서울위생병원, 국립농업자재검사소, 축산진흥원 등이 있고, 삼육간호보건대학이 있다.</t>
         </is>
       </c>
       <c r="M83" s="0">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">동대문구 북쪽에 위치하고 있다.</t>
         </is>
       </c>
     </row>
@@ -6435,8 +6396,7 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동작구 서쪽에 위치한 동이다.
-동쪽은 노량진동 · 상도동, 남쪽은 신대방동, 서쪽은 영등포구 신길동, 북쪽은 한강을 경계로 여의도와 접하고 있다.
+          <t xml:space="preserve">동쪽은 노량진동 · 상도동, 남쪽은 신대방동, 서쪽은 영등포구 신길동, 북쪽은 한강을 경계로 여의도와 접하고 있다.
 성남중고등학교 운동장에는 용마(龍馬)가 났다는 용마우물이 있고, 학교 뒷산을 용마산이라 하는데, 용마우물에서 용이 나와 산으로 올라갔다고 하여 붙여진 이름이다.
 1943년 영등포구 관할로 되었다.
 1973년 관악구 관할로 바뀌었고, 1980년 동작구 신설로 이에 속하게 되었다.
@@ -6444,11 +6404,11 @@
         </is>
       </c>
       <c r="M85" s="0">
-        <v>333</v>
+        <v>316</v>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">동작구 서쪽에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -6511,8 +6471,7 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동작구 동쪽에 위치한 동이다.
-동쪽은 서초구 반포동, 서쪽은 흑석동 · 상도동, 남쪽은 사당동, 북쪽은 흑석동과 한강에 접해 있다.
+          <t xml:space="preserve">동쪽은 서초구 반포동, 서쪽은 흑석동 · 상도동, 남쪽은 사당동, 북쪽은 흑석동과 한강에 접해 있다.
 조선시대에 용산(龍山)에서 수원(水源)으로 통하는 나루터의 하나였던 동작진(銅雀津), 즉 ‘동재기나루터’라고 부른 데서 동명이 유래되었다.
 1946년 동작동으로 바뀌었고, 1973년 관악구 관할로 되었으며, 1980년 동작구로 이관되었다.
 조선시대 동작진이 있던 자리에 동작대교가 놓여 강남과 강북을 이어주고, 동작대로가 사당사거리를 거쳐 경기도 과천시와 연결된다.
@@ -6522,11 +6481,11 @@
         </is>
       </c>
       <c r="M86" s="0">
-        <v>459</v>
+        <v>442</v>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">동작구 동쪽에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -6589,8 +6548,7 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동작구 북쪽에 위치한 동이다.
-한강대교의 남안(南岸) 지역으로 동쪽은 흑석동, 서쪽은 노량진동, 남쪽은 상도동, 북쪽은 올림픽대로와 한강에 접해 있다.
+          <t xml:space="preserve">한강대교의 남안(南岸) 지역으로 동쪽은 흑석동, 서쪽은 노량진동, 남쪽은 상도동, 북쪽은 올림픽대로와 한강에 접해 있다.
 조선시대부터 오랫동안 불리어오던 자연부락 이름으로 노량진(鷺梁津)의 ‘원마을’이라는 뜻에서 동명이 유래되었다.
 1943년 영등포구에 속하게 되었고, 1973년 관악구를 거쳐 1980년 동작구 신설로 편입되었다.
 용산구 한강로와 이 동을 잇는 한강대교가 있고, 현충로가 동서로 지나며, 노량진로가 영등포로터리까지 이른다.
@@ -6599,11 +6557,11 @@
         </is>
       </c>
       <c r="M87" s="0">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">동작구 북쪽에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -6667,8 +6625,7 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동작구 동남쪽에 위치한 동이다.
-동쪽은 관악구 봉천동, 서쪽은 서초구 방배동, 남쪽은 관악구 신림동, 북쪽은 동작동과 접해 있다.
+          <t xml:space="preserve">동쪽은 관악구 봉천동, 서쪽은 서초구 방배동, 남쪽은 관악구 신림동, 북쪽은 동작동과 접해 있다.
 옛날 큰 사당이 있었던 마을인 데서 동명이 유래하였다.
 1963년 서울특별시에 편입되면서 사당동으로 바뀌었다.
 1973년 관악구 관할로 되었으며, 1980년 동작구 신설로 이에 속하게 되었다.
@@ -6682,11 +6639,11 @@
         </is>
       </c>
       <c r="M88" s="0">
-        <v>569</v>
+        <v>551</v>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">동작구 동남쪽에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -6815,8 +6772,7 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동작구 중앙에 위치한 동이다.
-동쪽은 흑석동, 서쪽은 대방동과 신대방동, 남쪽은 관악구 봉천동, 북쪽은 노량진동과 접해 있다.
+          <t xml:space="preserve">동쪽은 흑석동, 서쪽은 대방동과 신대방동, 남쪽은 관악구 봉천동, 북쪽은 노량진동과 접해 있다.
 오래전 이 지역에 상여꾼들이 집단으로 거주하여 ‘상투굴’이라고 부른 데서 동명이 유래하였다.
 1943년 영등포구역소 관할 아래 있다가 1946년 상도동으로 바뀌었고, 1973년 관악구 소속으로 되었으며, 1980년 동작구로 이관되었다.
 동서로 횡단하는 상도동길과 장승배기길, 관악로 등이 있으며, 한강대교 확장과 함께 준공된 상도터널이 도심과 상도동을 직선으로 연결하고 있다.
@@ -6826,11 +6782,12 @@
         </is>
       </c>
       <c r="M90" s="0">
-        <v>610</v>
+        <v>593</v>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상도2동 영도시장 맞은편 삼거리 일대를 장승배기라고 하는데, 이정표 역할을 하던 장승이 있었던 곳이다.</t>
+          <t xml:space="preserve">동작구 중앙에 위치한 동이다.
+상도2동 영도시장 맞은편 삼거리 일대를 장승배기라고 하는데, 이정표 역할을 하던 장승이 있었던 곳이다.</t>
         </is>
       </c>
     </row>
@@ -6893,8 +6850,7 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동작구 서쪽에 위치한 동이다.
-동쪽은 관악구 봉천동과 상도동, 서쪽은 구로구 신도림동, 남쪽은 관악구 신림동, 북쪽은 대방동과 영등포구 신길동에 접해 있다.
+          <t xml:space="preserve">동쪽은 관악구 봉천동과 상도동, 서쪽은 구로구 신도림동, 남쪽은 관악구 신림동, 북쪽은 대방동과 영등포구 신길동에 접해 있다.
 대방동 근방의 새로 생긴 마을인 데서 동명이 유래하였다.
 1949년 영등포구에 편입되었고, 1973년 관악구 신설로 이에 속하게 되었다.
 1975년 동의 일부가 영등포구 신길동에 편입되었고, 1980년 동작구로 이관되었다.
@@ -6909,11 +6865,12 @@
         </is>
       </c>
       <c r="M91" s="0">
-        <v>726</v>
+        <v>709</v>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">공군본부와 해군본부가 이전한 자리에는 아파트단지가 들어섰다.</t>
+          <t xml:space="preserve">동작구 서쪽에 위치한 동이다.
+공군본부와 해군본부가 이전한 자리에는 아파트단지가 들어섰다.</t>
         </is>
       </c>
     </row>
@@ -6976,8 +6933,7 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동작구 동북쪽에 위치한 동이다.
-한강대교와 동작대교 사이의 남쪽에 있으며, 동 · 서 · 남쪽의 3면이 산으로 둘러싸여 있다.
+          <t xml:space="preserve">한강대교와 동작대교 사이의 남쪽에 있으며, 동 · 서 · 남쪽의 3면이 산으로 둘러싸여 있다.
 동쪽은 동작동, 서쪽은 본동, 남쪽은 상도동, 북쪽은 한강과 접해 있다.
 흑석1동사무소 남쪽 일대에서 나오는 돌의 빛이 검은색을 띠어 ‘검은돌[黑石]’ 마을이라 한 데서 동명이 유래되었다.
 1946년 흑석동으로 바뀌었고, 1973년 관악구 관할로 되었으며, 1980년 동작구로 이관되었다.
@@ -6986,11 +6942,12 @@
         </is>
       </c>
       <c r="M92" s="0">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">흑석시장 뒤편에는 조석견과 완성군(莞城君) 이귀정 묘역이 있다.</t>
+          <t xml:space="preserve">동작구 동북쪽에 위치한 동이다.
+흑석시장 뒤편에는 조석견과 완성군(莞城君) 이귀정 묘역이 있다.</t>
         </is>
       </c>
     </row>
@@ -7051,8 +7008,7 @@
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">마포구 동부에 위치한 동이다.
-동명은 우리말 높은 언덕을 의미하는 ‘큰더기’가 음이 비슷한 한자로 옮겨지면서 붙여진 것이라는 설과, 유교에서 딴 이름이라는 설이 있다.
+          <t xml:space="preserve">동명은 우리말 높은 언덕을 의미하는 ‘큰더기’가 음이 비슷한 한자로 옮겨지면서 붙여진 것이라는 설과, 유교에서 딴 이름이라는 설이 있다.
 조선시대 한성부 성저십리(城底十里)에 속하였고, 1895년 한성부 서서(西署) 용산방(성외) 공덕리계에 포함되었다.
 1911년 경성부 용산면(龍山面)에 속하였다가 1914년 경기도 고양군(高陽郡) 용강면(龍江面) 공덕리(孔德里)가 되었다.
 1936년 경성부 공덕정(孔德町)이 되었으며, 1943년에는 서대문구에 편입되었다가 이듬해 마포구 공덕정이 되었다.
@@ -7062,11 +7018,12 @@
         </is>
       </c>
       <c r="M93" s="0">
-        <v>384</v>
+        <v>367</v>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">지하철 공덕역에서는 5호선과 6호선이 교차하고 있어 교통이 편리하다.</t>
+          <t xml:space="preserve">마포구 동부에 위치한 동이다.
+지하철 공덕역에서는 5호선과 6호선이 교차하고 있어 교통이 편리하다.</t>
         </is>
       </c>
     </row>
@@ -7347,8 +7304,7 @@
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">마포구 동부에 위치한 동이다.
-이 마을은 독을 구워 파는 것을 업으로 삼는 곳이라는 의미에서 ‘독막(甕幕)’ 또는 ‘독마을(甕里)’로 불리던 곳이었데, 음의 변전을 겪다가 일제강점기에 붙여진 이름이다.
+          <t xml:space="preserve">이 마을은 독을 구워 파는 것을 업으로 삼는 곳이라는 의미에서 ‘독막(甕幕)’ 또는 ‘독마을(甕里)’로 불리던 곳이었데, 음의 변전을 겪다가 일제강점기에 붙여진 이름이다.
 조선시대 한성부 성저십리(城底十里)였으며, 1895년 한성부 서서(西署) 용산방(성외) 옹리하계로 칭하였다.
 1911년 경성부 용산면(龍山面) 동막하계(東幕下契)로 되었다가, 1914년 경기도 고양군 용강면 동막하리가 되었다.
 1936년 경성부 대흥정(大興町)이라 하였고, 1943년 용산구 관할이 되었다가 이듬해 마포구 대흥정이 되었다.
@@ -7357,11 +7313,11 @@
         </is>
       </c>
       <c r="M97" s="0">
-        <v>370</v>
+        <v>353</v>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">마포구 동부에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -7422,8 +7378,7 @@
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">마포구 남부에 위치한 동이다.
-동명은 이곳에 복숭아나무가 많고 봄철이 되면 복사꽃이 피어 경치가 좋아 ‘복사골’이라 부르던 데서 유래하였다.
+          <t xml:space="preserve">동명은 이곳에 복숭아나무가 많고 봄철이 되면 복사꽃이 피어 경치가 좋아 ‘복사골’이라 부르던 데서 유래하였다.
 조선시대 한성부 성저십리(城底十里)였으며, 1895년 한성부 서서(西署) 용산방(성외) 도화동계 외동 · 내동, 마포계였다.
 1911년 경성부 관할이었다가 1914년 경기도 도화정(桃花町)이 되었다.
 1943년 용산구 관할이었다가 이듬해 마포구 도화정이 되었다.
@@ -7433,11 +7388,11 @@
         </is>
       </c>
       <c r="M98" s="0">
-        <v>314</v>
+        <v>297</v>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">마포구 남부에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -7646,8 +7601,7 @@
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">마포구 남부에 위치한 동이다.
-동명은 한강변의 명소인 망원정(望遠亭)이 있었던 데서 유래한다.
+          <t xml:space="preserve">동명은 한강변의 명소인 망원정(望遠亭)이 있었던 데서 유래한다.
 조선시대 한성부 성저십리에 속하였으며, 1895년 한성부 북서(北署) 연희방(성외) 망원정계에 속하였다.
 1911년 경성부 관할이었다가, 1914년 경기도 고양군 연희면 망원리가 되었다.
 1936년 경성부 망원정(望遠町)이 되었고, 1943년 서대문구에 편입되었다가, 이듬해 마포구 망원정이 되었다.
@@ -7657,11 +7611,11 @@
         </is>
       </c>
       <c r="M101" s="0">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">마포구 남부에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -7722,8 +7676,7 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">마포구 남부에 위치한 동으로, 동명은 한강 가의 마을 중에서 위쪽에 있는 마을인 데서 유래한다.
-조선시대 한성부 성저십리(城底十里)에 속하였고, 1895년 한성부 서서(西署) 서강방(西江坊, 성외) 상수일리계(上水溢里契) 하수일리였다.
+          <t xml:space="preserve">조선시대 한성부 성저십리(城底十里)에 속하였고, 1895년 한성부 서서(西署) 서강방(西江坊, 성외) 상수일리계(上水溢里契) 하수일리였다.
 1911년 경성부의 관할이었다가 1914년 경기도 고양군 용강면 상수일리가 되었다.
 1936년 경성부 상수일정(上水溢町)이 되었고 1943년 서대문구에 소속되었다가, 1944년 마포구 상수일정이 되었으며, 1946년 마포구 상수동이 되었다.
 1989년 하수동을 상수동에 편입시켰다.
@@ -7731,11 +7684,11 @@
         </is>
       </c>
       <c r="M102" s="0">
-        <v>306</v>
+        <v>252</v>
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">마포구 남부에 위치한 동으로, 동명은 한강 가의 마을 중에서 위쪽에 있는 마을인 데서 유래한다.</t>
         </is>
       </c>
     </row>
@@ -7796,8 +7749,7 @@
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">마포구 서부에 위치한 동이다.
-동명은 옛날 이 지역의 상수리(水上里)의 ‘상(上)’자와 휴암리(休岩里)의 ‘암(岩)’자를 따서 지은 것이다.
+          <t xml:space="preserve">동명은 옛날 이 지역의 상수리(水上里)의 ‘상(上)’자와 휴암리(休岩里)의 ‘암(岩)’자를 따서 지은 것이다.
 조선시대 한성부 북부(성외) 수암리계(水岩里契), 수생리계(水生里契)에 속하였고, 1895년 한성부 북서(北署) 연희방(성외) 수상리계(水上里契) 수상리(水上里), 음월리계(陰月里契) 휴암(休岩)이라 하였다.
 1911년 경성부의 관할이었다가 1914년 경기도 고양군 연희면 상암리가 되었고 1936년 은평면에 편입되었다.
 1949년 서울시 서대문구로 편입되어 이듬해 서대문구 상암동이 되었고, 1975년 마포구로 편입되었다.
@@ -7805,11 +7757,11 @@
         </is>
       </c>
       <c r="M103" s="0">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">마포구 서부에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -7943,8 +7895,7 @@
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">마포구 서북부에 위치한 동이다.
-동명은 부근의 산이 성같이 둘러 있어서 우리말로 ‘성메’, ‘성미’로 부르던 것을 한자로 옮긴 것이다.
+          <t xml:space="preserve">동명은 부근의 산이 성같이 둘러 있어서 우리말로 ‘성메’, ‘성미’로 부르던 것을 한자로 옮긴 것이다.
 조선시대 한성부 성저십리(城底十里)에 속하였으며, 1895년 한성부 북서(北署) 연희방(延禧坊, 城外) 성산리계(城山里契) 중동(中洞) · 야지동(野芝洞) · 후동(後洞) · 무이동(武夷洞) · 야동(冶洞)에 속하였다.
 1911년 경성부의 관할이었다가 1914년 경기도 고양군 연희면 성산리라고 하였으며, 1936년에는 은평면(恩平面)에 속하였다.
 1949년 서대문구에 편입되었고, 이듬해 서대문구 성산동으로 되었으며, 1975년에 마포구 성산동이 되었다.
@@ -7954,11 +7905,12 @@
         </is>
       </c>
       <c r="M105" s="0">
-        <v>461</v>
+        <v>443</v>
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">인근의 마포농수산물시장은 서부 지역 농산물 유통의 중심으로 각광을 받고 있다.</t>
+          <t xml:space="preserve">마포구 서북부에 위치한 동이다.
+인근의 마포농수산물시장은 서부 지역 농산물 유통의 중심으로 각광을 받고 있다.</t>
         </is>
       </c>
     </row>
@@ -8014,13 +7966,12 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">판정보류</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">마포구 동부에 위치한 동이다.
-동명은 옛이름 공덕리에서 비롯되었으며, 우리말 ‘큰더기’에서 유래된 것으로 보인다.
+          <t xml:space="preserve">동명은 옛이름 공덕리에서 비롯되었으며, 우리말 ‘큰더기’에서 유래된 것으로 보인다.
 조선시대 한성부 성저십리(城底十里)에 속하였으며, 1895년 한성부 서서(西署) 용산방 신창내계(新倉內契) 신창내(新倉內), 공덕리계(孔德里契) 흥례동(興禮洞) · 신동(新洞)이라 하였다.
 1911년 경성부의 관할이었다가 1914년 경기도 고양군 용강면 신공덕리가 되었고, 1936년 경성부 신공덕정(新孔德町)이 되었다.
 1943년 서대문구에 편입되었다가 이듬해 마포구 신공덕정이 되었다.
@@ -8028,11 +7979,11 @@
         </is>
       </c>
       <c r="M106" s="0">
-        <v>308</v>
+        <v>291</v>
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">마포구 동부에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -8093,8 +8044,7 @@
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">마포구 남부에 위치한 동이다.
-동명은 수철리(水鐵里)에서 기원하였다.
+          <t xml:space="preserve">동명은 수철리(水鐵里)에서 기원하였다.
 조선시대 한성부 성저십리(城底十里)에 속하였으며, 1895년 한성부 서서(西署) 서강방(성외) 신수철리계 신수철리였다.
 1911년 경성부 관할이었다가, 1914년 경기도 고양군 용강면 신수철리로 되었다.
 1936년 경성부 신수정(新水町)이 되고, 1943년 서대문구에 편입되었다가 이듬해 마포구 신수정이 되었다.
@@ -8103,11 +8053,11 @@
         </is>
       </c>
       <c r="M107" s="0">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">마포구 남부에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -8241,8 +8191,7 @@
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">마포구 동부에 위치한 동이다.
-동명은 ‘애고개’, ‘애우개’, ‘아이고개’, 즉 ‘아현(兒峴)’으로 부르던 것이 ‘아(兒)’가 ‘아(阿)’로 변하여 ‘아현(阿峴)’이 되었다.
+          <t xml:space="preserve">동명은 ‘애고개’, ‘애우개’, ‘아이고개’, 즉 ‘아현(兒峴)’으로 부르던 것이 ‘아(兒)’가 ‘아(阿)’로 변하여 ‘아현(阿峴)’이 되었다.
 조선시대 한성부 성저십리(城底十里)에 속하였으며, 1895년 한성부 서서(西署) 반송방(성외) 권정승계, 아현계, 차자리계(車子里契)에 속하였다.
 1911년 경성부 관할이 되었다가 1914년 경기도 고양군 용강면 아현리가 되었다.
 1936년 경성부 아현정(阿峴町)이 되고, 1943년 서대문구에 편입되었다가 이듬해 마포구 아현정이 되었다.
@@ -8254,11 +8203,11 @@
         </is>
       </c>
       <c r="M109" s="0">
-        <v>478</v>
+        <v>461</v>
       </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">마포구 동부에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -8314,13 +8263,12 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">판정보류</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">마포구 북부에 위치한 동이다.
-동명은 연희동에서 갈려 나와 연희동 남쪽에 위치한다는 뜻에서 붙여진 이름이다.
+          <t xml:space="preserve">동명은 연희동에서 갈려 나와 연희동 남쪽에 위치한다는 뜻에서 붙여진 이름이다.
 조선시대 한성부 성저십리(城底十里)에 속하였으며, 1895년 한성부 북서(北署) 연희방(성외) 정자동계(亭子洞契), 염동일계(廉洞一契), 음월리계(陰月里契), 세교이계(細橋二契)에 속하였다.
 1911년 경성부 관할이 되었다가 1914년 경기도 고양군 연희면 연희리가 되었다.
 1936년 경성부 연희정(延禧町)이 되었고, 1943년 경성부 용산구 대흥정(大興町)으로 바뀌었으며, 1944년 서대문구 연희정이 되었다.
@@ -8328,11 +8276,11 @@
         </is>
       </c>
       <c r="M110" s="0">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="N110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">마포구 북부에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -8393,8 +8341,7 @@
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">마포구 동부에 위치한 동이다.
-동명은 이 마을에 옛날부터 소금장수들이 많이 살았기 때문에 붙여진 이름이다.
+          <t xml:space="preserve">동명은 이 마을에 옛날부터 소금장수들이 많이 살았기 때문에 붙여진 이름이다.
 조선시대 한성부 성저십리(城底十里)에 속하였으며, 1895년 한성부 서서(西署) 용산방(성외) 공덕리계 염동(鹽洞)이었다.
 1911년 경성부 관할이었다가 1914년 경기도 고양군 용강면(龍江面) 염리가 되었다.
 1936년 경성부 염리정(鹽里町)이 되었고, 1943년 용산구에 편입되었다가 1944년 마포구 염리정이 되었다.
@@ -8403,11 +8350,11 @@
         </is>
       </c>
       <c r="M111" s="0">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">마포구 동부에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -8468,8 +8415,7 @@
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">마포구 남부에 위치한 동이다.동명은 용산의 ‘용(龍)’자와 서강의 ‘강(江)’자를 따서 붙인 것이다.
-조선시대 한성부 성저십리(城底十里)에 속하였으며, 1895년 한성부 서서(西署) 용산방(성외) 옹리상계, 옹리중계, 옹리하계라 하였다.
+          <t xml:space="preserve">조선시대 한성부 성저십리(城底十里)에 속하였으며, 1895년 한성부 서서(西署) 용산방(성외) 옹리상계, 옹리중계, 옹리하계라 하였다.
 1911년 경성부 관할이었다가 1914년 경기도 고양군 용강면(龍江面) 동막상리(東幕上里)라고 하였다.
 1936년 경성부 용강정(龍江町)이 되었고, 1943년 용산구에 편입되었다가 1944년 마포구 용강정이 되었다.
 광복 후인 1946년 마포구 용강동으로 이름을 바꾸었다.
@@ -8477,11 +8423,11 @@
         </is>
       </c>
       <c r="M112" s="0">
-        <v>365</v>
+        <v>308</v>
       </c>
       <c r="N112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">마포구 남부에 위치한 동이다.동명은 용산의 ‘용(龍)’자와 서강의 ‘강(江)’자를 따서 붙인 것이다.</t>
         </is>
       </c>
     </row>
@@ -8542,19 +8488,18 @@
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">마포구 북부에 위치한 동으로, 중동의 행정은 성산2동사무소에서 담당하고 있다.
-동명은 마을의 한 가운데 있기 때문에 붙여진 것이다.
+          <t xml:space="preserve">동명은 마을의 한 가운데 있기 때문에 붙여진 것이다.
 조선시대 한성부 성저십리(城底十里)에 속하였으며, 1895년 한성부 북서(北署) 연희방(성외) 성산리계 중동에 속하였다.
 1911년 경성부 관할이었다가 1914년 경기도 고양군 연희면(延禧面) 중리라고 하였으며, 1936년 고양군 은평면(恩平面) 중리가 되었다.
 광복 후인 1946년 서대문구에 편입되었으며, 1975년 마포구 중동이 되었다.</t>
         </is>
       </c>
       <c r="M113" s="0">
-        <v>265</v>
+        <v>221</v>
       </c>
       <c r="N113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">마포구 북부에 위치한 동으로, 중동의 행정은 성산2동사무소에서 담당하고 있다.</t>
         </is>
       </c>
     </row>
@@ -8979,19 +8924,19 @@
       </c>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">서대문구의 서부에 위치한 동이다.
-조선시대 한성부 북부(北部, 城外) 가좌동계(加佐洞契) 가재율이었으며, 1895년 한성부 북서(北署) 연희방(성외) 가좌동1계에 속하였다.
+          <t xml:space="preserve">조선시대 한성부 북부(北部, 城外) 가좌동계(加佐洞契) 가재율이었으며, 1895년 한성부 북서(北署) 연희방(성외) 가좌동1계에 속하였다.
 1911년 경성부 연희면 가좌동1계 월사동이라 하였다가 1914년 경기도 고양군 연희면 남가좌리(南加佐里)로 변경되었다.
 1936년 경성부에 편입되었고, 1946년 서대문구 남가좌동이 되었다.
 행정동으로는 남가좌1동과 남가좌2동의 2개 동이 있다.</t>
         </is>
       </c>
       <c r="M119" s="0">
-        <v>235</v>
+        <v>216</v>
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동명은 이 마을에 가재가 있고 산에 둘러싸였기 때문에 ‘가재율’이라 부르던 자연 마을을 한자로 가좌동(加佐洞)이라 부르게 되었으며, 인구가 증가하면서 남북으로 나뉘었다.
+          <t xml:space="preserve">서대문구의 서부에 위치한 동이다.
+동명은 이 마을에 가재가 있고 산에 둘러싸였기 때문에 ‘가재율’이라 부르던 자연 마을을 한자로 가좌동(加佐洞)이라 부르게 되었으며, 인구가 증가하면서 남북으로 나뉘었다.
 수색로 옆의 오래된 모래내시장은 서민들이 자주 찾는 곳이고, 대학으로는 명지대학교가 있다.</t>
         </is>
       </c>
@@ -9419,18 +9364,18 @@
       </c>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">서대문구의 서부에 위치한 동이다.
-조선시대 한성부 북부(北部, 城外) 가좌동이계(加佐洞二契)였으며, 1895년 한성부 북서(北署) 연희방(성외) 가좌동2계에 속하였다.
+          <t xml:space="preserve">조선시대 한성부 북부(北部, 城外) 가좌동이계(加佐洞二契)였으며, 1895년 한성부 북서(北署) 연희방(성외) 가좌동2계에 속하였다.
 1911년 경성부 관할이 되었으며, 1914년 경기도 고양군 연희면 북가좌리(北加佐里)로 변경되었고, 광복 후 1946년에 서대문구 북가좌동이 되었다.
 행정동은 북가좌1동과 북가좌2동의 2개 동이 있다.</t>
         </is>
       </c>
       <c r="M125" s="0">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="N125" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동명은 이 마을에 가재가 있고 산으로 둘러싸였기 때문에 ‘가재율’이라 부르던 자연 마을을 한자로 가좌동(加佐洞)이라 부르게 되었으며, 인구가 증가하면서 남북으로 나뉘었다.</t>
+          <t xml:space="preserve">서대문구의 서부에 위치한 동이다.
+동명은 이 마을에 가재가 있고 산으로 둘러싸였기 때문에 ‘가재율’이라 부르던 자연 마을을 한자로 가좌동(加佐洞)이라 부르게 되었으며, 인구가 증가하면서 남북으로 나뉘었다.</t>
         </is>
       </c>
     </row>
@@ -9491,8 +9436,7 @@
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">서대문구의 동남부에 위치한 동이다.
-동명은 애오개, 즉 아이고개에서 비롯되었으며, 1914년 아현의 북쪽에 위치하여 아현 북리라 한 것이 시초이다.
+          <t xml:space="preserve">동명은 애오개, 즉 아이고개에서 비롯되었으며, 1914년 아현의 북쪽에 위치하여 아현 북리라 한 것이 시초이다.
 조선시대에는 한성부 성외 지역이었으며, 1895년에는 한성부 서서(西署) 반송방 아현계 · 북부 연희방 아현1계로 하였다.
 1911년 경성부 연희면(延禧面) 아현북리(阿峴北里)로, 1914년 경기도 고양군 연희면 아현북리로 칭하였다.
 1936년 경성부 북아현정(北阿峴町)이 되었으며, 1943년 서대문구에 속하였고, 1946년 서대문구 북아현동이 되었다.
@@ -9501,11 +9445,11 @@
         </is>
       </c>
       <c r="M126" s="0">
-        <v>328</v>
+        <v>308</v>
       </c>
       <c r="N126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">서대문구의 동남부에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -9859,8 +9803,7 @@
       </c>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">서대문구의 남부에 위치한 동이다.
-동명은 이 지역을 흐르는 하천인 창천(滄川)에서 유래되었다.
+          <t xml:space="preserve">동명은 이 지역을 흐르는 하천인 창천(滄川)에서 유래되었다.
 조선시대에는 한성부 성저십리(城底十里)였으며, 1895년 한성부 북서(北署) 연희방(성외) 아현3계 창천이라 하였다.
 1911년 경성부 소속이 되었다가 1914년 경기도 고양군 연희면 창천리가 되었다.
 1936년 경성부 창천정(滄川町)으로 변경되었고, 1943년 서대문구 관할이 되었으며, 1946년 서대문구 창천동으로 하였다.
@@ -9868,11 +9811,11 @@
         </is>
       </c>
       <c r="M131" s="0">
-        <v>253</v>
+        <v>234</v>
       </c>
       <c r="N131" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">서대문구의 남부에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -9933,19 +9876,18 @@
       </c>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">서대문구의 동부에 위치한 동이다.
-동명은 이 지역에 천연정(天然亭)이란 정자가 있었기 때문에 붙여진 이름이다.
+          <t xml:space="preserve">동명은 이 지역에 천연정(天然亭)이란 정자가 있었기 때문에 붙여진 이름이다.
 조선시대 한성부 서부 반송방(盤松坊, 城外)에 속했으며, 1895년 서부 반송방 지하계 석교동(石橋洞) · 이판동(李判洞)이라 하였다.
 1911년 경성부 관할이 되었고, 1914년 경성부 천연동이라 하였다.
 1936년 천연정(天然町)으로 변경되었고, 1943년 서대문구 관할이 되었으며, 1946년 서대문구 천연동으로 하였다.</t>
         </is>
       </c>
       <c r="M132" s="0">
-        <v>244</v>
+        <v>225</v>
       </c>
       <c r="N132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">서대문구의 동부에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -10006,8 +9948,7 @@
       </c>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">서대문구의 동부에 위치한 동으로 법정동인 충정로2가와 충정로3가의 행정은 충정로동사무소에서 담당하고 있다.
-충정로의 동명은 충정공(忠正公) 민영환(閔泳煥)의 시호를 따서 붙여진 이름이다.
+          <t xml:space="preserve">충정로의 동명은 충정공(忠正公) 민영환(閔泳煥)의 시호를 따서 붙여진 이름이다.
 조선시대 한성부 서부 반송방(盤松坊, 城外)에 속했으며, 1895년 서부 반송방 노첨정계(盧僉正契), 조판부사계(曺判府事契) 유동 · 팔각정, 수근답계(水芹畓契) 근동, 지하계(池下契) 냉동(冷洞), 차자리계(車子里契) 아현(阿峴) · 형제정(兄弟井)이라 하였다.
 1911년 경성부 관할이 되었고, 1914년 경성부 죽첨정2정목(竹添町2丁目)이라 하였다.
 죽첨정은 갑신정변 때 일본공사 죽첨진일랑(竹添進一郞)이 충정로 부근의 민가에 거주한 일이 있었던 것을 기념하는 뜻으로 일제가 정하게 된 것이다.
@@ -10016,11 +9957,12 @@
         </is>
       </c>
       <c r="M133" s="0">
-        <v>484</v>
+        <v>424</v>
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">지하철 5호선이 지나고 있어 교통이 편리하다.</t>
+          <t xml:space="preserve">서대문구의 동부에 위치한 동으로 법정동인 충정로2가와 충정로3가의 행정은 충정로동사무소에서 담당하고 있다.
+지하철 5호선이 지나고 있어 교통이 편리하다.</t>
         </is>
       </c>
     </row>
@@ -10081,8 +10023,7 @@
       </c>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">서대문구의 동부에 위치한 동으로 법정동인 충정로2가와 충정로3가의 행정은 충정로동사무소에서 담당하고 있다.
-충정로의 동명은 충정공(忠正公) 민영환(閔泳煥)의 시호를 따서 붙여진 이름이다.
+          <t xml:space="preserve">충정로의 동명은 충정공(忠正公) 민영환(閔泳煥)의 시호를 따서 붙여진 이름이다.
 조선시대 한성부 서부 반송방(盤松坊, 城外)에 속했으며, 1895년 서부 반송방 노첨정계(盧僉正契), 조판부사계(曺判府事契) 유동 · 팔각정, 수근답계(水芹畓契) 근동, 지하계(池下契) 냉동(冷洞), 차자리계(車子里契) 아현(阿峴) · 형제정(兄弟井)이라 하였다.
 1911년 경성부 관할이 되었고, 1914년 경성부 죽첨정2정목(竹添町2丁目)이라 하였다.
 죽첨정은 갑신정변 때 일본공사 죽첨진일랑(竹添進一郞)이 충정로 부근의 민가에 거주한 일이 있었던 것을 기념하는 뜻으로 일제가 정하게 된 것이다.
@@ -10091,11 +10032,12 @@
         </is>
       </c>
       <c r="M134" s="0">
-        <v>484</v>
+        <v>424</v>
       </c>
       <c r="N134" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">지하철 5호선이 지나고 있어 교통이 편리하다.</t>
+          <t xml:space="preserve">서대문구의 동부에 위치한 동으로 법정동인 충정로2가와 충정로3가의 행정은 충정로동사무소에서 담당하고 있다.
+지하철 5호선이 지나고 있어 교통이 편리하다.</t>
         </is>
       </c>
     </row>
@@ -10156,8 +10098,7 @@
       </c>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">서대문구의 동부에 위치한 동이다.
-동명은 조선시대 어물 가운데 조개가 끊어지지 않았기 때문에 이곳을 ‘조개전’이라 하였고, 이것이 합동(蛤洞)이 된 것이라 전한다.
+          <t xml:space="preserve">동명은 조선시대 어물 가운데 조개가 끊어지지 않았기 때문에 이곳을 ‘조개전’이라 하였고, 이것이 합동(蛤洞)이 된 것이라 전한다.
 조선시대 한성부 서부 반석방(盤石坊), 반송방(盤松坊)에 속했으며, 1895년 서부 반석방 미전하계(米廛下契) · 합동 한림동(翰林洞), 반송방 수근답계(水芹畓契) 근동(芹洞)이라 하였다.
 1911년 경성부 관할이 되었고, 1914년 경성부 합동이라 하였다.
 1936년 합정(蛤町)으로 변경되었고, 1943년 서대문구 관할이 되었으며, 1946년 서대문구 천연동이 되었다.
@@ -10165,11 +10106,12 @@
         </is>
       </c>
       <c r="M135" s="0">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="N135" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">합동의 행정은 충정로동사무소에서 담당하고 있다.</t>
+          <t xml:space="preserve">서대문구의 동부에 위치한 동이다.
+합동의 행정은 충정로동사무소에서 담당하고 있다.</t>
         </is>
       </c>
     </row>
@@ -10302,8 +10244,7 @@
       </c>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">서대문구의 서북부에 위치한 동이다.
-동명은 홍제외리(弘濟外里)의 ‘홍’(弘)자와 은평면의 ‘은’(恩)자를 따서 붙여진 것이다.
+          <t xml:space="preserve">동명은 홍제외리(弘濟外里)의 ‘홍’(弘)자와 은평면의 ‘은’(恩)자를 따서 붙여진 것이다.
 조선시대에 한성부 성저십리(城底十里)였으며, 1895년에는 북서(北署) 홍은방(성외) 홍제원계 답동(畓洞) · 백련동(白蓮洞) · 외동(外洞)이라 하였다.
 1911년 경성부 관할이 되었다가 1914년 경기도 고양군 은평면 홍제외리가 되었다.
 1936년 경성부의 관할구역 확장 때 홍제외리 중에서 홍제천 좌변 지역만 경성부에 편입되었고, 1949년에 서대문구 홍은동이 되었다.
@@ -10312,11 +10253,12 @@
         </is>
       </c>
       <c r="M137" s="0">
-        <v>382</v>
+        <v>362</v>
       </c>
       <c r="N137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동쪽으로 홍체천이 흐르고 하천을 따라 내부순환로가 지나며, 지하철 3호선이 관통하고 있어 교통이 편리하다.</t>
+          <t xml:space="preserve">서대문구의 서북부에 위치한 동이다.
+동쪽으로 홍체천이 흐르고 하천을 따라 내부순환로가 지나며, 지하철 3호선이 관통하고 있어 교통이 편리하다.</t>
         </is>
       </c>
     </row>
@@ -10370,24 +10312,24 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">판정보류</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">서대문구의 동북부에 위치한 동이다.
-동명은 조선시대 중국 사신이 유숙하던 홍제원(弘濟院)이 있었던 데서 유래하였다.
+          <t xml:space="preserve">동명은 조선시대 중국 사신이 유숙하던 홍제원(弘濟院)이 있었던 데서 유래하였다.
 조선시대 한성부 성저십리(城底十里)였으며, 1895년에는 북서(北署) 연은방(延恩坊, 성외) 홍제원계 내동이라 하였다.
 1911년 경성부 관할이 되었다가 1914년 경기도 고양군 은평면 홍제내리가 되었다.
 1936년 경성부 홍제정(弘濟町)이 되었고, 1943년 서대문구에 소속되었으며, 1949년에 서대문구 홍제동이 되었다.</t>
         </is>
       </c>
       <c r="M138" s="0">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="N138" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">서쪽으로 홍제천이 흐르고 내부순환로가 지나고 있으며, 지하철 3호선이 관통하고 있어 교통이 편리하다.</t>
+          <t xml:space="preserve">서대문구의 동북부에 위치한 동이다.
+서쪽으로 홍제천이 흐르고 내부순환로가 지나고 있으며, 지하철 3호선이 관통하고 있어 교통이 편리하다.</t>
         </is>
       </c>
     </row>
@@ -10519,8 +10461,7 @@
       </c>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 서북부에 위치한 동이다.
-반포동의 동명 유래는 이 마을로 흐르는 개울이 서리서리 구비 흐른다 하여 ‘서릿개’ 곧 반포(蟠浦)라 하다가 변음되어 반포(盤浦)로 칭하게 되었다 한다.
+          <t xml:space="preserve">반포동의 동명 유래는 이 마을로 흐르는 개울이 서리서리 구비 흐른다 하여 ‘서릿개’ 곧 반포(蟠浦)라 하다가 변음되어 반포(盤浦)로 칭하게 되었다 한다.
 또 일설에는 이곳이 홍수의 피해를 입는 상습 침수지역이므로 반포라 칭했다고도 한다.
 내곡동은 조선시대 말까지 경기도 과천군(果川郡) 상북면(上北面)이었으며, 1914년 시흥군(始興郡) 신동면(新東面) 반포리(盤浦里)라 하였고, 1963년에는 서울시 행정구역 확장에 따라 영등포구 반포동이 되었다.
 이후 1973년에는 성동구, 1975년에는 강남구, 1988년에는 서초구의 법정동이 되었다.
@@ -10531,11 +10472,11 @@
         </is>
       </c>
       <c r="M140" s="0">
-        <v>514</v>
+        <v>497</v>
       </c>
       <c r="N140" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 서북부에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -10591,23 +10532,23 @@
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">판정보류</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 서부에 위치한 동이다.
-방배동의 동명 유래는 우면산을 등지고 있는 동리라는 뜻의 방배(方背)라 한 데서 붙여졌다.
+          <t xml:space="preserve">방배동의 동명 유래는 우면산을 등지고 있는 동리라는 뜻의 방배(方背)라 한 데서 붙여졌다.
 방배동은 조선시대 말까지 경기도 과천군(果川郡) 상북면(上北面) 방배리(方背里)였으며, 1914년 시흥군(始興郡) 신동면(新東面) 방배리라 하였고, 1963년에는 서울시 행정구역 확장에 따라 영등포구 방배동이 되었다.
 이후 1973년에는 관악구, 1980년 강남구, 1988년에는 서초구의 법정동이 되었다.</t>
         </is>
       </c>
       <c r="M141" s="0">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="N141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">지하철 7호선과 2호선이 동서로 관통하고 있으며, 방배로 · 사평로 · 사당로가 거미줄같이 연결되어 교통이 편리하다.</t>
+          <t xml:space="preserve">구의 서부에 위치한 동이다.
+지하철 7호선과 2호선이 동서로 관통하고 있으며, 방배로 · 사평로 · 사당로가 거미줄같이 연결되어 교통이 편리하다.</t>
         </is>
       </c>
     </row>
@@ -10737,24 +10678,23 @@
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">판정보류</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 동남부에 위치한 동으로 인근의 내곡동에서 행정을 담당하고 있다.
-신원동의 동명 유래는 조선시대 원터 아래쪽에 새로 조성된 마을이므로 ‘새원’이라 하던 것을 한자명으로 신원동(新院洞)이라 한 것이다.
+          <t xml:space="preserve">신원동의 동명 유래는 조선시대 원터 아래쪽에 새로 조성된 마을이므로 ‘새원’이라 하던 것을 한자명으로 신원동(新院洞)이라 한 것이다.
 서초동은 조선시대 말까지 경기도 광주군(廣州郡) 언주면(彦州面) 신원리(新院里), 신정리(新亭里)였으며, 1914년 광주군 언주면 신원리라 하였고, 1963년에는 서울시 행정구역 확장에 따라 성동구 신원동이 되었다.
 이후 1973년에는 성동구, 1975년 강남구, 1988년에는 서초구의 법정동이 되었다.
 이 지역은 경부고속도로가 지나고 있으며, 서울특별시라는 느낌이 안들 정도로 한적하고 아직까지 논농사가 이루어지는 곳이다.</t>
         </is>
       </c>
       <c r="M143" s="0">
-        <v>352</v>
+        <v>313</v>
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 동남부에 위치한 동으로 인근의 내곡동에서 행정을 담당하고 있다.</t>
         </is>
       </c>
     </row>
@@ -10963,8 +10903,7 @@
       </c>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 남부에 위치한 동으로 이 지역의 행정업무는 양재1동에서 담당하고 있다.
-우면동의 동명은 우면산 아래 골짜기에 있는 마을이라 하여 유래되었다.
+          <t xml:space="preserve">우면동의 동명은 우면산 아래 골짜기에 있는 마을이라 하여 유래되었다.
 우면동은 조선시대 말까지 경기도 과천군(果川郡) 동면(東面) 우면리(牛眠里)였으며, 1914년 시흥군(始興郡) 신동면 우면리라 하였고, 1963년에는 서울시 행정구역 확장에 따라 영등포구 우면동이 되었다.
 이후 1973년에는 성동구, 1975년 강남구, 1988년에는 서초구의 법정동이 되었다.
 문화유산으로는 관문사에 소장된 보물이 있으며, 박물관으로는 분재박물관이 있고, 민속놀이로 우면두레가 있다.
@@ -10972,11 +10911,12 @@
         </is>
       </c>
       <c r="M146" s="0">
-        <v>381</v>
+        <v>338</v>
       </c>
       <c r="N146" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">과천 · 우면산 간 연결도로가 우면산터널을 통해 연결되어 교통이 편리하며, 대부분의 지역이 우면산 주변에 자리잡고 있어 공기가 맑고 주민들은 근교농업에 종사하고 있다.</t>
+          <t xml:space="preserve">구의 남부에 위치한 동으로 이 지역의 행정업무는 양재1동에서 담당하고 있다.
+과천 · 우면산 간 연결도로가 우면산터널을 통해 연결되어 교통이 편리하며, 대부분의 지역이 우면산 주변에 자리잡고 있어 공기가 맑고 주민들은 근교농업에 종사하고 있다.</t>
         </is>
       </c>
     </row>
@@ -11037,19 +10977,18 @@
       </c>
       <c r="L147" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 동남부에 위치한 동으로 이 지역의 행정업무는 양재2동이 담당하고 있다.
-원지동의 동명 유래는 조선시대에 이곳에 원(院)이 있었던 곳이기에 원지(院址)라고 칭하던 것을 한자 표기의 잘못으로 원지동(院趾洞)이 되었다고 한다.
+          <t xml:space="preserve">원지동의 동명 유래는 조선시대에 이곳에 원(院)이 있었던 곳이기에 원지(院址)라고 칭하던 것을 한자 표기의 잘못으로 원지동(院趾洞)이 되었다고 한다.
 원지동은 조선시대 말까지 경기도 과천군(果川郡) 동면(東面) 신원리(新院里)였으며, 1914년 시흥군(始興郡) 신동면 신원리라 하였고, 1963년에는 서울시 행정구역 확장에 따라 영등포구에 편입되면서 현재의 신원동과 분리하여 바람골, 양수리, 원터마을을 원지동이라 하였다.
 이후 1973년에는 성동구, 1975년 강남구, 1988년에는 서초구의 법정동이 되었다.
 대부분의 지역이 산악지대이고 일부 지역에서 논농사와 근교농업을 하고 있다.</t>
         </is>
       </c>
       <c r="M147" s="0">
-        <v>371</v>
+        <v>328</v>
       </c>
       <c r="N147" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 동남부에 위치한 동으로 이 지역의 행정업무는 양재2동이 담당하고 있다.</t>
         </is>
       </c>
     </row>
@@ -11103,23 +11042,23 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">판정보류</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 서북부에 위치한 동이다.
-잠원동의 동명 유래는 조선 초기에 국립양잠소격인 잠실도회(蠶室都會)가 이곳에 설치되어 잠실리(蠶室里)라 칭하던 것을 1963년 서울시에 편입될 때 이미 현 송파구에 잠실동이 있으므로 중복을 피하기 위해 잠실리의 ‘잠’(蠶)자와 인근 신동면(新東面) 신원리(新院里)의 ‘원’(院)자를 따서 잠원동(蠶院洞)이라 한 것이다.
+          <t xml:space="preserve">잠원동의 동명 유래는 조선 초기에 국립양잠소격인 잠실도회(蠶室都會)가 이곳에 설치되어 잠실리(蠶室里)라 칭하던 것을 1963년 서울시에 편입될 때 이미 현 송파구에 잠실동이 있으므로 중복을 피하기 위해 잠실리의 ‘잠’(蠶)자와 인근 신동면(新東面) 신원리(新院里)의 ‘원’(院)자를 따서 잠원동(蠶院洞)이라 한 것이다.
 잠원동은 조선시대 말까지 경기도 과천군(果川郡) 상북면(上北面) 잠실리(蠶室里)와 사평리(沙平里)였으며, 1914년 시흥군(始興郡) 신동면 잠실리라 하였고, 1963년에는 서울시 행정구역 확장에 따라 영등포구에 편입되면서 잠원동이라 하였다.
 이후 1973년에는 성동구, 1975년 강남구, 1988년에는 서초구의 법정동이 되었다.</t>
         </is>
       </c>
       <c r="M148" s="0">
-        <v>380</v>
+        <v>363</v>
       </c>
       <c r="N148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">한강변으로 한강시민공원 잠원지구가 있으며, 아파트가 밀집되어 있고, 한남대교를 이용하여 강북으로의 이동이 편리하고 지하철 3호선과 7호선이 지나 교통이 편리하다.</t>
+          <t xml:space="preserve">구의 서북부에 위치한 동이다.
+한강변으로 한강시민공원 잠원지구가 있으며, 아파트가 밀집되어 있고, 한남대교를 이용하여 강북으로의 이동이 편리하고 지하철 3호선과 7호선이 지나 교통이 편리하다.</t>
         </is>
       </c>
     </row>
@@ -11180,8 +11119,7 @@
       </c>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성동구의 동서부에 위치한 동이다.
-금호동의 옛 이름은 수철리(水鐵里)이며, 금호동(金湖洞)의 ‘금’(金)은 수철리의 ‘철’(鐵)에서, ‘호’(湖)는 ‘수’(水)에서 인용하여 금호동이라 하였다.
+          <t xml:space="preserve">금호동의 옛 이름은 수철리(水鐵里)이며, 금호동(金湖洞)의 ‘금’(金)은 수철리의 ‘철’(鐵)에서, ‘호’(湖)는 ‘수’(水)에서 인용하여 금호동이라 하였다.
 조선시대 한성부 남부 두모방(豆毛坊, 城外) 수철리계(水鐵里契)였으며, 1911년 경성부 두모면 수철리라 하였다.
 1914년 경기도 고양군 한지면 수철리라 하였고, 1936년 경성부 금호정(金湖町)이 되었다.
 광복 후 1946년 성동구 금호동이 되었고, 1964년 금호동은 금호동1가 ·2가 ·3가 ·4가의 4개 법정동으로 분동되었고, 행정은 금호1가동에서 금호4가동까지 모두 4개의 동사무소가 있다.
@@ -11189,11 +11127,12 @@
         </is>
       </c>
       <c r="M149" s="0">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="N149" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동쪽에 남북으로 연결되는 동호로가 동호대교와 연계되고, 지하철 3호선이 지나고 있어 교통이 편리하다.</t>
+          <t xml:space="preserve">성동구의 동서부에 위치한 동이다.
+동쪽에 남북으로 연결되는 동호로가 동호대교와 연계되고, 지하철 3호선이 지나고 있어 교통이 편리하다.</t>
         </is>
       </c>
     </row>
@@ -11254,8 +11193,7 @@
       </c>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성동구의 동서부에 위치한 동이다.
-금호동의 옛 이름은 수철리(水鐵里)이며, 금호동(金湖洞)의 ‘금’(金)은 수철리의 ‘철’(鐵)에서, ‘호’(湖)는 ‘수’(水)에서 인용하여 금호동이라 하였다.
+          <t xml:space="preserve">금호동의 옛 이름은 수철리(水鐵里)이며, 금호동(金湖洞)의 ‘금’(金)은 수철리의 ‘철’(鐵)에서, ‘호’(湖)는 ‘수’(水)에서 인용하여 금호동이라 하였다.
 조선시대 한성부 남부 두모방(豆毛坊, 城外) 수철리계(水鐵里契)였으며, 1911년 경성부 두모면 수철리라 하였다.
 1914년 경기도 고양군 한지면 수철리라 하였고, 1936년 경성부 금호정(金湖町)이 되었다.
 광복 후 1946년 성동구 금호동이 되었고, 1964년 금호동은 금호동1가 ·2가 ·3가 ·4가의 4개 법정동으로 분동되었고, 행정은 금호1가동에서 금호4가동까지 모두 4개의 동사무소가 있다.
@@ -11263,11 +11201,12 @@
         </is>
       </c>
       <c r="M150" s="0">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="N150" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동쪽에 남북으로 연결되는 동호로가 동호대교와 연계되고, 지하철 3호선이 지나고 있어 교통이 편리하다.</t>
+          <t xml:space="preserve">성동구의 동서부에 위치한 동이다.
+동쪽에 남북으로 연결되는 동호로가 동호대교와 연계되고, 지하철 3호선이 지나고 있어 교통이 편리하다.</t>
         </is>
       </c>
     </row>
@@ -11328,8 +11267,7 @@
       </c>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성동구의 동서부에 위치한 동이다.
-금호동의 옛 이름은 수철리(水鐵里)이며, 금호동(金湖洞)의 ‘금’(金)은 수철리의 ‘철’(鐵)에서, ‘호’(湖)는 ‘수’(水)에서 인용하여 금호동이라 하였다.
+          <t xml:space="preserve">금호동의 옛 이름은 수철리(水鐵里)이며, 금호동(金湖洞)의 ‘금’(金)은 수철리의 ‘철’(鐵)에서, ‘호’(湖)는 ‘수’(水)에서 인용하여 금호동이라 하였다.
 조선시대 한성부 남부 두모방(豆毛坊, 城外) 수철리계(水鐵里契)였으며, 1911년 경성부 두모면 수철리라 하였다.
 1914년 경기도 고양군 한지면 수철리라 하였고, 1936년 경성부 금호정(金湖町)이 되었다.
 광복 후 1946년 성동구 금호동이 되었고, 1964년 금호동은 금호동1가 ·2가 ·3가 ·4가의 4개 법정동으로 분동되었고, 행정은 금호1가동에서 금호4가동까지 모두 4개의 동사무소가 있다.
@@ -11337,11 +11275,12 @@
         </is>
       </c>
       <c r="M151" s="0">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="N151" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동쪽에 남북으로 연결되는 동호로가 동호대교와 연계되고, 지하철 3호선이 지나고 있어 교통이 편리하다.</t>
+          <t xml:space="preserve">성동구의 동서부에 위치한 동이다.
+동쪽에 남북으로 연결되는 동호로가 동호대교와 연계되고, 지하철 3호선이 지나고 있어 교통이 편리하다.</t>
         </is>
       </c>
     </row>
@@ -11402,8 +11341,7 @@
       </c>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성동구의 동서부에 위치한 동이다.
-금호동의 옛 이름은 수철리(水鐵里)이며, 금호동(金湖洞)의 ‘금’(金)은 수철리의 ‘철’(鐵)에서, ‘호’(湖)는 ‘수’(水)에서 인용하여 금호동이라 하였다.
+          <t xml:space="preserve">금호동의 옛 이름은 수철리(水鐵里)이며, 금호동(金湖洞)의 ‘금’(金)은 수철리의 ‘철’(鐵)에서, ‘호’(湖)는 ‘수’(水)에서 인용하여 금호동이라 하였다.
 조선시대 한성부 남부 두모방(豆毛坊, 城外) 수철리계(水鐵里契)였으며, 1911년 경성부 두모면 수철리라 하였다.
 1914년 경기도 고양군 한지면 수철리라 하였고, 1936년 경성부 금호정(金湖町)이 되었다.
 광복 후 1946년 성동구 금호동이 되었고, 1964년 금호동은 금호동1가 ·2가 ·3가 ·4가의 4개 법정동으로 분동되었고, 행정은 금호1가동에서 금호4가동까지 모두 4개의 동사무소가 있다.
@@ -11411,11 +11349,12 @@
         </is>
       </c>
       <c r="M152" s="0">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="N152" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동쪽에 남북으로 연결되는 동호로가 동호대교와 연계되고, 지하철 3호선이 지나고 있어 교통이 편리하다.</t>
+          <t xml:space="preserve">성동구의 동서부에 위치한 동이다.
+동쪽에 남북으로 연결되는 동호로가 동호대교와 연계되고, 지하철 3호선이 지나고 있어 교통이 편리하다.</t>
         </is>
       </c>
     </row>
@@ -11471,13 +11410,12 @@
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">판정보류</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="L153" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성동구의 서북부에 위치한 동이다.
-동명의 유래는 통일신라의 도선대사(道詵大師)가 무학봉(舞鶴峰)에서 수도하여 도선대사의 이름을 따서 붙였다는 설, 조선 초에 무학대사가 도읍지를 물색할 때 왕십리에서 만난 노인이 현령(顯靈)한 도선국사라 생각하여 도선동이라고 했다는 설이 있다.
+          <t xml:space="preserve">동명의 유래는 통일신라의 도선대사(道詵大師)가 무학봉(舞鶴峰)에서 수도하여 도선대사의 이름을 따서 붙였다는 설, 조선 초에 무학대사가 도읍지를 물색할 때 왕십리에서 만난 노인이 현령(顯靈)한 도선국사라 생각하여 도선동이라고 했다는 설이 있다.
 조선시대 한성부 동부 인창방(仁昌坊, 城外) 왕십리(往十里)에 속하였고, 1911년 경기도 고양군 한지면에 속하였다.
 1914년 고양군 한지면 하왕십리였다가, 1936년 경성부 하왕십리정(下往十里町)이 되었다.
 1946년 성동구 하왕십리동으로 바꾸었고, 1963년 하왕십리동에서 분동되어 도선동이라 하였다.
@@ -11485,11 +11423,12 @@
         </is>
       </c>
       <c r="M153" s="0">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">이 지역의 행정업무를 담당하고 있는 도선동사무소는 홍익동의 행정도 겸하고 있다.</t>
+          <t xml:space="preserve">성동구의 서북부에 위치한 동이다.
+이 지역의 행정업무를 담당하고 있는 도선동사무소는 홍익동의 행정도 겸하고 있다.</t>
         </is>
       </c>
     </row>
@@ -11550,8 +11489,7 @@
       </c>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성동구의 북부에 위치한 동이다.
-동명은 조선 초기부터 말을 기르던 양마장(養馬場)이 이곳에 있어 유래되었다.
+          <t xml:space="preserve">동명은 조선 초기부터 말을 기르던 양마장(養馬場)이 이곳에 있어 유래되었다.
 조선시대 한성부 동부 인창방(仁昌坊, 城外) 마장리계(馬場里契)에 속하였고, 1895년 한성부 동서(東署) 인창방 동소문외계 마장리라 하였으며, 1911년 경성부 인창면 마장리라 하였다.
 1914년에는 경기도 고양군 한지면 마장리라 하고 1936년 경성부 마장정(馬場町)이 되었다.
 1946년에 성동구 마장동이 되었다.
@@ -11560,11 +11498,12 @@
         </is>
       </c>
       <c r="M154" s="0">
-        <v>367</v>
+        <v>349</v>
       </c>
       <c r="N154" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">이곳의 마장축산물시장과 서울축산물총판매장은 널리 알려져 있다.</t>
+          <t xml:space="preserve">성동구의 북부에 위치한 동이다.
+이곳의 마장축산물시장과 서울축산물총판매장은 널리 알려져 있다.</t>
         </is>
       </c>
     </row>
@@ -11625,8 +11564,7 @@
       </c>
       <c r="L155" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성동구의 북부에 위치한 동이다.
-동명은 이 마을에 사근절[沙斤寺]이 있었던 데서 유래하였다.
+          <t xml:space="preserve">동명은 이 마을에 사근절[沙斤寺]이 있었던 데서 유래하였다.
 조선시대 한성부 동부 인창방(仁昌坊, 城外)에 속하였고, 1895년 한성부 동서 인창방 사근리라 하였으며, 1911년 경성부 인창면 사근리라 하였다.
 1914년에는 경기도 고양군 한지면 사근리라 하고 1936년 경성부 사근정(沙斤町)이 되었다.
 1946년 성동구 사근동이 되었다.
@@ -11635,11 +11573,11 @@
         </is>
       </c>
       <c r="M155" s="0">
-        <v>307</v>
+        <v>289</v>
       </c>
       <c r="N155" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">성동구의 북부에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -11695,24 +11633,23 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">판정보류</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성동구의 서북부에 위치한 동이다.
-동명은 조선 초 무학대사(無學大師)가 도읍을 정할 때 이곳에서 노인을 만나 십리를 더 가라는 말을 듣고 도읍을 정했다는 설에 따라 만들어졌다는 것과 도성으로부터 10리 떨어진 거리에 있었기 때문에 답십리(踏十里)와 같이 왕십리(往十里)라는 동명이 생겨났다는 설이 있다.
+          <t xml:space="preserve">동명은 조선 초 무학대사(無學大師)가 도읍을 정할 때 이곳에서 노인을 만나 십리를 더 가라는 말을 듣고 도읍을 정했다는 설에 따라 만들어졌다는 것과 도성으로부터 10리 떨어진 거리에 있었기 때문에 답십리(踏十里)와 같이 왕십리(往十里)라는 동명이 생겨났다는 설이 있다.
 조선시대 한성부 동부 인창방(仁昌坊, 城外)에 속하였고, 1895년 한성부 동서 인창방 왕십리계였으며, 1911년 경성부 인창면에 속하였다.
 1914년에는 경기도 고양군 한지면 상왕십리가 되었고, 1936년 경성부 상왕십리정으로 바뀐 뒤 1946년에 성동구 상왕십리동이 되었다.
 위치는 동쪽에 도선동, 서쪽에 중구, 북쪽에 청계천, 남쪽에 하왕십리동이 접해 있다.</t>
         </is>
       </c>
       <c r="M156" s="0">
-        <v>373</v>
+        <v>354</v>
       </c>
       <c r="N156" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">성동구의 서북부에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -11773,8 +11710,7 @@
       </c>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성동구의 남동부에 위치한 동이다.
-동명은 조선시대 임금이 말 기르는 것과 군대의 훈련을 사열하던 성덕정(聖德亭)의 ‘성’(聖)자와 624번지 일대 뚝섬수원지(纛島水源池)의 ‘수’(水)자를 따서 붙인 데서 유래되었다.
+          <t xml:space="preserve">동명은 조선시대 임금이 말 기르는 것과 군대의 훈련을 사열하던 성덕정(聖德亭)의 ‘성’(聖)자와 624번지 일대 뚝섬수원지(纛島水源池)의 ‘수’(水)자를 따서 붙인 데서 유래되었다.
 조선시대 한성부 남부 두모방 전관일계(箭串一契)와 전관이계 전관동(箭串洞)이었으며, 1911년 경성부 두모면 뚝도일계(纛島一契)와 뚝도이계에 속하였다.
 1914년 경기도 고양군 뚝도면 서뚝도리와 동뚝도리라 하였고, 1949년에 성동구에 편입되어 뚝도출장소에서 행정을 담당하였다.
 이후 1950년에 성동구 성수동1가와 성수동2가의 법정동으로 분리되었다.
@@ -11785,11 +11721,11 @@
         </is>
       </c>
       <c r="M157" s="0">
-        <v>559</v>
+        <v>540</v>
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">성동구의 남동부에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -11850,8 +11786,7 @@
       </c>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성동구의 남동부에 위치한 동이다.
-동명은 조선시대 임금이 말 기르는 것과 군대의 훈련을 사열하던 성덕정(聖德亭)의 ‘성’(聖)자와 624번지 일대 뚝섬수원지(纛島水源池)의 ‘수’(水)자를 따서 붙인 데서 유래되었다.
+          <t xml:space="preserve">동명은 조선시대 임금이 말 기르는 것과 군대의 훈련을 사열하던 성덕정(聖德亭)의 ‘성’(聖)자와 624번지 일대 뚝섬수원지(纛島水源池)의 ‘수’(水)자를 따서 붙인 데서 유래되었다.
 조선시대 한성부 남부 두모방 전관일계(箭串一契)와 전관이계 전관동(箭串洞)이었으며, 1911년 경성부 두모면 뚝도일계(纛島一契)와 뚝도이계에 속하였다.
 1914년 경기도 고양군 뚝도면 서뚝도리와 동뚝도리라 하였고, 1949년에 성동구에 편입되어 뚝도출장소에서 행정을 담당하였다.
 이후 1950년에 성동구 성수동1가와 성수동2가의 법정동으로 분리되었다.
@@ -11862,11 +11797,11 @@
         </is>
       </c>
       <c r="M158" s="0">
-        <v>559</v>
+        <v>540</v>
       </c>
       <c r="N158" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">성동구의 남동부에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -11927,8 +11862,7 @@
       </c>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성동구의 동부에 위치한 동이다.
-동명은 정확한 유래는 알 수 없으며 조선시대 경기도 양주군(楊州郡) 고양주면(古楊州面)에 속하였다가 1895년 한성부 남서(南署) 두모방 전관계(箭串契) 장내능동(場內陵洞)이라 하였다.
+          <t xml:space="preserve">동명은 정확한 유래는 알 수 없으며 조선시대 경기도 양주군(楊州郡) 고양주면(古楊州面)에 속하였다가 1895년 한성부 남서(南署) 두모방 전관계(箭串契) 장내능동(場內陵洞)이라 하였다.
 1911년 경성부 두모면 장내능동이 되었고, 1914년 경기도 고양군 뚝도면(纛島面) 송정리(松亭里)라 하였다.
 1949년 서울시 성동구에 편입되어 1950년 송정동이 되었다.
 위치는 동쪽에 광진구, 서쪽에 중랑천, 북쪽에 용답동, 남쪽에 성수동2가가 접해 있다.
@@ -11936,11 +11870,11 @@
         </is>
       </c>
       <c r="M159" s="0">
-        <v>342</v>
+        <v>324</v>
       </c>
       <c r="N159" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">성동구의 동부에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -12001,8 +11935,7 @@
       </c>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성동구의 서남부에 위치한 동이다.
-조선시대 한성부 남부 두모방 두모포계(豆毛浦契)에 속하였다.
+          <t xml:space="preserve">조선시대 한성부 남부 두모방 두모포계(豆毛浦契)에 속하였다.
 1895년에는 한성부 남서 두모방 두모포계 두모동이라 하였고, 1911년 경성부 두모면 두모리에 속하였다.
 1914년에 경기도 고양군 한지면 두모리였고, 1936년 경성부 옥수정(玉水町)이 되었다.
 광복 후 1946년에 성동구 옥수동이 되었다.
@@ -12013,11 +11946,12 @@
         </is>
       </c>
       <c r="M160" s="0">
-        <v>353</v>
+        <v>334</v>
       </c>
       <c r="N160" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동명은 ‘옥정수’(玉井水)라는 유명한 우물이 있었으므로 ‘옥정숫골’로 불리었는데, 한자로 쓰면서 옥수동으로 되었다.
+          <t xml:space="preserve">성동구의 서남부에 위치한 동이다.
+동명은 ‘옥정수’(玉井水)라는 유명한 우물이 있었으므로 ‘옥정숫골’로 불리었는데, 한자로 쓰면서 옥수동으로 되었다.
 동쪽에 남북으로 연결되는 동호로가 동호대교와 연계되고 지하철 3호선이 지나고 있으며, 남쪽으로는 강변북로와 연결되어 교통이 편리하다.</t>
         </is>
       </c>
@@ -12079,8 +12013,7 @@
       </c>
       <c r="L161" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성동구의 북부에 위치한 동이다.
-동명은 용두동 지역과 답십리동 지역이 통합되어 이루어졌기 때문에 머리글자인 ‘용’(龍)자와 ‘답’(踏)자를 따서 지었다.
+          <t xml:space="preserve">동명은 용두동 지역과 답십리동 지역이 통합되어 이루어졌기 때문에 머리글자인 ‘용’(龍)자와 ‘답’(踏)자를 따서 지었다.
 조선시대 한성부 동부(東部) 인창방(仁昌坊) 답십리계(踏十里契)에 속하였고, 1895년 한성부 동서 인창방(성외) 용두리(龍頭里)라 하였다.
 1911년 경성부 인창면에 속하다가 1914년 경기도 고양군 숭인면에 속하였으며, 1936년 경성부 답십리정(踏十里町) · 용두정(龍頭町)이 되었다.
 1946년 동대문구 답십리동 · 용두동이 되었으며, 1975년 두 지역을 통합하여 용답동이라 하고 성동구에 편입하였다.
@@ -12089,11 +12022,11 @@
         </is>
       </c>
       <c r="M161" s="0">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="N161" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">성동구의 북부에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -12154,8 +12087,7 @@
       </c>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성동구의 중앙에 위치한 동이다.
-동명은 이곳에 있는 응봉산에서 유래되었다.
+          <t xml:space="preserve">동명은 이곳에 있는 응봉산에서 유래되었다.
 조선시대 한성부 남부 두모방 신촌리계(新村里契)에 속하였다.
 1895년 한성부 남서 두모방 신촌리계 신촌리동이라 하고, 1911년 경성부 두모면 신촌리에 속하였다.
 1914년 경기도 고양군 한지면 신촌리로 하고 1936년 경성부 응봉정(鷹峰町)이 되었다.
@@ -12165,11 +12097,11 @@
         </is>
       </c>
       <c r="M162" s="0">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="N162" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">성동구의 중앙에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -12225,24 +12157,23 @@
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">판정보류</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="L163" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성동구의 서북부에 위치한 동으로 동명에 대한 두 가지 설은 상왕십리동과 같다.
-조선시대 한성부 동부 인창방(仁昌坊, 城外)에 속하였고, 1895년 한성부 동서 인창방 왕십리계였으며, 1911년 경성부 인창면에 속하였다.
+          <t xml:space="preserve">조선시대 한성부 동부 인창방(仁昌坊, 城外)에 속하였고, 1895년 한성부 동서 인창방 왕십리계였으며, 1911년 경성부 인창면에 속하였다.
 1914년에는 경기도 고양군 한지면 하왕십리가 되었고, 1936년 경성부 하왕십리정으로 바뀐 뒤 1946년 성동구 하왕십리동이 되었다.
 위치는 동쪽에 도선동, 서쪽에 중구, 북쪽에 상왕십리동과 청계천, 남쪽에 행당동이 접해 있다.
 전통사찰로는 신라 때 창건되었다고 알려진 안정사(安靜寺)가 있고, 중앙교육진흥연구소와 무학초등학교가 있다.</t>
         </is>
       </c>
       <c r="M163" s="0">
-        <v>311</v>
+        <v>267</v>
       </c>
       <c r="N163" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">성동구의 서북부에 위치한 동으로 동명에 대한 두 가지 설은 상왕십리동과 같다.</t>
         </is>
       </c>
     </row>
@@ -12303,8 +12234,7 @@
       </c>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성동구의 중앙에 위치한 동이다.
-동명은 구전에 의하면 행당초등학교 동쪽 산 일대, 즉 아기씨당이 위치한 곳에 예로부터 살구나무와 은행나무가 많이 심어져 있었기 때문에 붙여진 이름이라고 한다.
+          <t xml:space="preserve">동명은 구전에 의하면 행당초등학교 동쪽 산 일대, 즉 아기씨당이 위치한 곳에 예로부터 살구나무와 은행나무가 많이 심어져 있었기 때문에 붙여진 이름이라고 한다.
 조선시대 한성부 남부 두모방(豆毛坊, 城外) 신촌리계(新村里契)에 속하였다.
 1895년 한성부 남서(南署) 두모방 신촌리계 행당리동이라 하였고, 1911년에는 경성부 두모면 행당리에 속하였다.
 1914년 경기도 고양군 한지면 행당리였고, 1936년에는 경성부 행당정(杏堂町)이 되었다.
@@ -12315,11 +12245,11 @@
         </is>
       </c>
       <c r="M164" s="0">
-        <v>479</v>
+        <v>461</v>
       </c>
       <c r="N164" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">성동구의 중앙에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -12526,8 +12456,7 @@
       </c>
       <c r="L167" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성북구의 중앙에 위치한 동이다.
-동명은 미아리고개의 옛 이름이 ‘되너미고개’이며 이것을 한자로 옮겨 돈암현(敦岩峴)이라 한 데서 비롯되었다.
+          <t xml:space="preserve">동명은 미아리고개의 옛 이름이 ‘되너미고개’이며 이것을 한자로 옮겨 돈암현(敦岩峴)이라 한 데서 비롯되었다.
 조선시대에 한성부 동부 숭신방에 속하였고, 1895년에는 한성부 동서 숭신방 동소문외계 돈암리(敦岩里)로 칭하였다.
 1911년 경성부 숭신면 돈암리로 칭하다가 1914년에 경기도 고양군 숭인면 돈암리가 되었다.
 1943년 구제도가 시행될 때 동대문구에 속했으며, 광복 후 돈암동이 되었고, 1949년 성북구 법정동이 되었다.
@@ -12536,11 +12465,11 @@
         </is>
       </c>
       <c r="M167" s="0">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="N167" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">성북구의 중앙에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -12601,8 +12530,7 @@
       </c>
       <c r="L168" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성북구의 중앙에 위치한 동이다.
-동명은 1949년 동소문동(東小門洞)과 삼선동(三仙洞)에서 각각 한 글자를 따서 이루어진 것이다.
+          <t xml:space="preserve">동명은 1949년 동소문동(東小門洞)과 삼선동(三仙洞)에서 각각 한 글자를 따서 이루어진 것이다.
 조선시대 한성부 동부 숭신방에 속하였고, 1895년에는 한성부 동서 숭신방 동소문외계 돈암리로 칭하였다.
 1911년 경성부 숭신면 돈암리로 칭하다가 1914년에 경기도 고양군 숭인면 돈암리가 되었다.
 1943년 구제도가 시행될 때 동대문구에 속했으며, 광복 후 돈암동이 되었고, 1949년 성북구의 돈암동이 되었다.
@@ -12611,11 +12539,12 @@
         </is>
       </c>
       <c r="M168" s="0">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="N168" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">따라서 동선동1가에서 동선동3가까지 법정동의 행정은 동선1동사무소에서 담당하며, 동선동4가와 동선동5가의 행정은 동선2동사무소에서 담당하고 있다.
+          <t xml:space="preserve">성북구의 중앙에 위치한 동이다.
+따라서 동선동1가에서 동선동3가까지 법정동의 행정은 동선1동사무소에서 담당하며, 동선동4가와 동선동5가의 행정은 동선2동사무소에서 담당하고 있다.
 지하철 4호선 성신여대입구역을 이용할 수 있어 교통이 편리하다.</t>
         </is>
       </c>
@@ -12677,8 +12606,7 @@
       </c>
       <c r="L169" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성북구의 중앙에 위치한 동이다.
-동명은 1949년 동소문동(東小門洞)과 삼선동(三仙洞)에서 각각 한 글자를 따서 이루어진 것이다.
+          <t xml:space="preserve">동명은 1949년 동소문동(東小門洞)과 삼선동(三仙洞)에서 각각 한 글자를 따서 이루어진 것이다.
 조선시대 한성부 동부 숭신방에 속하였고, 1895년에는 한성부 동서 숭신방 동소문외계 돈암리로 칭하였다.
 1911년 경성부 숭신면 돈암리로 칭하다가 1914년에 경기도 고양군 숭인면 돈암리가 되었다.
 1943년 구제도가 시행될 때 동대문구에 속했으며, 광복 후 돈암동이 되었고, 1949년 성북구의 돈암동이 되었다.
@@ -12687,11 +12615,12 @@
         </is>
       </c>
       <c r="M169" s="0">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="N169" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">따라서 동선동1가에서 동선동3가까지 법정동의 행정은 동선1동사무소에서 담당하며, 동선동4가와 동선동5가의 행정은 동선2동사무소에서 담당하고 있다.
+          <t xml:space="preserve">성북구의 중앙에 위치한 동이다.
+따라서 동선동1가에서 동선동3가까지 법정동의 행정은 동선1동사무소에서 담당하며, 동선동4가와 동선동5가의 행정은 동선2동사무소에서 담당하고 있다.
 지하철 4호선 성신여대입구역을 이용할 수 있어 교통이 편리하다.</t>
         </is>
       </c>
@@ -12753,8 +12682,7 @@
       </c>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성북구의 중앙에 위치한 동이다.
-동명은 1949년 동소문동(東小門洞)과 삼선동(三仙洞)에서 각각 한 글자를 따서 이루어진 것이다.
+          <t xml:space="preserve">동명은 1949년 동소문동(東小門洞)과 삼선동(三仙洞)에서 각각 한 글자를 따서 이루어진 것이다.
 조선시대 한성부 동부 숭신방에 속하였고, 1895년에는 한성부 동서 숭신방 동소문외계 돈암리로 칭하였다.
 1911년 경성부 숭신면 돈암리로 칭하다가 1914년에 경기도 고양군 숭인면 돈암리가 되었다.
 1943년 구제도가 시행될 때 동대문구에 속했으며, 광복 후 돈암동이 되었고, 1949년 성북구의 돈암동이 되었다.
@@ -12763,11 +12691,12 @@
         </is>
       </c>
       <c r="M170" s="0">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="N170" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">따라서 동선동1가에서 동선동3가까지 법정동의 행정은 동선1동사무소에서 담당하며, 동선동4가와 동선동5가의 행정은 동선2동사무소에서 담당하고 있다.
+          <t xml:space="preserve">성북구의 중앙에 위치한 동이다.
+따라서 동선동1가에서 동선동3가까지 법정동의 행정은 동선1동사무소에서 담당하며, 동선동4가와 동선동5가의 행정은 동선2동사무소에서 담당하고 있다.
 지하철 4호선 성신여대입구역을 이용할 수 있어 교통이 편리하다.</t>
         </is>
       </c>
@@ -12829,8 +12758,7 @@
       </c>
       <c r="L171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성북구의 중앙에 위치한 동이다.
-동명은 1949년 동소문동(東小門洞)과 삼선동(三仙洞)에서 각각 한 글자를 따서 이루어진 것이다.
+          <t xml:space="preserve">동명은 1949년 동소문동(東小門洞)과 삼선동(三仙洞)에서 각각 한 글자를 따서 이루어진 것이다.
 조선시대 한성부 동부 숭신방에 속하였고, 1895년에는 한성부 동서 숭신방 동소문외계 돈암리로 칭하였다.
 1911년 경성부 숭신면 돈암리로 칭하다가 1914년에 경기도 고양군 숭인면 돈암리가 되었다.
 1943년 구제도가 시행될 때 동대문구에 속했으며, 광복 후 돈암동이 되었고, 1949년 성북구의 돈암동이 되었다.
@@ -12839,11 +12767,12 @@
         </is>
       </c>
       <c r="M171" s="0">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="N171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">따라서 동선동1가에서 동선동3가까지 법정동의 행정은 동선1동사무소에서 담당하며, 동선동4가와 동선동5가의 행정은 동선2동사무소에서 담당하고 있다.
+          <t xml:space="preserve">성북구의 중앙에 위치한 동이다.
+따라서 동선동1가에서 동선동3가까지 법정동의 행정은 동선1동사무소에서 담당하며, 동선동4가와 동선동5가의 행정은 동선2동사무소에서 담당하고 있다.
 지하철 4호선 성신여대입구역을 이용할 수 있어 교통이 편리하다.</t>
         </is>
       </c>
@@ -12905,8 +12834,7 @@
       </c>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성북구의 중앙에 위치한 동이다.
-동명은 1949년 동소문동(東小門洞)과 삼선동(三仙洞)에서 각각 한 글자를 따서 이루어진 것이다.
+          <t xml:space="preserve">동명은 1949년 동소문동(東小門洞)과 삼선동(三仙洞)에서 각각 한 글자를 따서 이루어진 것이다.
 조선시대 한성부 동부 숭신방에 속하였고, 1895년에는 한성부 동서 숭신방 동소문외계 돈암리로 칭하였다.
 1911년 경성부 숭신면 돈암리로 칭하다가 1914년에 경기도 고양군 숭인면 돈암리가 되었다.
 1943년 구제도가 시행될 때 동대문구에 속했으며, 광복 후 돈암동이 되었고, 1949년 성북구의 돈암동이 되었다.
@@ -12915,11 +12843,12 @@
         </is>
       </c>
       <c r="M172" s="0">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="N172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">따라서 동선동1가에서 동선동3가까지 법정동의 행정은 동선1동사무소에서 담당하며, 동선동4가와 동선동5가의 행정은 동선2동사무소에서 담당하고 있다.
+          <t xml:space="preserve">성북구의 중앙에 위치한 동이다.
+따라서 동선동1가에서 동선동3가까지 법정동의 행정은 동선1동사무소에서 담당하며, 동선동4가와 동선동5가의 행정은 동선2동사무소에서 담당하고 있다.
 지하철 4호선 성신여대입구역을 이용할 수 있어 교통이 편리하다.</t>
         </is>
       </c>
@@ -12981,8 +12910,7 @@
       </c>
       <c r="L173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성북구의 중앙에 위치한 동이다.
-동명은 1949년 서울 4소문의 하나인 동소문(東小門)의 이름을 따서 제정된 것이다.
+          <t xml:space="preserve">동명은 1949년 서울 4소문의 하나인 동소문(東小門)의 이름을 따서 제정된 것이다.
 조선시대 한성부 동부 숭신방(崇信坊, 城外)에 속하였고, 1895년에는 한성부 동서 숭신방 동소문외계 돈암리로 칭하였다.
 1911년 경성부 숭신면 돈암리로 칭하다가 1914년에 경기도 고양군 숭인면 돈암리가 되었다.
 1943년 구제도가 시행될 때 동대문구에 속했으며, 광복 후 돈암동이 되었다.
@@ -12991,11 +12919,12 @@
         </is>
       </c>
       <c r="M173" s="0">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="N173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동의 행정업무는 동소문동1가에서 동소문동4가까지는 동소문동사무소에서, 동소문동5가는 동선1동사무소에서, 동소문동6가와 동소문동7가는 동선2동사무소에서 각각 담당하였다.
+          <t xml:space="preserve">성북구의 중앙에 위치한 동이다.
+동의 행정업무는 동소문동1가에서 동소문동4가까지는 동소문동사무소에서, 동소문동5가는 동선1동사무소에서, 동소문동6가와 동소문동7가는 동선2동사무소에서 각각 담당하였다.
 동의 남쪽으로 동소문로가 있고, 지하철 4호선 한성대입구역이 있어 교통이 편리하다.
 동의 중앙으로 동소문로가 있고, 지하철 4호선 성신여대입구역과 한성대입구역을 이용할 수 있어 교통이 편리하다.</t>
         </is>
@@ -13058,8 +12987,7 @@
       </c>
       <c r="L174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성북구의 중앙에 위치한 동이다.
-동명은 1949년 서울 4소문의 하나인 동소문(東小門)의 이름을 따서 제정된 것이다.
+          <t xml:space="preserve">동명은 1949년 서울 4소문의 하나인 동소문(東小門)의 이름을 따서 제정된 것이다.
 조선시대 한성부 동부 숭신방(崇信坊, 城外)에 속하였고, 1895년에는 한성부 동서 숭신방 동소문외계 돈암리로 칭하였다.
 1911년 경성부 숭신면 돈암리로 칭하다가 1914년에 경기도 고양군 숭인면 돈암리가 되었다.
 1943년 구제도가 시행될 때 동대문구에 속했으며, 광복 후 돈암동이 되었다.
@@ -13068,11 +12996,12 @@
         </is>
       </c>
       <c r="M174" s="0">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="N174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동의 행정업무는 동소문동1가에서 동소문동4가까지는 동소문동사무소에서, 동소문동5가는 동선1동사무소에서, 동소문동6가와 동소문동7가는 동선2동사무소에서 각각 담당하였다.
+          <t xml:space="preserve">성북구의 중앙에 위치한 동이다.
+동의 행정업무는 동소문동1가에서 동소문동4가까지는 동소문동사무소에서, 동소문동5가는 동선1동사무소에서, 동소문동6가와 동소문동7가는 동선2동사무소에서 각각 담당하였다.
 동의 남쪽으로 동소문로가 있고, 지하철 4호선 한성대입구역이 있어 교통이 편리하다.
 동의 중앙으로 동소문로가 있고, 지하철 4호선 성신여대입구역과 한성대입구역을 이용할 수 있어 교통이 편리하다.</t>
         </is>
@@ -13135,8 +13064,7 @@
       </c>
       <c r="L175" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성북구의 중앙에 위치한 동이다.
-동명은 1949년 서울 4소문의 하나인 동소문(東小門)의 이름을 따서 제정된 것이다.
+          <t xml:space="preserve">동명은 1949년 서울 4소문의 하나인 동소문(東小門)의 이름을 따서 제정된 것이다.
 조선시대 한성부 동부 숭신방(崇信坊, 城外)에 속하였고, 1895년에는 한성부 동서 숭신방 동소문외계 돈암리로 칭하였다.
 1911년 경성부 숭신면 돈암리로 칭하다가 1914년에 경기도 고양군 숭인면 돈암리가 되었다.
 1943년 구제도가 시행될 때 동대문구에 속했으며, 광복 후 돈암동이 되었다.
@@ -13145,11 +13073,12 @@
         </is>
       </c>
       <c r="M175" s="0">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="N175" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동의 행정업무는 동소문동1가에서 동소문동4가까지는 동소문동사무소에서, 동소문동5가는 동선1동사무소에서, 동소문동6가와 동소문동7가는 동선2동사무소에서 각각 담당하였다.
+          <t xml:space="preserve">성북구의 중앙에 위치한 동이다.
+동의 행정업무는 동소문동1가에서 동소문동4가까지는 동소문동사무소에서, 동소문동5가는 동선1동사무소에서, 동소문동6가와 동소문동7가는 동선2동사무소에서 각각 담당하였다.
 동의 남쪽으로 동소문로가 있고, 지하철 4호선 한성대입구역이 있어 교통이 편리하다.
 동의 중앙으로 동소문로가 있고, 지하철 4호선 성신여대입구역과 한성대입구역을 이용할 수 있어 교통이 편리하다.</t>
         </is>
@@ -13212,8 +13141,7 @@
       </c>
       <c r="L176" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성북구의 중앙에 위치한 동이다.
-동명은 1949년 서울 4소문의 하나인 동소문(東小門)의 이름을 따서 제정된 것이다.
+          <t xml:space="preserve">동명은 1949년 서울 4소문의 하나인 동소문(東小門)의 이름을 따서 제정된 것이다.
 조선시대 한성부 동부 숭신방(崇信坊, 城外)에 속하였고, 1895년에는 한성부 동서 숭신방 동소문외계 돈암리로 칭하였다.
 1911년 경성부 숭신면 돈암리로 칭하다가 1914년에 경기도 고양군 숭인면 돈암리가 되었다.
 1943년 구제도가 시행될 때 동대문구에 속했으며, 광복 후 돈암동이 되었다.
@@ -13222,11 +13150,12 @@
         </is>
       </c>
       <c r="M176" s="0">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="N176" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동의 행정업무는 동소문동1가에서 동소문동4가까지는 동소문동사무소에서, 동소문동5가는 동선1동사무소에서, 동소문동6가와 동소문동7가는 동선2동사무소에서 각각 담당하였다.
+          <t xml:space="preserve">성북구의 중앙에 위치한 동이다.
+동의 행정업무는 동소문동1가에서 동소문동4가까지는 동소문동사무소에서, 동소문동5가는 동선1동사무소에서, 동소문동6가와 동소문동7가는 동선2동사무소에서 각각 담당하였다.
 동의 남쪽으로 동소문로가 있고, 지하철 4호선 한성대입구역이 있어 교통이 편리하다.
 동의 중앙으로 동소문로가 있고, 지하철 4호선 성신여대입구역과 한성대입구역을 이용할 수 있어 교통이 편리하다.</t>
         </is>
@@ -13289,8 +13218,7 @@
       </c>
       <c r="L177" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성북구의 중앙에 위치한 동이다.
-동명은 1949년 서울 4소문의 하나인 동소문(東小門)의 이름을 따서 제정된 것이다.
+          <t xml:space="preserve">동명은 1949년 서울 4소문의 하나인 동소문(東小門)의 이름을 따서 제정된 것이다.
 조선시대 한성부 동부 숭신방(崇信坊, 城外)에 속하였고, 1895년에는 한성부 동서 숭신방 동소문외계 돈암리로 칭하였다.
 1911년 경성부 숭신면 돈암리로 칭하다가 1914년에 경기도 고양군 숭인면 돈암리가 되었다.
 1943년 구제도가 시행될 때 동대문구에 속했으며, 광복 후 돈암동이 되었다.
@@ -13299,11 +13227,12 @@
         </is>
       </c>
       <c r="M177" s="0">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="N177" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동의 행정업무는 동소문동1가에서 동소문동4가까지는 동소문동사무소에서, 동소문동5가는 동선1동사무소에서, 동소문동6가와 동소문동7가는 동선2동사무소에서 각각 담당하였다.
+          <t xml:space="preserve">성북구의 중앙에 위치한 동이다.
+동의 행정업무는 동소문동1가에서 동소문동4가까지는 동소문동사무소에서, 동소문동5가는 동선1동사무소에서, 동소문동6가와 동소문동7가는 동선2동사무소에서 각각 담당하였다.
 동의 남쪽으로 동소문로가 있고, 지하철 4호선 한성대입구역이 있어 교통이 편리하다.
 동의 중앙으로 동소문로가 있고, 지하철 4호선 성신여대입구역과 한성대입구역을 이용할 수 있어 교통이 편리하다.</t>
         </is>
@@ -13366,8 +13295,7 @@
       </c>
       <c r="L178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성북구의 중앙에 위치한 동이다.
-동명은 1949년 서울 4소문의 하나인 동소문(東小門)의 이름을 따서 제정된 것이다.
+          <t xml:space="preserve">동명은 1949년 서울 4소문의 하나인 동소문(東小門)의 이름을 따서 제정된 것이다.
 조선시대 한성부 동부 숭신방(崇信坊, 城外)에 속하였고, 1895년에는 한성부 동서 숭신방 동소문외계 돈암리로 칭하였다.
 1911년 경성부 숭신면 돈암리로 칭하다가 1914년에 경기도 고양군 숭인면 돈암리가 되었다.
 1943년 구제도가 시행될 때 동대문구에 속했으며, 광복 후 돈암동이 되었다.
@@ -13376,11 +13304,12 @@
         </is>
       </c>
       <c r="M178" s="0">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="N178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동의 행정업무는 동소문동1가에서 동소문동4가까지는 동소문동사무소에서, 동소문동5가는 동선1동사무소에서, 동소문동6가와 동소문동7가는 동선2동사무소에서 각각 담당하였다.
+          <t xml:space="preserve">성북구의 중앙에 위치한 동이다.
+동의 행정업무는 동소문동1가에서 동소문동4가까지는 동소문동사무소에서, 동소문동5가는 동선1동사무소에서, 동소문동6가와 동소문동7가는 동선2동사무소에서 각각 담당하였다.
 동의 남쪽으로 동소문로가 있고, 지하철 4호선 한성대입구역이 있어 교통이 편리하다.
 동의 중앙으로 동소문로가 있고, 지하철 4호선 성신여대입구역과 한성대입구역을 이용할 수 있어 교통이 편리하다.</t>
         </is>
@@ -13443,8 +13372,7 @@
       </c>
       <c r="L179" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성북구의 중앙에 위치한 동이다.
-동명은 1949년 서울 4소문의 하나인 동소문(東小門)의 이름을 따서 제정된 것이다.
+          <t xml:space="preserve">동명은 1949년 서울 4소문의 하나인 동소문(東小門)의 이름을 따서 제정된 것이다.
 조선시대 한성부 동부 숭신방(崇信坊, 城外)에 속하였고, 1895년에는 한성부 동서 숭신방 동소문외계 돈암리로 칭하였다.
 1911년 경성부 숭신면 돈암리로 칭하다가 1914년에 경기도 고양군 숭인면 돈암리가 되었다.
 1943년 구제도가 시행될 때 동대문구에 속했으며, 광복 후 돈암동이 되었다.
@@ -13453,11 +13381,12 @@
         </is>
       </c>
       <c r="M179" s="0">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="N179" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동의 행정업무는 동소문동1가에서 동소문동4가까지는 동소문동사무소에서, 동소문동5가는 동선1동사무소에서, 동소문동6가와 동소문동7가는 동선2동사무소에서 각각 담당하였다.
+          <t xml:space="preserve">성북구의 중앙에 위치한 동이다.
+동의 행정업무는 동소문동1가에서 동소문동4가까지는 동소문동사무소에서, 동소문동5가는 동선1동사무소에서, 동소문동6가와 동소문동7가는 동선2동사무소에서 각각 담당하였다.
 동의 남쪽으로 동소문로가 있고, 지하철 4호선 한성대입구역이 있어 교통이 편리하다.
 동의 중앙으로 동소문로가 있고, 지하철 4호선 성신여대입구역과 한성대입구역을 이용할 수 있어 교통이 편리하다.</t>
         </is>
@@ -13520,8 +13449,7 @@
       </c>
       <c r="L180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성북구의 남부에 위치한 동이다.
-동명은 보문동3가 168번지에 있는 보문사(普門寺)의 이름을 딴 것이다.
+          <t xml:space="preserve">동명은 보문동3가 168번지에 있는 보문사(普門寺)의 이름을 딴 것이다.
 조선시대 한성부 동부 숭신방에 속하였고, 1895년에는 한성부 동서 숭신방 동문외계(東門外契) 신설동(新設洞)이라 칭하였다.
 1911년 경성부 숭신면 신설계(新設契) 탑동(塔洞) 우산리(遇仙里)로 칭하다가 1914년 경기도 고양군 숭인면 신설리가 되었다.
 1943년 구제도가 시행될 때 동대문구에 속했으며, 광복 후 신설동이 되었고, 1955년 신설동에서 분리되어 보문동이라 칭하였다.
@@ -13529,11 +13457,12 @@
         </is>
       </c>
       <c r="M180" s="0">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="N180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">그러나 모든 법정동의 행정업무는 보문동사무소에서 담당하고 있다.
+          <t xml:space="preserve">성북구의 남부에 위치한 동이다.
+그러나 모든 법정동의 행정업무는 보문동사무소에서 담당하고 있다.
 청계천의 지류인 안암천이 흐르고, 지하철 6호선 보문역과 창신역을 이용할 수 있어 교통이 편리하다.</t>
         </is>
       </c>
@@ -13595,8 +13524,7 @@
       </c>
       <c r="L181" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성북구의 남부에 위치한 동이다.
-동명은 보문동3가 168번지에 있는 보문사(普門寺)의 이름을 딴 것이다.
+          <t xml:space="preserve">동명은 보문동3가 168번지에 있는 보문사(普門寺)의 이름을 딴 것이다.
 조선시대 한성부 동부 숭신방에 속하였고, 1895년에는 한성부 동서 숭신방 동문외계(東門外契) 신설동(新設洞)이라 칭하였다.
 1911년 경성부 숭신면 신설계(新設契) 탑동(塔洞) 우산리(遇仙里)로 칭하다가 1914년 경기도 고양군 숭인면 신설리가 되었다.
 1943년 구제도가 시행될 때 동대문구에 속했으며, 광복 후 신설동이 되었고, 1955년 신설동에서 분리되어 보문동이라 칭하였다.
@@ -13604,11 +13532,12 @@
         </is>
       </c>
       <c r="M181" s="0">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="N181" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">그러나 모든 법정동의 행정업무는 보문동사무소에서 담당하고 있다.
+          <t xml:space="preserve">성북구의 남부에 위치한 동이다.
+그러나 모든 법정동의 행정업무는 보문동사무소에서 담당하고 있다.
 청계천의 지류인 안암천이 흐르고, 지하철 6호선 보문역과 창신역을 이용할 수 있어 교통이 편리하다.</t>
         </is>
       </c>
@@ -13670,8 +13599,7 @@
       </c>
       <c r="L182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성북구의 남부에 위치한 동이다.
-동명은 보문동3가 168번지에 있는 보문사(普門寺)의 이름을 딴 것이다.
+          <t xml:space="preserve">동명은 보문동3가 168번지에 있는 보문사(普門寺)의 이름을 딴 것이다.
 조선시대 한성부 동부 숭신방에 속하였고, 1895년에는 한성부 동서 숭신방 동문외계(東門外契) 신설동(新設洞)이라 칭하였다.
 1911년 경성부 숭신면 신설계(新設契) 탑동(塔洞) 우산리(遇仙里)로 칭하다가 1914년 경기도 고양군 숭인면 신설리가 되었다.
 1943년 구제도가 시행될 때 동대문구에 속했으며, 광복 후 신설동이 되었고, 1955년 신설동에서 분리되어 보문동이라 칭하였다.
@@ -13679,11 +13607,12 @@
         </is>
       </c>
       <c r="M182" s="0">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="N182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">그러나 모든 법정동의 행정업무는 보문동사무소에서 담당하고 있다.
+          <t xml:space="preserve">성북구의 남부에 위치한 동이다.
+그러나 모든 법정동의 행정업무는 보문동사무소에서 담당하고 있다.
 청계천의 지류인 안암천이 흐르고, 지하철 6호선 보문역과 창신역을 이용할 수 있어 교통이 편리하다.</t>
         </is>
       </c>
@@ -13745,8 +13674,7 @@
       </c>
       <c r="L183" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성북구의 남부에 위치한 동이다.
-동명은 보문동3가 168번지에 있는 보문사(普門寺)의 이름을 딴 것이다.
+          <t xml:space="preserve">동명은 보문동3가 168번지에 있는 보문사(普門寺)의 이름을 딴 것이다.
 조선시대 한성부 동부 숭신방에 속하였고, 1895년에는 한성부 동서 숭신방 동문외계(東門外契) 신설동(新設洞)이라 칭하였다.
 1911년 경성부 숭신면 신설계(新設契) 탑동(塔洞) 우산리(遇仙里)로 칭하다가 1914년 경기도 고양군 숭인면 신설리가 되었다.
 1943년 구제도가 시행될 때 동대문구에 속했으며, 광복 후 신설동이 되었고, 1955년 신설동에서 분리되어 보문동이라 칭하였다.
@@ -13754,11 +13682,12 @@
         </is>
       </c>
       <c r="M183" s="0">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="N183" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">그러나 모든 법정동의 행정업무는 보문동사무소에서 담당하고 있다.
+          <t xml:space="preserve">성북구의 남부에 위치한 동이다.
+그러나 모든 법정동의 행정업무는 보문동사무소에서 담당하고 있다.
 청계천의 지류인 안암천이 흐르고, 지하철 6호선 보문역과 창신역을 이용할 수 있어 교통이 편리하다.</t>
         </is>
       </c>
@@ -13820,8 +13749,7 @@
       </c>
       <c r="L184" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성북구의 남부에 위치한 동이다.
-동명은 보문동3가 168번지에 있는 보문사(普門寺)의 이름을 딴 것이다.
+          <t xml:space="preserve">동명은 보문동3가 168번지에 있는 보문사(普門寺)의 이름을 딴 것이다.
 조선시대 한성부 동부 숭신방에 속하였고, 1895년에는 한성부 동서 숭신방 동문외계(東門外契) 신설동(新設洞)이라 칭하였다.
 1911년 경성부 숭신면 신설계(新設契) 탑동(塔洞) 우산리(遇仙里)로 칭하다가 1914년 경기도 고양군 숭인면 신설리가 되었다.
 1943년 구제도가 시행될 때 동대문구에 속했으며, 광복 후 신설동이 되었고, 1955년 신설동에서 분리되어 보문동이라 칭하였다.
@@ -13829,11 +13757,12 @@
         </is>
       </c>
       <c r="M184" s="0">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="N184" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">그러나 모든 법정동의 행정업무는 보문동사무소에서 담당하고 있다.
+          <t xml:space="preserve">성북구의 남부에 위치한 동이다.
+그러나 모든 법정동의 행정업무는 보문동사무소에서 담당하고 있다.
 청계천의 지류인 안암천이 흐르고, 지하철 6호선 보문역과 창신역을 이용할 수 있어 교통이 편리하다.</t>
         </is>
       </c>
@@ -13895,8 +13824,7 @@
       </c>
       <c r="L185" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성북구의 남부에 위치한 동이다.
-동명은 보문동3가 168번지에 있는 보문사(普門寺)의 이름을 딴 것이다.
+          <t xml:space="preserve">동명은 보문동3가 168번지에 있는 보문사(普門寺)의 이름을 딴 것이다.
 조선시대 한성부 동부 숭신방에 속하였고, 1895년에는 한성부 동서 숭신방 동문외계(東門外契) 신설동(新設洞)이라 칭하였다.
 1911년 경성부 숭신면 신설계(新設契) 탑동(塔洞) 우산리(遇仙里)로 칭하다가 1914년 경기도 고양군 숭인면 신설리가 되었다.
 1943년 구제도가 시행될 때 동대문구에 속했으며, 광복 후 신설동이 되었고, 1955년 신설동에서 분리되어 보문동이라 칭하였다.
@@ -13904,11 +13832,12 @@
         </is>
       </c>
       <c r="M185" s="0">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="N185" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">그러나 모든 법정동의 행정업무는 보문동사무소에서 담당하고 있다.
+          <t xml:space="preserve">성북구의 남부에 위치한 동이다.
+그러나 모든 법정동의 행정업무는 보문동사무소에서 담당하고 있다.
 청계천의 지류인 안암천이 흐르고, 지하철 6호선 보문역과 창신역을 이용할 수 있어 교통이 편리하다.</t>
         </is>
       </c>
@@ -13970,8 +13899,7 @@
       </c>
       <c r="L186" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성북구의 남부에 위치한 동이다.
-동명은 보문동3가 168번지에 있는 보문사(普門寺)의 이름을 딴 것이다.
+          <t xml:space="preserve">동명은 보문동3가 168번지에 있는 보문사(普門寺)의 이름을 딴 것이다.
 조선시대 한성부 동부 숭신방에 속하였고, 1895년에는 한성부 동서 숭신방 동문외계(東門外契) 신설동(新設洞)이라 칭하였다.
 1911년 경성부 숭신면 신설계(新設契) 탑동(塔洞) 우산리(遇仙里)로 칭하다가 1914년 경기도 고양군 숭인면 신설리가 되었다.
 1943년 구제도가 시행될 때 동대문구에 속했으며, 광복 후 신설동이 되었고, 1955년 신설동에서 분리되어 보문동이라 칭하였다.
@@ -13979,11 +13907,12 @@
         </is>
       </c>
       <c r="M186" s="0">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="N186" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">그러나 모든 법정동의 행정업무는 보문동사무소에서 담당하고 있다.
+          <t xml:space="preserve">성북구의 남부에 위치한 동이다.
+그러나 모든 법정동의 행정업무는 보문동사무소에서 담당하고 있다.
 청계천의 지류인 안암천이 흐르고, 지하철 6호선 보문역과 창신역을 이용할 수 있어 교통이 편리하다.</t>
         </is>
       </c>
@@ -14420,8 +14349,7 @@
       </c>
       <c r="L192" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성북구의 동부에 위치한 동이다.
-동명은 이 지역의 반달 모양을 한 산과 연해 있는 마을을 다릿굴(골)이라 하였고 그 위쪽을 웃다리골(上月谷里)이라 한데서 유래되었다.
+          <t xml:space="preserve">동명은 이 지역의 반달 모양을 한 산과 연해 있는 마을을 다릿굴(골)이라 하였고 그 위쪽을 웃다리골(上月谷里)이라 한데서 유래되었다.
 조선시대 한성부 동부 숭신방에 속하였고, 1895년에는 한성부 동서 인창방 동소문외계 월곡상리라 칭하였다.
 1911년 경성부 인창면 월곡상리로 칭하다가 1914년에 경기도 고양군 숭인면 상월곡리가 되었다.
 1949년 서울시 성북구 숭인출장소에 편입되었다가 1950년 상월곡동으로 명칭이 개정되었으며, 1973년 성북구의 법정동이 되었다.
@@ -14429,11 +14357,12 @@
         </is>
       </c>
       <c r="M192" s="0">
-        <v>309</v>
+        <v>291</v>
       </c>
       <c r="N192" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">행정은 상월곡동사무소에서 담당하고 있다.</t>
+          <t xml:space="preserve">성북구의 동부에 위치한 동이다.
+행정은 상월곡동사무소에서 담당하고 있다.</t>
         </is>
       </c>
     </row>
@@ -14494,8 +14423,7 @@
       </c>
       <c r="L193" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성북구의 동부에 위치한 동이다.
-동명은 이 지역의 땅 이름인 돌곶이를 의역(意譯)하여 한자로 표현한 것이다.
+          <t xml:space="preserve">동명은 이 지역의 땅 이름인 돌곶이를 의역(意譯)하여 한자로 표현한 것이다.
 조선시대 한성부 동부 숭신방(崇信坊, 城外) 장위리계(長位里契)에 속하였고, 1895년 한성부 동서 인창방 동소문외계 석관리(石串里)가 되었다.
 1911년 경성부 인창면이 되었다가 1914년 경기도 고양군 숭인면에 속하였다.
 1949년 서울시 성북구 숭인출장소에 편입되었다가 1950년 석관동으로 명칭이 개정되었으며, 1973년 성북구의 법정동이 되었다.
@@ -14505,11 +14433,12 @@
         </is>
       </c>
       <c r="M193" s="0">
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="N193" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동쪽으로 동부간선도로와 중랑천이 우이천과 합류되며, 북쪽으로는 북부순환도로가 지나고 있고 전철 1호선 석계역이 가까이 있어 교통이 편리하다.</t>
+          <t xml:space="preserve">성북구의 동부에 위치한 동이다.
+동쪽으로 동부간선도로와 중랑천이 우이천과 합류되며, 북쪽으로는 북부순환도로가 지나고 있고 전철 1호선 석계역이 가까이 있어 교통이 편리하다.</t>
         </is>
       </c>
     </row>
@@ -14720,8 +14649,7 @@
       </c>
       <c r="L196" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성북구의 동부에 위치한 동이다.
-동명은 예전에 여러 명이 편안하게 앉을 수 있는 넓은 바위가 있었다 하여 이 바위 이름을 ‘앉일바위’라 하였고, 이것을 한자로 안암(安岩)이라 한데서 연유한다.
+          <t xml:space="preserve">동명은 예전에 여러 명이 편안하게 앉을 수 있는 넓은 바위가 있었다 하여 이 바위 이름을 ‘앉일바위’라 하였고, 이것을 한자로 안암(安岩)이라 한데서 연유한다.
 조선시대 한성부 동부 숭신방에 속하였고, 1895년 한성부 동서 숭신방 동문외계 원리(園里), 궁리(宮里), 상리(上里), 중리(中里)로 칭하였다.
 1911년 경성부 숭신면에 속하였다가 1914년에 경기도 고양군 숭인면 안암리가 되었다.
 1936년 경성부에 편입된 후 1943년 동대문구 안암정(安岩町)이 되었고, 1946년 안암동으로 이름을 바꾸었다.
@@ -14732,11 +14660,11 @@
         </is>
       </c>
       <c r="M196" s="0">
-        <v>579</v>
+        <v>561</v>
       </c>
       <c r="N196" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">성북구의 동부에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -14797,8 +14725,7 @@
       </c>
       <c r="L197" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성북구의 동부에 위치한 동이다.
-동명은 예전에 여러 명이 편안하게 앉을 수 있는 넓은 바위가 있었다 하여 이 바위 이름을 ‘앉일바위’라 하였고, 이것을 한자로 안암(安岩)이라 한데서 연유한다.
+          <t xml:space="preserve">동명은 예전에 여러 명이 편안하게 앉을 수 있는 넓은 바위가 있었다 하여 이 바위 이름을 ‘앉일바위’라 하였고, 이것을 한자로 안암(安岩)이라 한데서 연유한다.
 조선시대 한성부 동부 숭신방에 속하였고, 1895년 한성부 동서 숭신방 동문외계 원리(園里), 궁리(宮里), 상리(上里), 중리(中里)로 칭하였다.
 1911년 경성부 숭신면에 속하였다가 1914년에 경기도 고양군 숭인면 안암리가 되었다.
 1936년 경성부에 편입된 후 1943년 동대문구 안암정(安岩町)이 되었고, 1946년 안암동으로 이름을 바꾸었다.
@@ -14809,11 +14736,11 @@
         </is>
       </c>
       <c r="M197" s="0">
-        <v>579</v>
+        <v>561</v>
       </c>
       <c r="N197" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">성북구의 동부에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -14874,8 +14801,7 @@
       </c>
       <c r="L198" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성북구의 동부에 위치한 동이다.
-동명은 예전에 여러 명이 편안하게 앉을 수 있는 넓은 바위가 있었다 하여 이 바위 이름을 ‘앉일바위’라 하였고, 이것을 한자로 안암(安岩)이라 한데서 연유한다.
+          <t xml:space="preserve">동명은 예전에 여러 명이 편안하게 앉을 수 있는 넓은 바위가 있었다 하여 이 바위 이름을 ‘앉일바위’라 하였고, 이것을 한자로 안암(安岩)이라 한데서 연유한다.
 조선시대 한성부 동부 숭신방에 속하였고, 1895년 한성부 동서 숭신방 동문외계 원리(園里), 궁리(宮里), 상리(上里), 중리(中里)로 칭하였다.
 1911년 경성부 숭신면에 속하였다가 1914년에 경기도 고양군 숭인면 안암리가 되었다.
 1936년 경성부에 편입된 후 1943년 동대문구 안암정(安岩町)이 되었고, 1946년 안암동으로 이름을 바꾸었다.
@@ -14886,11 +14812,11 @@
         </is>
       </c>
       <c r="M198" s="0">
-        <v>579</v>
+        <v>561</v>
       </c>
       <c r="N198" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">성북구의 동부에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -14951,8 +14877,7 @@
       </c>
       <c r="L199" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성북구의 동부에 위치한 동이다.
-동명은 예전에 여러 명이 편안하게 앉을 수 있는 넓은 바위가 있었다 하여 이 바위 이름을 ‘앉일바위’라 하였고, 이것을 한자로 안암(安岩)이라 한데서 연유한다.
+          <t xml:space="preserve">동명은 예전에 여러 명이 편안하게 앉을 수 있는 넓은 바위가 있었다 하여 이 바위 이름을 ‘앉일바위’라 하였고, 이것을 한자로 안암(安岩)이라 한데서 연유한다.
 조선시대 한성부 동부 숭신방에 속하였고, 1895년 한성부 동서 숭신방 동문외계 원리(園里), 궁리(宮里), 상리(上里), 중리(中里)로 칭하였다.
 1911년 경성부 숭신면에 속하였다가 1914년에 경기도 고양군 숭인면 안암리가 되었다.
 1936년 경성부에 편입된 후 1943년 동대문구 안암정(安岩町)이 되었고, 1946년 안암동으로 이름을 바꾸었다.
@@ -14963,11 +14888,11 @@
         </is>
       </c>
       <c r="M199" s="0">
-        <v>579</v>
+        <v>561</v>
       </c>
       <c r="N199" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">성북구의 동부에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -15028,8 +14953,7 @@
       </c>
       <c r="L200" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성북구의 동부에 위치한 동이다.
-동명은 예전에 여러 명이 편안하게 앉을 수 있는 넓은 바위가 있었다 하여 이 바위 이름을 ‘앉일바위’라 하였고, 이것을 한자로 안암(安岩)이라 한데서 연유한다.
+          <t xml:space="preserve">동명은 예전에 여러 명이 편안하게 앉을 수 있는 넓은 바위가 있었다 하여 이 바위 이름을 ‘앉일바위’라 하였고, 이것을 한자로 안암(安岩)이라 한데서 연유한다.
 조선시대 한성부 동부 숭신방에 속하였고, 1895년 한성부 동서 숭신방 동문외계 원리(園里), 궁리(宮里), 상리(上里), 중리(中里)로 칭하였다.
 1911년 경성부 숭신면에 속하였다가 1914년에 경기도 고양군 숭인면 안암리가 되었다.
 1936년 경성부에 편입된 후 1943년 동대문구 안암정(安岩町)이 되었고, 1946년 안암동으로 이름을 바꾸었다.
@@ -15040,11 +14964,11 @@
         </is>
       </c>
       <c r="M200" s="0">
-        <v>579</v>
+        <v>561</v>
       </c>
       <c r="N200" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">성북구의 동부에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -15105,19 +15029,18 @@
       </c>
       <c r="L201" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성북구의 동북부에 위치한 동이다.
-동명은 마을 뒤 장위산(獐位山)의 이름을 따서 장위동(長位洞)이 된 것으로 보인다.
+          <t xml:space="preserve">동명은 마을 뒤 장위산(獐位山)의 이름을 따서 장위동(長位洞)이 된 것으로 보인다.
 조선시대 한성부 동부 숭신방에 속하였고, 1895년 한성부 동서 인창방 동소문외계 장위리로 칭하였다.
 1911년 경성부 인창면에 속하였다가 1914년에 경기도 고양군 숭인면에 속하였다.
 1949년 서울시 성북구 숭인출장소 장위리로 편입되었고, 1950년 장위동이 되었으며, 1973년에 성북구의 법정동이 되었다.</t>
         </is>
       </c>
       <c r="M201" s="0">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="N201" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">성북구의 동북부에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -15178,8 +15101,7 @@
       </c>
       <c r="L202" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성북구의 동북부에 위치한 동이다.
-동명은 이 마을에 조선 태종의 계비 신덕왕후(神德王后) 강씨(康氏)의 정릉(貞陵)에서 연유되었다.
+          <t xml:space="preserve">동명은 이 마을에 조선 태종의 계비 신덕왕후(神德王后) 강씨(康氏)의 정릉(貞陵)에서 연유되었다.
 조선시대 한성부 동부 숭신방 정릉계(貞陵契)에 속하였고, 1895년 한성부 동서 숭신방 동소문외계 대정릉동(大貞陵洞), 소정릉동(小貞陵洞), 청수동(淸水洞), 손가정(孫哥亭) 지역으로 칭했다.
 1911년 경성부 숭신면에 속하였다가 1914년에 경기도 고양군 숭인면 정릉리가 되었다.
 1949년 서울시 성북구 정릉리로 편입되어 1950년에 정릉동이 되었다.
@@ -15189,11 +15111,11 @@
         </is>
       </c>
       <c r="M202" s="0">
-        <v>385</v>
+        <v>366</v>
       </c>
       <c r="N202" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">성북구의 동북부에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -15252,8 +15174,7 @@
       </c>
       <c r="L203" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성북구의 서남부에 위치한 동이다.
-동명은 고려대학교 뒷산에 북처럼 생긴 커다란 바위가 있는 마을이라 하여 한자로 종암(鍾岩, 또는 敲岩)이라 한 데서 연유한다.
+          <t xml:space="preserve">동명은 고려대학교 뒷산에 북처럼 생긴 커다란 바위가 있는 마을이라 하여 한자로 종암(鍾岩, 또는 敲岩)이라 한 데서 연유한다.
 조선시대에 한성부 동부 숭신방 종암리계(鍾岩里契)였고, 1895년 한성부 동서 숭신방 동문외계 대종암(大鍾岩), 소종암(小鍾岩) 지역으로 칭했다.
 1911년 경성부 숭신면에 속하였다가 1914년에 경기도 고양군 숭인면 종암리가 되었다.
 1943년 동대문구 종암정(鍾岩町)이 되었다가 1946년에 종암동으로 바뀌었으며, 1949년 성북구 종암동이 되었다.
@@ -15261,11 +15182,12 @@
         </is>
       </c>
       <c r="M203" s="0">
-        <v>311</v>
+        <v>292</v>
       </c>
       <c r="N203" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동의 동쪽으로 정릉천을 따라 내부순환도로가 지나고 있고, 지하철 6호선이 있으며, 동의 중앙으로 종암로가 개설되어 있어 교통이 편리하다.</t>
+          <t xml:space="preserve">성북구의 서남부에 위치한 동이다.
+동의 동쪽으로 정릉천을 따라 내부순환도로가 지나고 있고, 지하철 6호선이 있으며, 동의 중앙으로 종암로가 개설되어 있어 교통이 편리하다.</t>
         </is>
       </c>
     </row>
@@ -15326,8 +15248,7 @@
       </c>
       <c r="L204" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성북구의 동북부에 위치한 동이다.
-동명은 이 지역의 반달 모양을 한 산과 연해 있는 마을을 다릿굴(골)이라 하였고 그 아래쪽을 아랫다리골(下月谷里)이라 한데서 유래되었다.
+          <t xml:space="preserve">동명은 이 지역의 반달 모양을 한 산과 연해 있는 마을을 다릿굴(골)이라 하였고 그 아래쪽을 아랫다리골(下月谷里)이라 한데서 유래되었다.
 조선시대 한성부 동부 숭신방에 속하였고, 1895년에는 한성부 동서 인창방 동소문외계 월곡하리라 칭하였다.
 1911년 경성부 인창면 월곡하리로 칭하다가 1914년 경기도 고양군 숭인면 하월곡리가 되었다.
 1949년 서울시 성북구 숭인출장소에 편입되었다가 1950년 하월곡동으로 명칭이 개정되었으며, 1973년 성북구의 법정동이 되었다.
@@ -15336,11 +15257,11 @@
         </is>
       </c>
       <c r="M204" s="0">
-        <v>360</v>
+        <v>341</v>
       </c>
       <c r="N204" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">성북구의 동북부에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -15401,8 +15322,7 @@
       </c>
       <c r="L205" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">송파구의 남서쪽에 있는 동이다.
-동쪽은 오금동 · 거여동, 서쪽은 강남구 수서동, 남쪽은 문정동, 북쪽은 석촌동 · 송파동과 접해 있다.
+          <t xml:space="preserve">동쪽은 오금동 · 거여동, 서쪽은 강남구 수서동, 남쪽은 문정동, 북쪽은 석촌동 · 송파동과 접해 있다.
 옛 마을 이름인 가락골에서 동명이 유래되었다.
 1925년 을축년홍수로 송파동 일대 주민이 이주하면서 가히 살만한 땅이라 한데서 붙여진 이름이기도 하다.
 1963년 서울특별시 성동구에 편입되어 송파출장소 관할이 되었으며, 1975년 강남구, 1979년 강동구를 거쳐 1988년에 송파구가 신설되어 여기에 포함되었다.
@@ -15412,11 +15332,12 @@
         </is>
       </c>
       <c r="M205" s="0">
-        <v>469</v>
+        <v>451</v>
       </c>
       <c r="N205" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">송파대로와 남부순환로가 만나는 로터리는 광장을 이루고 있으며, 지하철 8호선이 지나 교통이 편리하다.</t>
+          <t xml:space="preserve">송파구의 남서쪽에 있는 동이다.
+송파대로와 남부순환로가 만나는 로터리는 광장을 이루고 있으며, 지하철 8호선이 지나 교통이 편리하다.</t>
         </is>
       </c>
     </row>
@@ -15477,8 +15398,7 @@
       </c>
       <c r="L206" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">송파구의 남쪽 끝에 있는 동이다.
-남한산성이 있는 청량산 북서쪽 기슭에 위치하여, 동쪽은 마천동, 서쪽은 문정동, 남쪽은 장지동과 하남시, 북쪽은 가락동 · 오금동에 접해 있다.
+          <t xml:space="preserve">남한산성이 있는 청량산 북서쪽 기슭에 위치하여, 동쪽은 마천동, 서쪽은 문정동, 남쪽은 장지동과 하남시, 북쪽은 가락동 · 오금동에 접해 있다.
 거암, 김이, 겜리라 불리다가 한자로 표기하면서 거여리(巨餘里)가 되었다.
 1963년 서울특별시 성동구에 편입되어 송파출장소 관할이 되었으며, 1975년 강남구, 1979년 강동구를 거쳐 1988년에 송파구가 신설되어 여기에 포함되었다.
 한적한 농촌지역에서 1967~1971년 사이에 서울시내 무허가 판잣집 철거민들이 이주하면서 인근의 마천동과 함께 인구가 늘기 시작하였다.
@@ -15487,11 +15407,11 @@
         </is>
       </c>
       <c r="M206" s="0">
-        <v>423</v>
+        <v>404</v>
       </c>
       <c r="N206" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">송파구의 남쪽 끝에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -15552,8 +15472,7 @@
       </c>
       <c r="L207" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">송파구의 남동쪽 끝에 있는 동이다.
-남한산성이 있는 청량산 북서쪽 기슭에 위치하여, 동쪽과 북쪽은 경기도 하남시, 서쪽은 오금동, 남쪽은 거여동과 접해 있다.
+          <t xml:space="preserve">남한산성이 있는 청량산 북서쪽 기슭에 위치하여, 동쪽과 북쪽은 경기도 하남시, 서쪽은 오금동, 남쪽은 거여동과 접해 있다.
 마을 동쪽에 있는 마산(천마산)에서 동명이 유래되었다.
 1963년 서울특별시 성동구에 편입되어 송파출장소 관할이 되었으며, 1975년 강남구, 1979년 강동구를 거쳐 1988년에 송파구가 신설되어 여기에 포함되었다.
 1982년 가락지구 토지구획정리사업 지구에 일부 포함되면서 주택지구로 변모하였다.
@@ -15561,11 +15480,11 @@
         </is>
       </c>
       <c r="M207" s="0">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="N207" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">송파구의 남동쪽 끝에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -15626,8 +15545,7 @@
       </c>
       <c r="L208" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">송파구의 남서쪽 끝에 있는 동이다.
-동쪽은 거여동, 서쪽은 강남구 수서동, 남쪽은 장지동, 북쪽은 가락동과 접해 있다.
+          <t xml:space="preserve">동쪽은 거여동, 서쪽은 강남구 수서동, 남쪽은 장지동, 북쪽은 가락동과 접해 있다.
 병자호란 때 인조가 남한산성으로 피난가다 이곳 문씨 마을에서 우물을 마셨던 것으로 동명이 유래되었다.
 1963년 서울특별시 성동구에 편입되어 송파출장소 관할이 되었으며, 1975년 강남구, 1979년 강동구를 거쳐 1988년에 송파구가 신설되어 여기에 포함되었다.
 성남시와 인접한 지역으로 주택지 · 농지 · 임야 등이 혼재한 도농 복합지역이었는데, 점차 전형적인 아파트단지와 주거지역으로 발전하였으며, 그 후 로데오거리와 같은 상업지역이 들어섰다.
@@ -15637,11 +15555,11 @@
         </is>
       </c>
       <c r="M208" s="0">
-        <v>448</v>
+        <v>428</v>
       </c>
       <c r="N208" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">송파구의 남서쪽 끝에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -15703,8 +15621,7 @@
       </c>
       <c r="L209" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">송파구의 중앙 동쪽에 있는 동이다.
-동쪽은 강동구 둔촌동, 서쪽은 신천동 · 잠실동, 남쪽은 오금동 · 가락동, 북쪽은 풍납동과 강동구 성내동에 접해 있다.
+          <t xml:space="preserve">동쪽은 강동구 둔촌동, 서쪽은 신천동 · 잠실동, 남쪽은 오금동 · 가락동, 북쪽은 풍납동과 강동구 성내동에 접해 있다.
 마을이 아늑하고 꽃이 많이 피어 방잇골로 불리다가 한자로 방이동이라 표기한 데서 동명이 유래되었다.
 1963년 서울특별시 성동구에 편입되어 송파출장소 관할이 되었으며, 1975년 강남구, 1979년 강동구를 거쳐 1988년에 송파구가 신설되어 여기에 포함되었다.
 1989년 올림픽공원 일대를 행정동으로 오륜동(五輪洞)을 신설하였다.
@@ -15713,11 +15630,12 @@
         </is>
       </c>
       <c r="M209" s="0">
-        <v>416</v>
+        <v>396</v>
       </c>
       <c r="N209" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">풍납로 · 위례성길 · 남부순환로 · 오금로가 바둑판식으로 나 있고, 지하철 8호선이 지나 교통이 편리하다.</t>
+          <t xml:space="preserve">송파구의 중앙 동쪽에 있는 동이다.
+풍납로 · 위례성길 · 남부순환로 · 오금로가 바둑판식으로 나 있고, 지하철 8호선이 지나 교통이 편리하다.</t>
         </is>
       </c>
     </row>
@@ -15844,8 +15762,7 @@
       </c>
       <c r="L211" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">송파구의 중앙 서쪽에 있는 동이다.
-동쪽은 송파동, 서쪽은 삼전동, 남쪽은 가락동, 북쪽은 잠실동 석촌호수와 접해 있다.
+          <t xml:space="preserve">동쪽은 송파동, 서쪽은 삼전동, 남쪽은 가락동, 북쪽은 잠실동 석촌호수와 접해 있다.
 돌 많은 마을이란 뜻으로 ‘돌마리’라고 하던 것을 한자로 석촌동이라 표기한데서 동명이 유래되었다.
 이 돌은 백제 초기 적석총에서 무너져 내린 돌들이었다.
 1963년 서울특별시 성동구에 편입되어 송파출장소 관할이 되었으며, 1975년 강남구, 1979년 강동구를 거쳐 1988년 송파구가 신설되어 여기에 포함되었다.
@@ -15855,11 +15772,11 @@
         </is>
       </c>
       <c r="M211" s="0">
-        <v>438</v>
+        <v>418</v>
       </c>
       <c r="N211" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">송파구의 중앙 서쪽에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -15920,8 +15837,7 @@
       </c>
       <c r="L212" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">송파구 중앙에 있는 동이다.
-석촌호수 남쪽에 위치하며, 동쪽은 방이동, 서쪽은 석촌동, 남쪽은 가락동, 북쪽은 잠실동과 접해 있다.
+          <t xml:space="preserve">석촌호수 남쪽에 위치하며, 동쪽은 방이동, 서쪽은 석촌동, 남쪽은 가락동, 북쪽은 잠실동과 접해 있다.
 조선 후기에 송파나루터가 있던 데서 동명이 유래되었다.
 1963년 서울특별시 성동구에 편입되어 송파출장소 관할이 되었으며, 1975년 강남구, 1979년 강동구를 거쳐 1988년에 송파구가 신설되어 여기에 포함되었다.
 조선시대 당시에 송파에는 교통 및 군사상의 요충지로 한강변 5진(鎭)의 하나인 송파진이 설치되었으며, 서울에서 용인 · 충주로 가려는 사람들이 많이 이용하였다.
@@ -15930,11 +15846,11 @@
         </is>
       </c>
       <c r="M212" s="0">
-        <v>494</v>
+        <v>478</v>
       </c>
       <c r="N212" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">송파구 중앙에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -15993,8 +15909,7 @@
       </c>
       <c r="L213" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">송파구의 북동쪽 끝에 있는 동이다.
-한강변에 있으며, 동쪽은 방이동 · 풍납동, 서쪽은 잠실동, 남쪽은 송파동, 북쪽은 한강 건너 성동구 구의동과 접해 있다.
+          <t xml:space="preserve">한강변에 있으며, 동쪽은 방이동 · 풍납동, 서쪽은 잠실동, 남쪽은 송파동, 북쪽은 한강 건너 성동구 구의동과 접해 있다.
 조선시대 대홍수로 인해 마을 북쪽 끝에 새로 생긴 작은 물줄기가 흘러 새내 · 새개라고 하던 것을 한자로 신천이라 표기한 데서 동명이 유래되었다.
 1949년 서울특별시 성동구에 편입되어 뚝도출장소 관할이 되었으며, 1975년 강남구, 1979년 강동구를 거쳐 1988년에 송파구가 신설되어 여기에 포함되었다.
 1970년대 초 잠실지구 토지구획정리사업에 따른 공유수면매립으로 조성된 넓은 택지가 개발되어 시영아파트를 중심으로 아파트단지가 조성되었다.
@@ -16003,11 +15918,12 @@
         </is>
       </c>
       <c r="M213" s="0">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="N213" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">올림픽로 인근에는 송파구청을 비롯하여 잠실전화국, 교통회관, 향군회관, 어린이교통공원 등이 있으며, 지하철 2·8호선이 지나고 풍납로 · 신천동길 · 올림픽로 · 잠실길 등이 바둑판식으로 이어져 교통이 편리하다.</t>
+          <t xml:space="preserve">송파구의 북동쪽 끝에 있는 동이다.
+올림픽로 인근에는 송파구청을 비롯하여 잠실전화국, 교통회관, 향군회관, 어린이교통공원 등이 있으며, 지하철 2·8호선이 지나고 풍납로 · 신천동길 · 올림픽로 · 잠실길 등이 바둑판식으로 이어져 교통이 편리하다.</t>
         </is>
       </c>
     </row>
@@ -16068,8 +15984,7 @@
       </c>
       <c r="L214" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">송파구의 동쪽 끝에 있는 동이다.
-동쪽은 마천동과 경기도 하남시, 서쪽은 가락동 · 송파동, 남쪽은 가락동 · 거여동, 북쪽은 방이동과 접해 있다.
+          <t xml:space="preserve">동쪽은 마천동과 경기도 하남시, 서쪽은 가락동 · 송파동, 남쪽은 가락동 · 거여동, 북쪽은 방이동과 접해 있다.
 오동나무가 많고 가야금을 만드는 사람이 살았던 데서 동명이 유래되었다.
 또 병자호란 때 인조가 남한산성으로 피난 가는 길에 이곳의 백토고개에서 오금이 아프다고 말한 데서 유래되었다고도 한다.
 1963년 서울특별시 성동구에 편입되어 송파출장소 관할이 되었으며, 1975년 강남구, 1979년 강동구를 거쳐 1988년에 송파구가 신설되어 여기에 포함되었다.
@@ -16078,11 +15993,12 @@
         </is>
       </c>
       <c r="M214" s="0">
-        <v>435</v>
+        <v>416</v>
       </c>
       <c r="N214" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동 가운데 성내천이 흐르며, 위례성길 · 오금로 · 남부순환로 · 거여동길이 있고 지하철 5호선이 지나 교통이 편리하다.</t>
+          <t xml:space="preserve">송파구의 동쪽 끝에 있는 동이다.
+동 가운데 성내천이 흐르며, 위례성길 · 오금로 · 남부순환로 · 거여동길이 있고 지하철 5호선이 지나 교통이 편리하다.</t>
         </is>
       </c>
     </row>
@@ -16143,8 +16059,7 @@
       </c>
       <c r="L215" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">송파구의 북서쪽 끝에 있는 동이다.
-한강변에 있으며, 북쪽은 광진구 자양동, 동쪽은 신천동, 서쪽은 탄천을 경계로 강남구 삼성동, 남쪽은 삼전동과 접해 있다.
+          <t xml:space="preserve">한강변에 있으며, 북쪽은 광진구 자양동, 동쪽은 신천동, 서쪽은 탄천을 경계로 강남구 삼성동, 남쪽은 삼전동과 접해 있다.
 조선시대 잠실도회(蠶室都會)가 설치된 데서 동명이 유래되었다.
 1949년 서울특별시 성동구에 편입되어 뚝도출장소 관할이 되었으며, 1975년 강남구, 1979년 강동구를 거쳐 1988년에 송파구가 신설되어 여기에 포함되었다.
 1970년대 초 잠실지구토지구획정리사업에 따른 공유수면매립으로 조성된 넓은 택지에 주공아파트단지가 형성되면서 농사를 짓는 조용한 뽕나무마을은 서울과 대한민국을 상징하는 시설물이 건설되는 상전벽해의 상업 및 일반 주거지역이 되었다.
@@ -16156,11 +16071,11 @@
         </is>
       </c>
       <c r="M215" s="0">
-        <v>691</v>
+        <v>671</v>
       </c>
       <c r="N215" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">송파구의 북서쪽 끝에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -16221,8 +16136,7 @@
       </c>
       <c r="L216" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">송파구의 남쪽 끝에 있는 동이다.
-동쪽은 거여동, 서쪽은 문정동, 남쪽은 성남시, 북쪽은 문정동 · 가락동 · 거여동과 접해 있다.
+          <t xml:space="preserve">동쪽은 거여동, 서쪽은 문정동, 남쪽은 성남시, 북쪽은 문정동 · 가락동 · 거여동과 접해 있다.
 마을 모습이 길게 형성되어 있고, 또 잔버들이 많이 있다 하여 동명이 유래되었다.
 1963년 서울특별시 성동구에 편입되어 송파출장소 관할이 되었으며, 1975년 강남구, 1979년 강동구를 거쳐 1988년에 송파구가 신설되어 여기에 포함되었다.
 1970년대까지도 서울 근교의 농촌마을로 주민 대부분이 농업에 종사하였으나, 송파구가 도시화되면서 서울특별시의 끝에 있어 시내버스 종점과 운수회사들이 입주하였다.
@@ -16231,11 +16145,11 @@
         </is>
       </c>
       <c r="M216" s="0">
-        <v>407</v>
+        <v>388</v>
       </c>
       <c r="N216" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">송파구의 남쪽 끝에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -16296,19 +16210,19 @@
       </c>
       <c r="L217" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">송파구의 북쪽 끝 한강변에 있는 동이다.
-동쪽은 강동구 성내동, 남쪽은 방이동, 서쪽은 신천동, 북쪽은 한강을 사이로 광진구 광장동과 접해 있다.
+          <t xml:space="preserve">동쪽은 강동구 성내동, 남쪽은 방이동, 서쪽은 신천동, 북쪽은 한강을 사이로 광진구 광장동과 접해 있다.
 바람드리 마을을 한자로 표기하여 동명이 유래되었다.
 1963년 서울특별시 성동구에 편입되어 송파출장소 관할이 되었으며, 1975년 강남구, 1979년 강동구를 거쳐 1988년 송파구가 신설되어 여기에 포함되었다.
 한강의 범람으로 질 좋은 흙이 퇴적되어 1970년대 이전 옹기 · 기와 · 벽돌 · 토관 · 화분 등을 만드는 도요업(陶窯業)이 발달하였으며, 이후 주택가로 변하면서 공장들이 외곽지대로 이전하게 되었다.</t>
         </is>
       </c>
       <c r="M217" s="0">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N217" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">북쪽 한강 제방 위로 올림픽대로가 지나며 강동대로가 올림픽대교와 이어져 있고, 천호대로 · 풍납로와 지하철 8호선이 지나 교통이 편리하다.</t>
+          <t xml:space="preserve">송파구의 북쪽 끝 한강변에 있는 동이다.
+북쪽 한강 제방 위로 올림픽대로가 지나며 강동대로가 올림픽대교와 이어져 있고, 천호대로 · 풍납로와 지하철 8호선이 지나 교통이 편리하다.</t>
         </is>
       </c>
     </row>
@@ -16369,8 +16283,7 @@
       </c>
       <c r="L218" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 북부에 위치한 동이다.
-목동의 동명 유래는 말을 방목하는 목장이 있었기 때문에 목동(牧洞)이라 하였다가 점차 표기가 달라져 목동(木洞)으로 되었다는 설과, 옛날부터 나무가 매우 많았으므로 목동(木洞)이라 하였다는 설이 있다.
+          <t xml:space="preserve">목동의 동명 유래는 말을 방목하는 목장이 있었기 때문에 목동(牧洞)이라 하였다가 점차 표기가 달라져 목동(木洞)으로 되었다는 설과, 옛날부터 나무가 매우 많았으므로 목동(木洞)이라 하였다는 설이 있다.
 조선시대 양천현(陽川縣)에 속하였고, 1895년 양천군 남산면(南山面)이 되었으며, 1914년 김포군 양동면 목동리(木洞里)라 칭하였다.
 1963년 서울특별시 영등포구 목동이 되었으며, 1977년 강서구에 속하였다가 1988년 강서구에서 양천구를 분리 신설할 때 양천구 관할이 되었다.
 동의 서쪽과 북쪽에는 강서구, 동쪽에는 안양천을 따라 영등포구, 남쪽에는 신정동이 접하고 있다.
@@ -16379,11 +16292,11 @@
         </is>
       </c>
       <c r="M218" s="0">
-        <v>444</v>
+        <v>428</v>
       </c>
       <c r="N218" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 북부에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -16444,8 +16357,7 @@
       </c>
       <c r="L219" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 동부에 위치한 동이다.
-신월동 동명의 유래는 조선시대 이 고을 원님이 양천향교(陽川鄕校)를 지나 현 화곡아파트 부근 돌다리 앞에 이르러 전망을 보니 마을이 신선하고 반달 모양을 하고 있어 신월리(新月里)라 부른 데서 비롯되었다.
+          <t xml:space="preserve">신월동 동명의 유래는 조선시대 이 고을 원님이 양천향교(陽川鄕校)를 지나 현 화곡아파트 부근 돌다리 앞에 이르러 전망을 보니 마을이 신선하고 반달 모양을 하고 있어 신월리(新月里)라 부른 데서 비롯되었다.
 조선시대 양천현에 속하였고, 1895년 양천군 남산면이 되었으며, 1914년 김포군 양동면 신당리(新堂里)라 칭하였다.
 1963년 서울특별시 영등포구 신월동이 되었으며, 1977년 강서구에 속하였다가 1988년 강서구에서 양천구를 분리 신설할 때 양천구 관할이 되었다.
 동의 서쪽은 경기도 부천시, 북쪽은 강서구, 동쪽은 신정동, 남쪽은 구로구에 접하고 있다.
@@ -16455,11 +16367,11 @@
         </is>
       </c>
       <c r="M219" s="0">
-        <v>460</v>
+        <v>444</v>
       </c>
       <c r="N219" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 동부에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -16518,8 +16430,7 @@
       </c>
       <c r="L220" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 중앙에 위치한 동이다.
-신정동 동명의 유래는 이 동의 자연마을이었던 신기(新機, 新基, 신트리, 새터)의 ‘신’(新)자와 은행정(銀杏亭)의 ‘정’(亭)자를 딴 데서 비롯되었다.
+          <t xml:space="preserve">신정동 동명의 유래는 이 동의 자연마을이었던 신기(新機, 新基, 신트리, 새터)의 ‘신’(新)자와 은행정(銀杏亭)의 ‘정’(亭)자를 딴 데서 비롯되었다.
 조선시대 양천현에 속하였고, 1895년 양천군 남산면이 되었으며, 1914년 김포군 양동면 신정리라 칭하였다.
 1963년 서울특별시 영등포구 신정동이 되었으며, 1977년 강서구에 속하였다가 1988년 강서구에서 양천구를 분리 신설할 때 양천구 관할이 되었다.
 동의 서쪽은 신월동, 북쪽은 목동, 동쪽에는 안양천을 따라 영등포구, 남쪽에는 구로구가 접하고 있다.
@@ -16528,11 +16439,11 @@
         </is>
       </c>
       <c r="M220" s="0">
-        <v>406</v>
+        <v>390</v>
       </c>
       <c r="N220" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 중앙에 위치한 동이다.</t>
         </is>
       </c>
     </row>
@@ -16596,8 +16507,7 @@
       </c>
       <c r="L221" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 북쪽에 있는 동이다.
-동쪽은 여의도동, 서쪽은 양평동, 남쪽은 영등포동, 북쪽은 한강을 경계로 마포구 합정동과 접해 있다.
+          <t xml:space="preserve">동쪽은 여의도동, 서쪽은 양평동, 남쪽은 영등포동, 북쪽은 한강을 경계로 마포구 합정동과 접해 있다.
 마을 언덕에 부군당(府君堂)이 있었던 데서 동명이 유래되었다.
 경기도 시흥군 상북면 · 북면 당산리였다가 1936년 경성부에 편입되어 당산정이 되어 영등포출장소 관할이 되었고, 1943년 구제가 실시되면서 영등포구에 속하였다가, 1946년에 당산동이 되었다.
 1912년 일제강점기부터 조선피혁주식회사 등 방적 · 기계 · 맥주 · 장유(醬油) 등의 공장이 들어서기 시작하였고, 1960년 이후에는 정부의 공업정책에 따라 많은 공장들이 세워지고 상가가 형성되었다.
@@ -16611,11 +16521,11 @@
         </is>
       </c>
       <c r="M221" s="0">
-        <v>822</v>
+        <v>807</v>
       </c>
       <c r="N221" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 북쪽에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -16679,8 +16589,7 @@
       </c>
       <c r="L222" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 북쪽에 있는 동이다.
-동쪽은 여의도동, 서쪽은 양평동, 남쪽은 영등포동, 북쪽은 한강을 경계로 마포구 합정동과 접해 있다.
+          <t xml:space="preserve">동쪽은 여의도동, 서쪽은 양평동, 남쪽은 영등포동, 북쪽은 한강을 경계로 마포구 합정동과 접해 있다.
 마을 언덕에 부군당(府君堂)이 있었던 데서 동명이 유래되었다.
 경기도 시흥군 상북면 · 북면 당산리였다가 1936년 경성부에 편입되어 당산정이 되어 영등포출장소 관할이 되었고, 1943년 구제가 실시되면서 영등포구에 속하였다가, 1946년에 당산동이 되었다.
 1912년 일제강점기부터 조선피혁주식회사 등 방적 · 기계 · 맥주 · 장유(醬油) 등의 공장이 들어서기 시작하였고, 1960년 이후에는 정부의 공업정책에 따라 많은 공장들이 세워지고 상가가 형성되었다.
@@ -16694,11 +16603,11 @@
         </is>
       </c>
       <c r="M222" s="0">
-        <v>822</v>
+        <v>807</v>
       </c>
       <c r="N222" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 북쪽에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -16762,8 +16671,7 @@
       </c>
       <c r="L223" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 북쪽에 있는 동이다.
-동쪽은 여의도동, 서쪽은 양평동, 남쪽은 영등포동, 북쪽은 한강을 경계로 마포구 합정동과 접해 있다.
+          <t xml:space="preserve">동쪽은 여의도동, 서쪽은 양평동, 남쪽은 영등포동, 북쪽은 한강을 경계로 마포구 합정동과 접해 있다.
 마을 언덕에 부군당(府君堂)이 있었던 데서 동명이 유래되었다.
 경기도 시흥군 상북면 · 북면 당산리였다가 1936년 경성부에 편입되어 당산정이 되어 영등포출장소 관할이 되었고, 1943년 구제가 실시되면서 영등포구에 속하였다가, 1946년에 당산동이 되었다.
 1912년 일제강점기부터 조선피혁주식회사 등 방적 · 기계 · 맥주 · 장유(醬油) 등의 공장이 들어서기 시작하였고, 1960년 이후에는 정부의 공업정책에 따라 많은 공장들이 세워지고 상가가 형성되었다.
@@ -16777,11 +16685,11 @@
         </is>
       </c>
       <c r="M223" s="0">
-        <v>822</v>
+        <v>807</v>
       </c>
       <c r="N223" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 북쪽에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -16845,8 +16753,7 @@
       </c>
       <c r="L224" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 북쪽에 있는 동이다.
-동쪽은 여의도동, 서쪽은 양평동, 남쪽은 영등포동, 북쪽은 한강을 경계로 마포구 합정동과 접해 있다.
+          <t xml:space="preserve">동쪽은 여의도동, 서쪽은 양평동, 남쪽은 영등포동, 북쪽은 한강을 경계로 마포구 합정동과 접해 있다.
 마을 언덕에 부군당(府君堂)이 있었던 데서 동명이 유래되었다.
 경기도 시흥군 상북면 · 북면 당산리였다가 1936년 경성부에 편입되어 당산정이 되어 영등포출장소 관할이 되었고, 1943년 구제가 실시되면서 영등포구에 속하였다가, 1946년에 당산동이 되었다.
 1912년 일제강점기부터 조선피혁주식회사 등 방적 · 기계 · 맥주 · 장유(醬油) 등의 공장이 들어서기 시작하였고, 1960년 이후에는 정부의 공업정책에 따라 많은 공장들이 세워지고 상가가 형성되었다.
@@ -16860,11 +16767,11 @@
         </is>
       </c>
       <c r="M224" s="0">
-        <v>822</v>
+        <v>807</v>
       </c>
       <c r="N224" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 북쪽에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -16928,8 +16835,7 @@
       </c>
       <c r="L225" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 북쪽에 있는 동이다.
-동쪽은 여의도동, 서쪽은 양평동, 남쪽은 영등포동, 북쪽은 한강을 경계로 마포구 합정동과 접해 있다.
+          <t xml:space="preserve">동쪽은 여의도동, 서쪽은 양평동, 남쪽은 영등포동, 북쪽은 한강을 경계로 마포구 합정동과 접해 있다.
 마을 언덕에 부군당(府君堂)이 있었던 데서 동명이 유래되었다.
 경기도 시흥군 상북면 · 북면 당산리였다가 1936년 경성부에 편입되어 당산정이 되어 영등포출장소 관할이 되었고, 1943년 구제가 실시되면서 영등포구에 속하였다가, 1946년에 당산동이 되었다.
 1912년 일제강점기부터 조선피혁주식회사 등 방적 · 기계 · 맥주 · 장유(醬油) 등의 공장이 들어서기 시작하였고, 1960년 이후에는 정부의 공업정책에 따라 많은 공장들이 세워지고 상가가 형성되었다.
@@ -16943,11 +16849,11 @@
         </is>
       </c>
       <c r="M225" s="0">
-        <v>822</v>
+        <v>807</v>
       </c>
       <c r="N225" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 북쪽에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -17011,8 +16917,7 @@
       </c>
       <c r="L226" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 북쪽에 있는 동이다.
-동쪽은 여의도동, 서쪽은 양평동, 남쪽은 영등포동, 북쪽은 한강을 경계로 마포구 합정동과 접해 있다.
+          <t xml:space="preserve">동쪽은 여의도동, 서쪽은 양평동, 남쪽은 영등포동, 북쪽은 한강을 경계로 마포구 합정동과 접해 있다.
 마을 언덕에 부군당(府君堂)이 있었던 데서 동명이 유래되었다.
 경기도 시흥군 상북면 · 북면 당산리였다가 1936년 경성부에 편입되어 당산정이 되어 영등포출장소 관할이 되었고, 1943년 구제가 실시되면서 영등포구에 속하였다가, 1946년에 당산동이 되었다.
 1912년 일제강점기부터 조선피혁주식회사 등 방적 · 기계 · 맥주 · 장유(醬油) 등의 공장이 들어서기 시작하였고, 1960년 이후에는 정부의 공업정책에 따라 많은 공장들이 세워지고 상가가 형성되었다.
@@ -17026,11 +16931,11 @@
         </is>
       </c>
       <c r="M226" s="0">
-        <v>822</v>
+        <v>807</v>
       </c>
       <c r="N226" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 북쪽에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -17094,8 +16999,7 @@
       </c>
       <c r="L227" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 북쪽에 있는 동이다.
-동쪽은 여의도동, 서쪽은 양평동, 남쪽은 영등포동, 북쪽은 한강을 경계로 마포구 합정동과 접해 있다.
+          <t xml:space="preserve">동쪽은 여의도동, 서쪽은 양평동, 남쪽은 영등포동, 북쪽은 한강을 경계로 마포구 합정동과 접해 있다.
 마을 언덕에 부군당(府君堂)이 있었던 데서 동명이 유래되었다.
 경기도 시흥군 상북면 · 북면 당산리였다가 1936년 경성부에 편입되어 당산정이 되어 영등포출장소 관할이 되었고, 1943년 구제가 실시되면서 영등포구에 속하였다가, 1946년에 당산동이 되었다.
 1912년 일제강점기부터 조선피혁주식회사 등 방적 · 기계 · 맥주 · 장유(醬油) 등의 공장이 들어서기 시작하였고, 1960년 이후에는 정부의 공업정책에 따라 많은 공장들이 세워지고 상가가 형성되었다.
@@ -17109,11 +17013,11 @@
         </is>
       </c>
       <c r="M227" s="0">
-        <v>822</v>
+        <v>807</v>
       </c>
       <c r="N227" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 북쪽에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -17173,8 +17077,7 @@
       </c>
       <c r="L228" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 남쪽 끝에 있는 동이다.
-동쪽은 동작구 신대방동, 서쪽은 도림천을 경계로 구로구 구로동, 남쪽은 금천구 가리봉동, 북쪽은 도림동 · 신길동과 접해 있다.
+          <t xml:space="preserve">동쪽은 동작구 신대방동, 서쪽은 도림천을 경계로 구로구 구로동, 남쪽은 금천구 가리봉동, 북쪽은 도림동 · 신길동과 접해 있다.
 동명은 신대방동의 ‘대’자와 신도림동의 ‘림’자를 따서 붙인 데서 유래되었다.
 금천현 상북면 도야미리(道也味里) 지역이었는데, 1914년 시흥군 북면 도림리가 되었고, 1936년 시흥군 동면에 속하게 되었다.
 1949년 영등포구에 편입되면서 도림리는 구로리 · 번대방리와 함께 신도림동이 되었고, 1980년 신도림동은 구로구 신도림동과 영등포구 도림동으로 분동되어 오늘에 이른다.
@@ -17183,11 +17086,12 @@
         </is>
       </c>
       <c r="M228" s="0">
-        <v>424</v>
+        <v>407</v>
       </c>
       <c r="N228" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동의 북서쪽에는 도림로, 남동쪽에는 시흥대로가 지나고, 지하철 2호선 대림역과 구로디지털단지역 및 지하철 7호선이 지나 대중교통 이용이 편리하다.</t>
+          <t xml:space="preserve">구의 남쪽 끝에 있는 동이다.
+동의 북서쪽에는 도림로, 남동쪽에는 시흥대로가 지나고, 지하철 2호선 대림역과 구로디지털단지역 및 지하철 7호선이 지나 대중교통 이용이 편리하다.</t>
         </is>
       </c>
     </row>
@@ -17249,8 +17153,7 @@
       </c>
       <c r="L229" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 중앙 서쪽에 있는 동이다.
-동쪽은 신길동, 서쪽의 문래동, 남쪽은 대림동 · 신길동, 북쪽은 영등포동과 접해 있다.
+          <t xml:space="preserve">동쪽은 신길동, 서쪽의 문래동, 남쪽은 대림동 · 신길동, 북쪽은 영등포동과 접해 있다.
 동명 유래는 마을 뒤쪽의 야산이 성처럼 둘러싸고 있다 하여 되미리, 도야미리(道也味里)라고 하던 것이 음이 바뀌어 도림리(道林里)가 되었다.
 경기도 시흥군 상북면 도야미리였다가, 1914년 북면 도림리로 변하였다.
 1936년 경성부에 편입되면서 도림정이 되어 영등포출장소 관할이 되었다가, 1943년 구제 실시에 따라 영등포구에 속하였고, 1946년에 도림동이 되었다.
@@ -17260,11 +17163,11 @@
         </is>
       </c>
       <c r="M229" s="0">
-        <v>461</v>
+        <v>443</v>
       </c>
       <c r="N229" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 중앙 서쪽에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -17327,8 +17230,7 @@
       </c>
       <c r="L230" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 중앙 서쪽에 있는 동이다.
-동쪽은 영등포동, 서쪽은 강서구 신정동, 남쪽은 도림동, 북쪽의 당산동과 접해 있다.
+          <t xml:space="preserve">동쪽은 영등포동, 서쪽은 강서구 신정동, 남쪽은 도림동, 북쪽의 당산동과 접해 있다.
 동명 유래는 일제강점기 이곳에 방직공장이 들어서면서 일본인들이 사옥정이라 부르던 것을 방적기계의 물레와 문익점의 목화 전래의미를 빌려 문래동이 되었다고 한다.
 1943년 도림동에서 분동되어 영등포구 사옥정이 되었고, 1946년 사옥동이 되었다가 1952년경에 문래동으로 개칭되었다.
 이 지역 일대는 늪지대로서 갈대숲을 이루었는데, 일제강점기에 영등포초등학교와 종연(鐘淵) · 동양 등 방직회사들이 들어서면서 마을이 개발되기 시작하였다.
@@ -17340,11 +17242,11 @@
         </is>
       </c>
       <c r="M230" s="0">
-        <v>629</v>
+        <v>611</v>
       </c>
       <c r="N230" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 중앙 서쪽에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -17407,8 +17309,7 @@
       </c>
       <c r="L231" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 중앙 서쪽에 있는 동이다.
-동쪽은 영등포동, 서쪽은 강서구 신정동, 남쪽은 도림동, 북쪽의 당산동과 접해 있다.
+          <t xml:space="preserve">동쪽은 영등포동, 서쪽은 강서구 신정동, 남쪽은 도림동, 북쪽의 당산동과 접해 있다.
 동명 유래는 일제강점기 이곳에 방직공장이 들어서면서 일본인들이 사옥정이라 부르던 것을 방적기계의 물레와 문익점의 목화 전래의미를 빌려 문래동이 되었다고 한다.
 1943년 도림동에서 분동되어 영등포구 사옥정이 되었고, 1946년 사옥동이 되었다가 1952년경에 문래동으로 개칭되었다.
 이 지역 일대는 늪지대로서 갈대숲을 이루었는데, 일제강점기에 영등포초등학교와 종연(鐘淵) · 동양 등 방직회사들이 들어서면서 마을이 개발되기 시작하였다.
@@ -17420,11 +17321,11 @@
         </is>
       </c>
       <c r="M231" s="0">
-        <v>629</v>
+        <v>611</v>
       </c>
       <c r="N231" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 중앙 서쪽에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -17487,8 +17388,7 @@
       </c>
       <c r="L232" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 중앙 서쪽에 있는 동이다.
-동쪽은 영등포동, 서쪽은 강서구 신정동, 남쪽은 도림동, 북쪽의 당산동과 접해 있다.
+          <t xml:space="preserve">동쪽은 영등포동, 서쪽은 강서구 신정동, 남쪽은 도림동, 북쪽의 당산동과 접해 있다.
 동명 유래는 일제강점기 이곳에 방직공장이 들어서면서 일본인들이 사옥정이라 부르던 것을 방적기계의 물레와 문익점의 목화 전래의미를 빌려 문래동이 되었다고 한다.
 1943년 도림동에서 분동되어 영등포구 사옥정이 되었고, 1946년 사옥동이 되었다가 1952년경에 문래동으로 개칭되었다.
 이 지역 일대는 늪지대로서 갈대숲을 이루었는데, 일제강점기에 영등포초등학교와 종연(鐘淵) · 동양 등 방직회사들이 들어서면서 마을이 개발되기 시작하였다.
@@ -17500,11 +17400,11 @@
         </is>
       </c>
       <c r="M232" s="0">
-        <v>629</v>
+        <v>611</v>
       </c>
       <c r="N232" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 중앙 서쪽에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -17567,8 +17467,7 @@
       </c>
       <c r="L233" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 중앙 서쪽에 있는 동이다.
-동쪽은 영등포동, 서쪽은 강서구 신정동, 남쪽은 도림동, 북쪽의 당산동과 접해 있다.
+          <t xml:space="preserve">동쪽은 영등포동, 서쪽은 강서구 신정동, 남쪽은 도림동, 북쪽의 당산동과 접해 있다.
 동명 유래는 일제강점기 이곳에 방직공장이 들어서면서 일본인들이 사옥정이라 부르던 것을 방적기계의 물레와 문익점의 목화 전래의미를 빌려 문래동이 되었다고 한다.
 1943년 도림동에서 분동되어 영등포구 사옥정이 되었고, 1946년 사옥동이 되었다가 1952년경에 문래동으로 개칭되었다.
 이 지역 일대는 늪지대로서 갈대숲을 이루었는데, 일제강점기에 영등포초등학교와 종연(鐘淵) · 동양 등 방직회사들이 들어서면서 마을이 개발되기 시작하였다.
@@ -17580,11 +17479,11 @@
         </is>
       </c>
       <c r="M233" s="0">
-        <v>629</v>
+        <v>611</v>
       </c>
       <c r="N233" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 중앙 서쪽에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -17647,8 +17546,7 @@
       </c>
       <c r="L234" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 중앙 서쪽에 있는 동이다.
-동쪽은 영등포동, 서쪽은 강서구 신정동, 남쪽은 도림동, 북쪽의 당산동과 접해 있다.
+          <t xml:space="preserve">동쪽은 영등포동, 서쪽은 강서구 신정동, 남쪽은 도림동, 북쪽의 당산동과 접해 있다.
 동명 유래는 일제강점기 이곳에 방직공장이 들어서면서 일본인들이 사옥정이라 부르던 것을 방적기계의 물레와 문익점의 목화 전래의미를 빌려 문래동이 되었다고 한다.
 1943년 도림동에서 분동되어 영등포구 사옥정이 되었고, 1946년 사옥동이 되었다가 1952년경에 문래동으로 개칭되었다.
 이 지역 일대는 늪지대로서 갈대숲을 이루었는데, 일제강점기에 영등포초등학교와 종연(鐘淵) · 동양 등 방직회사들이 들어서면서 마을이 개발되기 시작하였다.
@@ -17660,11 +17558,11 @@
         </is>
       </c>
       <c r="M234" s="0">
-        <v>629</v>
+        <v>611</v>
       </c>
       <c r="N234" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 중앙 서쪽에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -17727,8 +17625,7 @@
       </c>
       <c r="L235" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 중앙 서쪽에 있는 동이다.
-동쪽은 영등포동, 서쪽은 강서구 신정동, 남쪽은 도림동, 북쪽의 당산동과 접해 있다.
+          <t xml:space="preserve">동쪽은 영등포동, 서쪽은 강서구 신정동, 남쪽은 도림동, 북쪽의 당산동과 접해 있다.
 동명 유래는 일제강점기 이곳에 방직공장이 들어서면서 일본인들이 사옥정이라 부르던 것을 방적기계의 물레와 문익점의 목화 전래의미를 빌려 문래동이 되었다고 한다.
 1943년 도림동에서 분동되어 영등포구 사옥정이 되었고, 1946년 사옥동이 되었다가 1952년경에 문래동으로 개칭되었다.
 이 지역 일대는 늪지대로서 갈대숲을 이루었는데, 일제강점기에 영등포초등학교와 종연(鐘淵) · 동양 등 방직회사들이 들어서면서 마을이 개발되기 시작하였다.
@@ -17740,11 +17637,11 @@
         </is>
       </c>
       <c r="M235" s="0">
-        <v>629</v>
+        <v>611</v>
       </c>
       <c r="N235" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 중앙 서쪽에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -17806,8 +17703,7 @@
       </c>
       <c r="L236" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 남동쪽에 있는 동이다.
-동쪽은 동작구 대방동, 서쪽은 도림동과 영등포동, 남쪽은 대림동과 동작구 대방동, 북쪽은 여의도동과 접해 있다.
+          <t xml:space="preserve">동쪽은 동작구 대방동, 서쪽은 도림동과 영등포동, 남쪽은 대림동과 동작구 대방동, 북쪽은 여의도동과 접해 있다.
 동명 유래는 정확하지 않으나 신기리라 불렸던 마을이름과 새로운 좋은 일이 생기기를 기원하는 뜻에서 붙여진 이름으로 보고 있다.
 경기도 금천현 하북면 신길리였다가 1914년 시흥군 북면 신길리가 되었으며, 1936년 경성부에 편입되면서 신길정이 되어 영등포출장소 관할이 되었다.
 1943년 구제 실시에 따라 영등포구에 속하게 되었다가, 1946년 신길동이 되었다.
@@ -17816,11 +17712,11 @@
         </is>
       </c>
       <c r="M236" s="0">
-        <v>368</v>
+        <v>352</v>
       </c>
       <c r="N236" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 남동쪽에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -17883,8 +17779,7 @@
       </c>
       <c r="L237" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 서북 끝에 있는 동이다.
-서쪽은 안양천을 경계로 양천구 목동, 북쪽은 한강을 경계로 마포구 망원동, 동쪽은 당산동, 남쪽은 문래동과 접해 있다.
+          <t xml:space="preserve">서쪽은 안양천을 경계로 양천구 목동, 북쪽은 한강을 경계로 마포구 망원동, 동쪽은 당산동, 남쪽은 문래동과 접해 있다.
 동명 유래는 한강 나루터인 양화진(楊花津) 근처 벌판에 형성된 마을인 데서 붙여졌다.
 경기도 시흥군 상북면 · 북면의 양평리였다가 1931년 시흥군 영등포읍 양평리가 되었다.
 1936년 경성부에 편입되면서 양평정이 되어 영등포출장소 관할이 되었다.
@@ -17901,11 +17796,11 @@
         </is>
       </c>
       <c r="M237" s="0">
-        <v>813</v>
+        <v>796</v>
       </c>
       <c r="N237" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 서북 끝에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -17968,8 +17863,7 @@
       </c>
       <c r="L238" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 서북 끝에 있는 동이다.
-서쪽은 안양천을 경계로 양천구 목동, 북쪽은 한강을 경계로 마포구 망원동, 동쪽은 당산동, 남쪽은 문래동과 접해 있다.
+          <t xml:space="preserve">서쪽은 안양천을 경계로 양천구 목동, 북쪽은 한강을 경계로 마포구 망원동, 동쪽은 당산동, 남쪽은 문래동과 접해 있다.
 동명 유래는 한강 나루터인 양화진(楊花津) 근처 벌판에 형성된 마을인 데서 붙여졌다.
 경기도 시흥군 상북면 · 북면의 양평리였다가 1931년 시흥군 영등포읍 양평리가 되었다.
 1936년 경성부에 편입되면서 양평정이 되어 영등포출장소 관할이 되었다.
@@ -17986,11 +17880,11 @@
         </is>
       </c>
       <c r="M238" s="0">
-        <v>813</v>
+        <v>796</v>
       </c>
       <c r="N238" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 서북 끝에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -18053,8 +17947,7 @@
       </c>
       <c r="L239" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 서북 끝에 있는 동이다.
-서쪽은 안양천을 경계로 양천구 목동, 북쪽은 한강을 경계로 마포구 망원동, 동쪽은 당산동, 남쪽은 문래동과 접해 있다.
+          <t xml:space="preserve">서쪽은 안양천을 경계로 양천구 목동, 북쪽은 한강을 경계로 마포구 망원동, 동쪽은 당산동, 남쪽은 문래동과 접해 있다.
 동명 유래는 한강 나루터인 양화진(楊花津) 근처 벌판에 형성된 마을인 데서 붙여졌다.
 경기도 시흥군 상북면 · 북면의 양평리였다가 1931년 시흥군 영등포읍 양평리가 되었다.
 1936년 경성부에 편입되면서 양평정이 되어 영등포출장소 관할이 되었다.
@@ -18071,11 +17964,11 @@
         </is>
       </c>
       <c r="M239" s="0">
-        <v>813</v>
+        <v>796</v>
       </c>
       <c r="N239" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 서북 끝에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -18138,8 +18031,7 @@
       </c>
       <c r="L240" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 서북 끝에 있는 동이다.
-서쪽은 안양천을 경계로 양천구 목동, 북쪽은 한강을 경계로 마포구 망원동, 동쪽은 당산동, 남쪽은 문래동과 접해 있다.
+          <t xml:space="preserve">서쪽은 안양천을 경계로 양천구 목동, 북쪽은 한강을 경계로 마포구 망원동, 동쪽은 당산동, 남쪽은 문래동과 접해 있다.
 동명 유래는 한강 나루터인 양화진(楊花津) 근처 벌판에 형성된 마을인 데서 붙여졌다.
 경기도 시흥군 상북면 · 북면의 양평리였다가 1931년 시흥군 영등포읍 양평리가 되었다.
 1936년 경성부에 편입되면서 양평정이 되어 영등포출장소 관할이 되었다.
@@ -18156,11 +18048,11 @@
         </is>
       </c>
       <c r="M240" s="0">
-        <v>813</v>
+        <v>796</v>
       </c>
       <c r="N240" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 서북 끝에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -18223,8 +18115,7 @@
       </c>
       <c r="L241" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 서북 끝에 있는 동이다.
-서쪽은 안양천을 경계로 양천구 목동, 북쪽은 한강을 경계로 마포구 망원동, 동쪽은 당산동, 남쪽은 문래동과 접해 있다.
+          <t xml:space="preserve">서쪽은 안양천을 경계로 양천구 목동, 북쪽은 한강을 경계로 마포구 망원동, 동쪽은 당산동, 남쪽은 문래동과 접해 있다.
 동명 유래는 한강 나루터인 양화진(楊花津) 근처 벌판에 형성된 마을인 데서 붙여졌다.
 경기도 시흥군 상북면 · 북면의 양평리였다가 1931년 시흥군 영등포읍 양평리가 되었다.
 1936년 경성부에 편입되면서 양평정이 되어 영등포출장소 관할이 되었다.
@@ -18241,11 +18132,11 @@
         </is>
       </c>
       <c r="M241" s="0">
-        <v>813</v>
+        <v>796</v>
       </c>
       <c r="N241" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 서북 끝에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -18308,8 +18199,7 @@
       </c>
       <c r="L242" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 서북 끝에 있는 동이다.
-서쪽은 안양천을 경계로 양천구 목동, 북쪽은 한강을 경계로 마포구 망원동, 동쪽은 당산동, 남쪽은 문래동과 접해 있다.
+          <t xml:space="preserve">서쪽은 안양천을 경계로 양천구 목동, 북쪽은 한강을 경계로 마포구 망원동, 동쪽은 당산동, 남쪽은 문래동과 접해 있다.
 동명 유래는 한강 나루터인 양화진(楊花津) 근처 벌판에 형성된 마을인 데서 붙여졌다.
 경기도 시흥군 상북면 · 북면의 양평리였다가 1931년 시흥군 영등포읍 양평리가 되었다.
 1936년 경성부에 편입되면서 양평정이 되어 영등포출장소 관할이 되었다.
@@ -18326,11 +18216,11 @@
         </is>
       </c>
       <c r="M242" s="0">
-        <v>813</v>
+        <v>796</v>
       </c>
       <c r="N242" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 서북 끝에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -18393,8 +18283,7 @@
       </c>
       <c r="L243" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 서북 끝에 있는 동이다.
-서쪽은 안양천을 경계로 양천구 목동, 북쪽은 한강을 경계로 마포구 망원동, 동쪽은 당산동, 남쪽은 문래동과 접해 있다.
+          <t xml:space="preserve">서쪽은 안양천을 경계로 양천구 목동, 북쪽은 한강을 경계로 마포구 망원동, 동쪽은 당산동, 남쪽은 문래동과 접해 있다.
 동명 유래는 한강 나루터인 양화진(楊花津) 근처 벌판에 형성된 마을인 데서 붙여졌다.
 경기도 시흥군 상북면 · 북면의 양평리였다가 1931년 시흥군 영등포읍 양평리가 되었다.
 1936년 경성부에 편입되면서 양평정이 되어 영등포출장소 관할이 되었다.
@@ -18411,11 +18300,11 @@
         </is>
       </c>
       <c r="M243" s="0">
-        <v>813</v>
+        <v>796</v>
       </c>
       <c r="N243" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 서북 끝에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -18477,8 +18366,7 @@
       </c>
       <c r="L244" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 서북쪽 끝에 있는 동으로 면적과 인구의 통계는 양평동에 편입되어 있다.
-북쪽은 한강 건너 마포구 망원동, 서쪽은 안양천 건너 강서구 염창동, 남쪽은 안양천 건너 양천구 목동(木洞), 동쪽은 양평동과 접해 있다.
+          <t xml:space="preserve">북쪽은 한강 건너 마포구 망원동, 서쪽은 안양천 건너 강서구 염창동, 남쪽은 안양천 건너 양천구 목동(木洞), 동쪽은 양평동과 접해 있다.
 경기도 양천군 남산면 양화리였다가, 1914년 김포군 양동면 양화리가 되었으며, 1936년 경성부에 편입되어 영등포출장소 양화정이 되어 영등포출장소 관할이 되었다.
 1943년 구제 실시에 따라 영등포구에 속하게 되었다가, 1946년 10월 양화동이 되었다.
 동명 유래는 버드나무가 많은 나루터인 양화도가 있었던 데서 연유되었다.
@@ -18488,11 +18376,12 @@
         </is>
       </c>
       <c r="M244" s="0">
-        <v>428</v>
+        <v>385</v>
       </c>
       <c r="N244" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">선유정수사업소가 있던 곳은 선유도공원으로 꾸며져 자연생태학습장으로 구실하고 있다.</t>
+          <t xml:space="preserve">구의 서북쪽 끝에 있는 동으로 면적과 인구의 통계는 양평동에 편입되어 있다.
+선유정수사업소가 있던 곳은 선유도공원으로 꾸며져 자연생태학습장으로 구실하고 있다.</t>
         </is>
       </c>
     </row>
@@ -18636,8 +18525,7 @@
       </c>
       <c r="L246" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 중앙에 있는 동이다.
-동쪽은 여의도동 · 신길동, 서쪽은 당산동 · 문래동, 남쪽은 신길동 · 도림동, 북쪽은 당산동과 접해 있다.
+          <t xml:space="preserve">동쪽은 여의도동 · 신길동, 서쪽은 당산동 · 문래동, 남쪽은 신길동 · 도림동, 북쪽은 당산동과 접해 있다.
 동명의 유래는 정확히 알 수 없으나, 인근 신길동의 방아곶이나루와 연관하여 영등굿이 행해지던 갯마을(포구)이었던 것과 관련된 것으로 추정된다.
 경기도 금천현(衿川縣) 하북면에 속하였다가, 1914년 시흥군 하북면 하방하관리(下方下串里)와 중종리(重宗里)를 합쳐 북면 영등포리로 불리었고 1920년에 영등포면이 되었다.
 1931년 읍으로 승격되었으며, 1936년 경성부에 편입되면서 영등포정이 되었다가 1943년 구제가 실시되어 영등포구에 속하였고, 1946년 영등포동으로 바뀌었다.
@@ -18650,11 +18538,12 @@
         </is>
       </c>
       <c r="M246" s="0">
-        <v>723</v>
+        <v>708</v>
       </c>
       <c r="N246" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">영등포역 · 영등포우체국 · 영등포소방서 · 근로복지공사 · 한강성심병원 등 공공기관과 신세계 · 롯데 · 경방필백화점을 비롯한 많은 영등포시장 · 남서울시장 등 재래시장과 상가 및 유흥업소가 밀집해 있다.</t>
+          <t xml:space="preserve">구의 중앙에 있는 동이다.
+영등포역 · 영등포우체국 · 영등포소방서 · 근로복지공사 · 한강성심병원 등 공공기관과 신세계 · 롯데 · 경방필백화점을 비롯한 많은 영등포시장 · 남서울시장 등 재래시장과 상가 및 유흥업소가 밀집해 있다.</t>
         </is>
       </c>
     </row>
@@ -18717,8 +18606,7 @@
       </c>
       <c r="L247" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 중앙에 있는 동이다.
-동쪽은 여의도동 · 신길동, 서쪽은 당산동 · 문래동, 남쪽은 신길동 · 도림동, 북쪽은 당산동과 접해 있다.
+          <t xml:space="preserve">동쪽은 여의도동 · 신길동, 서쪽은 당산동 · 문래동, 남쪽은 신길동 · 도림동, 북쪽은 당산동과 접해 있다.
 동명의 유래는 정확히 알 수 없으나, 인근 신길동의 방아곶이나루와 연관하여 영등굿이 행해지던 갯마을(포구)이었던 것과 관련된 것으로 추정된다.
 경기도 금천현(衿川縣) 하북면에 속하였다가, 1914년 시흥군 하북면 하방하관리(下方下串里)와 중종리(重宗里)를 합쳐 북면 영등포리로 불리었고 1920년에 영등포면이 되었다.
 1931년 읍으로 승격되었으며, 1936년 경성부에 편입되면서 영등포정이 되었다가 1943년 구제가 실시되어 영등포구에 속하였고, 1946년 영등포동으로 바뀌었다.
@@ -18731,11 +18619,12 @@
         </is>
       </c>
       <c r="M247" s="0">
-        <v>723</v>
+        <v>708</v>
       </c>
       <c r="N247" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">영등포역 · 영등포우체국 · 영등포소방서 · 근로복지공사 · 한강성심병원 등 공공기관과 신세계 · 롯데 · 경방필백화점을 비롯한 많은 영등포시장 · 남서울시장 등 재래시장과 상가 및 유흥업소가 밀집해 있다.</t>
+          <t xml:space="preserve">구의 중앙에 있는 동이다.
+영등포역 · 영등포우체국 · 영등포소방서 · 근로복지공사 · 한강성심병원 등 공공기관과 신세계 · 롯데 · 경방필백화점을 비롯한 많은 영등포시장 · 남서울시장 등 재래시장과 상가 및 유흥업소가 밀집해 있다.</t>
         </is>
       </c>
     </row>
@@ -18798,8 +18687,7 @@
       </c>
       <c r="L248" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 중앙에 있는 동이다.
-동쪽은 여의도동 · 신길동, 서쪽은 당산동 · 문래동, 남쪽은 신길동 · 도림동, 북쪽은 당산동과 접해 있다.
+          <t xml:space="preserve">동쪽은 여의도동 · 신길동, 서쪽은 당산동 · 문래동, 남쪽은 신길동 · 도림동, 북쪽은 당산동과 접해 있다.
 동명의 유래는 정확히 알 수 없으나, 인근 신길동의 방아곶이나루와 연관하여 영등굿이 행해지던 갯마을(포구)이었던 것과 관련된 것으로 추정된다.
 경기도 금천현(衿川縣) 하북면에 속하였다가, 1914년 시흥군 하북면 하방하관리(下方下串里)와 중종리(重宗里)를 합쳐 북면 영등포리로 불리었고 1920년에 영등포면이 되었다.
 1931년 읍으로 승격되었으며, 1936년 경성부에 편입되면서 영등포정이 되었다가 1943년 구제가 실시되어 영등포구에 속하였고, 1946년 영등포동으로 바뀌었다.
@@ -18812,11 +18700,12 @@
         </is>
       </c>
       <c r="M248" s="0">
-        <v>723</v>
+        <v>708</v>
       </c>
       <c r="N248" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">영등포역 · 영등포우체국 · 영등포소방서 · 근로복지공사 · 한강성심병원 등 공공기관과 신세계 · 롯데 · 경방필백화점을 비롯한 많은 영등포시장 · 남서울시장 등 재래시장과 상가 및 유흥업소가 밀집해 있다.</t>
+          <t xml:space="preserve">구의 중앙에 있는 동이다.
+영등포역 · 영등포우체국 · 영등포소방서 · 근로복지공사 · 한강성심병원 등 공공기관과 신세계 · 롯데 · 경방필백화점을 비롯한 많은 영등포시장 · 남서울시장 등 재래시장과 상가 및 유흥업소가 밀집해 있다.</t>
         </is>
       </c>
     </row>
@@ -18879,8 +18768,7 @@
       </c>
       <c r="L249" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 중앙에 있는 동이다.
-동쪽은 여의도동 · 신길동, 서쪽은 당산동 · 문래동, 남쪽은 신길동 · 도림동, 북쪽은 당산동과 접해 있다.
+          <t xml:space="preserve">동쪽은 여의도동 · 신길동, 서쪽은 당산동 · 문래동, 남쪽은 신길동 · 도림동, 북쪽은 당산동과 접해 있다.
 동명의 유래는 정확히 알 수 없으나, 인근 신길동의 방아곶이나루와 연관하여 영등굿이 행해지던 갯마을(포구)이었던 것과 관련된 것으로 추정된다.
 경기도 금천현(衿川縣) 하북면에 속하였다가, 1914년 시흥군 하북면 하방하관리(下方下串里)와 중종리(重宗里)를 합쳐 북면 영등포리로 불리었고 1920년에 영등포면이 되었다.
 1931년 읍으로 승격되었으며, 1936년 경성부에 편입되면서 영등포정이 되었다가 1943년 구제가 실시되어 영등포구에 속하였고, 1946년 영등포동으로 바뀌었다.
@@ -18893,11 +18781,12 @@
         </is>
       </c>
       <c r="M249" s="0">
-        <v>723</v>
+        <v>708</v>
       </c>
       <c r="N249" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">영등포역 · 영등포우체국 · 영등포소방서 · 근로복지공사 · 한강성심병원 등 공공기관과 신세계 · 롯데 · 경방필백화점을 비롯한 많은 영등포시장 · 남서울시장 등 재래시장과 상가 및 유흥업소가 밀집해 있다.</t>
+          <t xml:space="preserve">구의 중앙에 있는 동이다.
+영등포역 · 영등포우체국 · 영등포소방서 · 근로복지공사 · 한강성심병원 등 공공기관과 신세계 · 롯데 · 경방필백화점을 비롯한 많은 영등포시장 · 남서울시장 등 재래시장과 상가 및 유흥업소가 밀집해 있다.</t>
         </is>
       </c>
     </row>
@@ -18960,8 +18849,7 @@
       </c>
       <c r="L250" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 중앙에 있는 동이다.
-동쪽은 여의도동 · 신길동, 서쪽은 당산동 · 문래동, 남쪽은 신길동 · 도림동, 북쪽은 당산동과 접해 있다.
+          <t xml:space="preserve">동쪽은 여의도동 · 신길동, 서쪽은 당산동 · 문래동, 남쪽은 신길동 · 도림동, 북쪽은 당산동과 접해 있다.
 동명의 유래는 정확히 알 수 없으나, 인근 신길동의 방아곶이나루와 연관하여 영등굿이 행해지던 갯마을(포구)이었던 것과 관련된 것으로 추정된다.
 경기도 금천현(衿川縣) 하북면에 속하였다가, 1914년 시흥군 하북면 하방하관리(下方下串里)와 중종리(重宗里)를 합쳐 북면 영등포리로 불리었고 1920년에 영등포면이 되었다.
 1931년 읍으로 승격되었으며, 1936년 경성부에 편입되면서 영등포정이 되었다가 1943년 구제가 실시되어 영등포구에 속하였고, 1946년 영등포동으로 바뀌었다.
@@ -18974,11 +18862,12 @@
         </is>
       </c>
       <c r="M250" s="0">
-        <v>723</v>
+        <v>708</v>
       </c>
       <c r="N250" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">영등포역 · 영등포우체국 · 영등포소방서 · 근로복지공사 · 한강성심병원 등 공공기관과 신세계 · 롯데 · 경방필백화점을 비롯한 많은 영등포시장 · 남서울시장 등 재래시장과 상가 및 유흥업소가 밀집해 있다.</t>
+          <t xml:space="preserve">구의 중앙에 있는 동이다.
+영등포역 · 영등포우체국 · 영등포소방서 · 근로복지공사 · 한강성심병원 등 공공기관과 신세계 · 롯데 · 경방필백화점을 비롯한 많은 영등포시장 · 남서울시장 등 재래시장과 상가 및 유흥업소가 밀집해 있다.</t>
         </is>
       </c>
     </row>
@@ -19041,8 +18930,7 @@
       </c>
       <c r="L251" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 중앙에 있는 동이다.
-동쪽은 여의도동 · 신길동, 서쪽은 당산동 · 문래동, 남쪽은 신길동 · 도림동, 북쪽은 당산동과 접해 있다.
+          <t xml:space="preserve">동쪽은 여의도동 · 신길동, 서쪽은 당산동 · 문래동, 남쪽은 신길동 · 도림동, 북쪽은 당산동과 접해 있다.
 동명의 유래는 정확히 알 수 없으나, 인근 신길동의 방아곶이나루와 연관하여 영등굿이 행해지던 갯마을(포구)이었던 것과 관련된 것으로 추정된다.
 경기도 금천현(衿川縣) 하북면에 속하였다가, 1914년 시흥군 하북면 하방하관리(下方下串里)와 중종리(重宗里)를 합쳐 북면 영등포리로 불리었고 1920년에 영등포면이 되었다.
 1931년 읍으로 승격되었으며, 1936년 경성부에 편입되면서 영등포정이 되었다가 1943년 구제가 실시되어 영등포구에 속하였고, 1946년 영등포동으로 바뀌었다.
@@ -19055,11 +18943,12 @@
         </is>
       </c>
       <c r="M251" s="0">
-        <v>723</v>
+        <v>708</v>
       </c>
       <c r="N251" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">영등포역 · 영등포우체국 · 영등포소방서 · 근로복지공사 · 한강성심병원 등 공공기관과 신세계 · 롯데 · 경방필백화점을 비롯한 많은 영등포시장 · 남서울시장 등 재래시장과 상가 및 유흥업소가 밀집해 있다.</t>
+          <t xml:space="preserve">구의 중앙에 있는 동이다.
+영등포역 · 영등포우체국 · 영등포소방서 · 근로복지공사 · 한강성심병원 등 공공기관과 신세계 · 롯데 · 경방필백화점을 비롯한 많은 영등포시장 · 남서울시장 등 재래시장과 상가 및 유흥업소가 밀집해 있다.</t>
         </is>
       </c>
     </row>
@@ -19122,8 +19011,7 @@
       </c>
       <c r="L252" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 중앙에 있는 동이다.
-동쪽은 여의도동 · 신길동, 서쪽은 당산동 · 문래동, 남쪽은 신길동 · 도림동, 북쪽은 당산동과 접해 있다.
+          <t xml:space="preserve">동쪽은 여의도동 · 신길동, 서쪽은 당산동 · 문래동, 남쪽은 신길동 · 도림동, 북쪽은 당산동과 접해 있다.
 동명의 유래는 정확히 알 수 없으나, 인근 신길동의 방아곶이나루와 연관하여 영등굿이 행해지던 갯마을(포구)이었던 것과 관련된 것으로 추정된다.
 경기도 금천현(衿川縣) 하북면에 속하였다가, 1914년 시흥군 하북면 하방하관리(下方下串里)와 중종리(重宗里)를 합쳐 북면 영등포리로 불리었고 1920년에 영등포면이 되었다.
 1931년 읍으로 승격되었으며, 1936년 경성부에 편입되면서 영등포정이 되었다가 1943년 구제가 실시되어 영등포구에 속하였고, 1946년 영등포동으로 바뀌었다.
@@ -19136,11 +19024,12 @@
         </is>
       </c>
       <c r="M252" s="0">
-        <v>723</v>
+        <v>708</v>
       </c>
       <c r="N252" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">영등포역 · 영등포우체국 · 영등포소방서 · 근로복지공사 · 한강성심병원 등 공공기관과 신세계 · 롯데 · 경방필백화점을 비롯한 많은 영등포시장 · 남서울시장 등 재래시장과 상가 및 유흥업소가 밀집해 있다.</t>
+          <t xml:space="preserve">구의 중앙에 있는 동이다.
+영등포역 · 영등포우체국 · 영등포소방서 · 근로복지공사 · 한강성심병원 등 공공기관과 신세계 · 롯데 · 경방필백화점을 비롯한 많은 영등포시장 · 남서울시장 등 재래시장과 상가 및 유흥업소가 밀집해 있다.</t>
         </is>
       </c>
     </row>
@@ -19203,8 +19092,7 @@
       </c>
       <c r="L253" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 중앙에 있는 동이다.
-동쪽은 여의도동 · 신길동, 서쪽은 당산동 · 문래동, 남쪽은 신길동 · 도림동, 북쪽은 당산동과 접해 있다.
+          <t xml:space="preserve">동쪽은 여의도동 · 신길동, 서쪽은 당산동 · 문래동, 남쪽은 신길동 · 도림동, 북쪽은 당산동과 접해 있다.
 동명의 유래는 정확히 알 수 없으나, 인근 신길동의 방아곶이나루와 연관하여 영등굿이 행해지던 갯마을(포구)이었던 것과 관련된 것으로 추정된다.
 경기도 금천현(衿川縣) 하북면에 속하였다가, 1914년 시흥군 하북면 하방하관리(下方下串里)와 중종리(重宗里)를 합쳐 북면 영등포리로 불리었고 1920년에 영등포면이 되었다.
 1931년 읍으로 승격되었으며, 1936년 경성부에 편입되면서 영등포정이 되었다가 1943년 구제가 실시되어 영등포구에 속하였고, 1946년 영등포동으로 바뀌었다.
@@ -19217,11 +19105,12 @@
         </is>
       </c>
       <c r="M253" s="0">
-        <v>723</v>
+        <v>708</v>
       </c>
       <c r="N253" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">영등포역 · 영등포우체국 · 영등포소방서 · 근로복지공사 · 한강성심병원 등 공공기관과 신세계 · 롯데 · 경방필백화점을 비롯한 많은 영등포시장 · 남서울시장 등 재래시장과 상가 및 유흥업소가 밀집해 있다.</t>
+          <t xml:space="preserve">구의 중앙에 있는 동이다.
+영등포역 · 영등포우체국 · 영등포소방서 · 근로복지공사 · 한강성심병원 등 공공기관과 신세계 · 롯데 · 경방필백화점을 비롯한 많은 영등포시장 · 남서울시장 등 재래시장과 상가 및 유흥업소가 밀집해 있다.</t>
         </is>
       </c>
     </row>
@@ -19284,8 +19173,7 @@
       </c>
       <c r="L254" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 중앙에 있는 동이다.
-동쪽은 여의도동 · 신길동, 서쪽은 당산동 · 문래동, 남쪽은 신길동 · 도림동, 북쪽은 당산동과 접해 있다.
+          <t xml:space="preserve">동쪽은 여의도동 · 신길동, 서쪽은 당산동 · 문래동, 남쪽은 신길동 · 도림동, 북쪽은 당산동과 접해 있다.
 동명의 유래는 정확히 알 수 없으나, 인근 신길동의 방아곶이나루와 연관하여 영등굿이 행해지던 갯마을(포구)이었던 것과 관련된 것으로 추정된다.
 경기도 금천현(衿川縣) 하북면에 속하였다가, 1914년 시흥군 하북면 하방하관리(下方下串里)와 중종리(重宗里)를 합쳐 북면 영등포리로 불리었고 1920년에 영등포면이 되었다.
 1931년 읍으로 승격되었으며, 1936년 경성부에 편입되면서 영등포정이 되었다가 1943년 구제가 실시되어 영등포구에 속하였고, 1946년 영등포동으로 바뀌었다.
@@ -19298,11 +19186,12 @@
         </is>
       </c>
       <c r="M254" s="0">
-        <v>723</v>
+        <v>708</v>
       </c>
       <c r="N254" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">영등포역 · 영등포우체국 · 영등포소방서 · 근로복지공사 · 한강성심병원 등 공공기관과 신세계 · 롯데 · 경방필백화점을 비롯한 많은 영등포시장 · 남서울시장 등 재래시장과 상가 및 유흥업소가 밀집해 있다.</t>
+          <t xml:space="preserve">구의 중앙에 있는 동이다.
+영등포역 · 영등포우체국 · 영등포소방서 · 근로복지공사 · 한강성심병원 등 공공기관과 신세계 · 롯데 · 경방필백화점을 비롯한 많은 영등포시장 · 남서울시장 등 재래시장과 상가 및 유흥업소가 밀집해 있다.</t>
         </is>
       </c>
     </row>
@@ -19439,8 +19328,7 @@
       </c>
       <c r="L256" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 중앙에 있는 동이다.
-동쪽은 용산동1가, 서쪽은 청파동3가 · 원효로1가, 남쪽은 한강로1가 · 용산동1가, 북쪽은 갈월동 · 후암동과 접해 있다.
+          <t xml:space="preserve">동쪽은 용산동1가, 서쪽은 청파동3가 · 원효로1가, 남쪽은 한강로1가 · 용산동1가, 북쪽은 갈월동 · 후암동과 접해 있다.
 동명은 서울의 남쪽인 이곳에 군영이 있었다 하여 유래되었다.
 조선시대 성저십리 지역으로, 1751년(영조 27)에 한성부 남부 둔지방 이태원계의 일부였다.
 1914년 경성부 한강통(漢江通)이 되었다가, 1941년에 연병정(練兵町)으로 되었다.
@@ -19450,11 +19338,12 @@
         </is>
       </c>
       <c r="M256" s="0">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="N256" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">남영동은 갈월동 · 동자동 · 용산동1가와 더불어 남영동사무소에서 행정을 관할하고 있다.</t>
+          <t xml:space="preserve">구의 중앙에 있는 동이다.
+남영동은 갈월동 · 동자동 · 용산동1가와 더불어 남영동사무소에서 행정을 관할하고 있다.</t>
         </is>
       </c>
     </row>
@@ -19814,8 +19703,7 @@
       </c>
       <c r="L261" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">용산구의 남쪽에 있는 동이다.
-동쪽은 한남동, 서쪽은 동빙고동, 북쪽은 한남동 · 이태원동, 남쪽은 주성동과 한강을 건너 서초구 반포동과 접해 있다.
+          <t xml:space="preserve">동쪽은 한남동, 서쪽은 동빙고동, 북쪽은 한남동 · 이태원동, 남쪽은 주성동과 한강을 건너 서초구 반포동과 접해 있다.
 동명은 신라 진흥왕 때 보광국사(普光國師)가 세운 절이 있었던 데서 유래되었다.
 조선시대 한성부 성저십리의 남부 한강방에 속하였다.
 1914년 고양군 한지면 보광리가 되었다가 1936년 경성부 보광정이 되었다.
@@ -19829,11 +19717,11 @@
         </is>
       </c>
       <c r="M261" s="0">
-        <v>569</v>
+        <v>552</v>
       </c>
       <c r="N261" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">용산구의 남쪽에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -20040,8 +19928,7 @@
       </c>
       <c r="L264" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">용산구의 남쪽에 있는 동이다.
-동쪽은 동빙고동, 서쪽은 이촌동, 북쪽은 용산동6가, 남쪽은 한강을 건너 서초구 반포동과 접해 있다.
+          <t xml:space="preserve">동쪽은 동빙고동, 서쪽은 이촌동, 북쪽은 용산동6가, 남쪽은 한강을 건너 서초구 반포동과 접해 있다.
 동명은 조선시대에 얼음을 저장하는 창고가 한강변에 두 군데 있었는데, 그 중 서쪽에 위치하여 궁중음식이나 관리에게 나누어주던 빙고가 있었던 데서 유래되었다.
 조선시대 한성부 성저십리의 남부 둔지방 서빙고1계였다.
 1914년 경기도 고양군 한지면 서빙고리로 되었다가 1936년 경성부 서빙고정이 되었다.
@@ -20052,11 +19939,12 @@
         </is>
       </c>
       <c r="M264" s="0">
-        <v>432</v>
+        <v>415</v>
       </c>
       <c r="N264" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">서빙고동사무소에서 서빙고동 · 주성동(鑄城洞) · 동빙고동(東氷庫洞) · 용산동6가의 행정을 관할하고 있다.
+          <t xml:space="preserve">용산구의 남쪽에 있는 동이다.
+서빙고동사무소에서 서빙고동 · 주성동(鑄城洞) · 동빙고동(東氷庫洞) · 용산동6가의 행정을 관할하고 있다.
 서빙고동은 신동아아파트가 대부분의 면적을 차지하며, 강변북로 · 서빙고로가 지나고 경원선 서빙고역이 있다.</t>
         </is>
       </c>
@@ -20118,8 +20006,7 @@
       </c>
       <c r="L265" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 서쪽에 있는 동이다.
-북쪽은 문배동, 서쪽은 원효로2~3가, 남쪽은 한강로3가와 접해 있다.
+          <t xml:space="preserve">북쪽은 문배동, 서쪽은 원효로2~3가, 남쪽은 한강로3가와 접해 있다.
 조선시대 한성부 성저십리의 서부 용산방 동문외계 지역이었다.
 1910년 10월 경성부 용산면(龍山面) 관할 지역이 되었다가, 1914년 영정(榮町)이 되었고, 1943년 용산구에 속하였다가, 1946년 신계동이 되었다.
 동명은 광복 후 새로 사람들이 살게 되어 생긴 동네라는 데서 유래되었다.
@@ -20129,11 +20016,11 @@
         </is>
       </c>
       <c r="M265" s="0">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="N265" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 서쪽에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -20269,8 +20156,7 @@
       </c>
       <c r="L267" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 서쪽에 있는 동이다.
-동쪽과 남쪽은 원효로동, 서쪽은 도원동, 북쪽은 효창동과 접해 있다.
+          <t xml:space="preserve">동쪽과 남쪽은 원효로동, 서쪽은 도원동, 북쪽은 효창동과 접해 있다.
 동명은 용산의 ‘용’ 자와 옛 지명인 동문외계(東門外契)의 ‘문’ 자를 붙인 데서 유래되었다.
 조선시대 한성부 성저십리의 서부 용산방 동문외계 지역이었다.
 1914년 경성부 대도정(大島町)으로 되었고, 1943년 용산구에 편입되었으며, 1946년 용문동으로 바뀌었다.
@@ -20280,11 +20166,11 @@
         </is>
       </c>
       <c r="M267" s="0">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="N267" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 서쪽에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -20346,8 +20232,7 @@
       </c>
       <c r="L268" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 중앙에 있는 1~6가의 동으로 용산동의 법정동은 1가에서 6가로 나뉘어져 있다.
-한강로와 반포로 사이에 위치하여 동쪽은 이태원동, 서쪽은 한강로동, 남쪽은 서빙고동, 북쪽은 후암동과 중구 예장동 · 장충동과 접해 있다.
+          <t xml:space="preserve">한강로와 반포로 사이에 위치하여 동쪽은 이태원동, 서쪽은 한강로동, 남쪽은 서빙고동, 북쪽은 후암동과 중구 예장동 · 장충동과 접해 있다.
 동명은 한강로 서쪽 마포구와 경계를 이루는 산줄기가 용 모습을 하고 있어 유래되었다.
 조선시대 한성부 성저십리 지역이었고, 1751년(영조 27)에 한성부 남부 둔지방에 속하였으며 일제 때 경성부 한강통(漢江通), 고양군 한지면(漢芝面) 지역이 되었다가 1941년 용산정1~6정목이 되었다.
 1943년 용산구에 편입되었고, 1946년 용산동으로 바뀌어 1가에서 6가로 분할되었다.
@@ -20360,11 +20245,11 @@
         </is>
       </c>
       <c r="M268" s="0">
-        <v>733</v>
+        <v>685</v>
       </c>
       <c r="N268" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 중앙에 있는 1~6가의 동으로 용산동의 법정동은 1가에서 6가로 나뉘어져 있다.</t>
         </is>
       </c>
     </row>
@@ -20426,8 +20311,7 @@
       </c>
       <c r="L269" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 중앙에 있는 1~6가의 동으로 용산동의 법정동은 1가에서 6가로 나뉘어져 있다.
-한강로와 반포로 사이에 위치하여 동쪽은 이태원동, 서쪽은 한강로동, 남쪽은 서빙고동, 북쪽은 후암동과 중구 예장동 · 장충동과 접해 있다.
+          <t xml:space="preserve">한강로와 반포로 사이에 위치하여 동쪽은 이태원동, 서쪽은 한강로동, 남쪽은 서빙고동, 북쪽은 후암동과 중구 예장동 · 장충동과 접해 있다.
 동명은 한강로 서쪽 마포구와 경계를 이루는 산줄기가 용 모습을 하고 있어 유래되었다.
 조선시대 한성부 성저십리 지역이었고, 1751년(영조 27)에 한성부 남부 둔지방에 속하였으며 일제 때 경성부 한강통(漢江通), 고양군 한지면(漢芝面) 지역이 되었다가 1941년 용산정1~6정목이 되었다.
 1943년 용산구에 편입되었고, 1946년 용산동으로 바뀌어 1가에서 6가로 분할되었다.
@@ -20440,11 +20324,11 @@
         </is>
       </c>
       <c r="M269" s="0">
-        <v>733</v>
+        <v>685</v>
       </c>
       <c r="N269" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 중앙에 있는 1~6가의 동으로 용산동의 법정동은 1가에서 6가로 나뉘어져 있다.</t>
         </is>
       </c>
     </row>
@@ -20506,8 +20390,7 @@
       </c>
       <c r="L270" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 중앙에 있는 1~6가의 동으로 용산동의 법정동은 1가에서 6가로 나뉘어져 있다.
-한강로와 반포로 사이에 위치하여 동쪽은 이태원동, 서쪽은 한강로동, 남쪽은 서빙고동, 북쪽은 후암동과 중구 예장동 · 장충동과 접해 있다.
+          <t xml:space="preserve">한강로와 반포로 사이에 위치하여 동쪽은 이태원동, 서쪽은 한강로동, 남쪽은 서빙고동, 북쪽은 후암동과 중구 예장동 · 장충동과 접해 있다.
 동명은 한강로 서쪽 마포구와 경계를 이루는 산줄기가 용 모습을 하고 있어 유래되었다.
 조선시대 한성부 성저십리 지역이었고, 1751년(영조 27)에 한성부 남부 둔지방에 속하였으며 일제 때 경성부 한강통(漢江通), 고양군 한지면(漢芝面) 지역이 되었다가 1941년 용산정1~6정목이 되었다.
 1943년 용산구에 편입되었고, 1946년 용산동으로 바뀌어 1가에서 6가로 분할되었다.
@@ -20520,11 +20403,11 @@
         </is>
       </c>
       <c r="M270" s="0">
-        <v>733</v>
+        <v>685</v>
       </c>
       <c r="N270" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 중앙에 있는 1~6가의 동으로 용산동의 법정동은 1가에서 6가로 나뉘어져 있다.</t>
         </is>
       </c>
     </row>
@@ -20586,8 +20469,7 @@
       </c>
       <c r="L271" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 중앙에 있는 1~6가의 동으로 용산동의 법정동은 1가에서 6가로 나뉘어져 있다.
-한강로와 반포로 사이에 위치하여 동쪽은 이태원동, 서쪽은 한강로동, 남쪽은 서빙고동, 북쪽은 후암동과 중구 예장동 · 장충동과 접해 있다.
+          <t xml:space="preserve">한강로와 반포로 사이에 위치하여 동쪽은 이태원동, 서쪽은 한강로동, 남쪽은 서빙고동, 북쪽은 후암동과 중구 예장동 · 장충동과 접해 있다.
 동명은 한강로 서쪽 마포구와 경계를 이루는 산줄기가 용 모습을 하고 있어 유래되었다.
 조선시대 한성부 성저십리 지역이었고, 1751년(영조 27)에 한성부 남부 둔지방에 속하였으며 일제 때 경성부 한강통(漢江通), 고양군 한지면(漢芝面) 지역이 되었다가 1941년 용산정1~6정목이 되었다.
 1943년 용산구에 편입되었고, 1946년 용산동으로 바뀌어 1가에서 6가로 분할되었다.
@@ -20600,11 +20482,11 @@
         </is>
       </c>
       <c r="M271" s="0">
-        <v>733</v>
+        <v>685</v>
       </c>
       <c r="N271" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 중앙에 있는 1~6가의 동으로 용산동의 법정동은 1가에서 6가로 나뉘어져 있다.</t>
         </is>
       </c>
     </row>
@@ -20666,8 +20548,7 @@
       </c>
       <c r="L272" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 중앙에 있는 1~6가의 동으로 용산동의 법정동은 1가에서 6가로 나뉘어져 있다.
-한강로와 반포로 사이에 위치하여 동쪽은 이태원동, 서쪽은 한강로동, 남쪽은 서빙고동, 북쪽은 후암동과 중구 예장동 · 장충동과 접해 있다.
+          <t xml:space="preserve">한강로와 반포로 사이에 위치하여 동쪽은 이태원동, 서쪽은 한강로동, 남쪽은 서빙고동, 북쪽은 후암동과 중구 예장동 · 장충동과 접해 있다.
 동명은 한강로 서쪽 마포구와 경계를 이루는 산줄기가 용 모습을 하고 있어 유래되었다.
 조선시대 한성부 성저십리 지역이었고, 1751년(영조 27)에 한성부 남부 둔지방에 속하였으며 일제 때 경성부 한강통(漢江通), 고양군 한지면(漢芝面) 지역이 되었다가 1941년 용산정1~6정목이 되었다.
 1943년 용산구에 편입되었고, 1946년 용산동으로 바뀌어 1가에서 6가로 분할되었다.
@@ -20680,11 +20561,11 @@
         </is>
       </c>
       <c r="M272" s="0">
-        <v>733</v>
+        <v>685</v>
       </c>
       <c r="N272" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 중앙에 있는 1~6가의 동으로 용산동의 법정동은 1가에서 6가로 나뉘어져 있다.</t>
         </is>
       </c>
     </row>
@@ -20746,8 +20627,7 @@
       </c>
       <c r="L273" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 중앙에 있는 1~6가의 동으로 용산동의 법정동은 1가에서 6가로 나뉘어져 있다.
-한강로와 반포로 사이에 위치하여 동쪽은 이태원동, 서쪽은 한강로동, 남쪽은 서빙고동, 북쪽은 후암동과 중구 예장동 · 장충동과 접해 있다.
+          <t xml:space="preserve">한강로와 반포로 사이에 위치하여 동쪽은 이태원동, 서쪽은 한강로동, 남쪽은 서빙고동, 북쪽은 후암동과 중구 예장동 · 장충동과 접해 있다.
 동명은 한강로 서쪽 마포구와 경계를 이루는 산줄기가 용 모습을 하고 있어 유래되었다.
 조선시대 한성부 성저십리 지역이었고, 1751년(영조 27)에 한성부 남부 둔지방에 속하였으며 일제 때 경성부 한강통(漢江通), 고양군 한지면(漢芝面) 지역이 되었다가 1941년 용산정1~6정목이 되었다.
 1943년 용산구에 편입되었고, 1946년 용산동으로 바뀌어 1가에서 6가로 분할되었다.
@@ -20760,11 +20640,11 @@
         </is>
       </c>
       <c r="M273" s="0">
-        <v>733</v>
+        <v>685</v>
       </c>
       <c r="N273" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 중앙에 있는 1~6가의 동으로 용산동의 법정동은 1가에서 6가로 나뉘어져 있다.</t>
         </is>
       </c>
     </row>
@@ -20826,8 +20706,7 @@
       </c>
       <c r="L274" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 서쪽에 있는 1~4가의 동이다.
-원효로를 중심으로 좌우로 길게 형성되었으며, 남쪽은 한강 건너 영등포구 여의도동, 동쪽은 한강로, 서쪽은 청파동 · 효창동 · 용문동 · 신창동 · 산천동 · 창암동, 북쪽은 남영동과 접해 있다.
+          <t xml:space="preserve">원효로를 중심으로 좌우로 길게 형성되었으며, 남쪽은 한강 건너 영등포구 여의도동, 동쪽은 한강로, 서쪽은 청파동 · 효창동 · 용문동 · 신창동 · 산천동 · 창암동, 북쪽은 남영동과 접해 있다.
 동명은 광복 직후 일제식 명칭을 고치고 우리 성현의 이름을 붙이면서 신라의 승려 원효대사(元曉大師)의 법호를 붙인 것이다.
 조선시대 한성부 성저십리(城底十里)지역이었고, 1911년에는 경기도 용산면에 속하였다가, 1914년 경성부 원정1·2·3·4정목이 되었고, 1946년 원효로1·2·3·4가로 바뀌었다.
 원효로1가에는 용산경찰서가 있으며, 원효로3가에는 조선시대 군자감(軍資監)의 강감(江監)이 있었다.
@@ -20837,11 +20716,12 @@
         </is>
       </c>
       <c r="M274" s="0">
-        <v>532</v>
+        <v>511</v>
       </c>
       <c r="N274" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">체신공무원교육원, 한국통신품질보증단, 용산전자상가가 있다.</t>
+          <t xml:space="preserve">구의 서쪽에 있는 1~4가의 동이다.
+체신공무원교육원, 한국통신품질보증단, 용산전자상가가 있다.</t>
         </is>
       </c>
     </row>
@@ -20903,8 +20783,7 @@
       </c>
       <c r="L275" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 서쪽에 있는 1~4가의 동이다.
-원효로를 중심으로 좌우로 길게 형성되었으며, 남쪽은 한강 건너 영등포구 여의도동, 동쪽은 한강로, 서쪽은 청파동 · 효창동 · 용문동 · 신창동 · 산천동 · 창암동, 북쪽은 남영동과 접해 있다.
+          <t xml:space="preserve">원효로를 중심으로 좌우로 길게 형성되었으며, 남쪽은 한강 건너 영등포구 여의도동, 동쪽은 한강로, 서쪽은 청파동 · 효창동 · 용문동 · 신창동 · 산천동 · 창암동, 북쪽은 남영동과 접해 있다.
 동명은 광복 직후 일제식 명칭을 고치고 우리 성현의 이름을 붙이면서 신라의 승려 원효대사(元曉大師)의 법호를 붙인 것이다.
 조선시대 한성부 성저십리(城底十里)지역이었고, 1911년에는 경기도 용산면에 속하였다가, 1914년 경성부 원정1·2·3·4정목이 되었고, 1946년 원효로1·2·3·4가로 바뀌었다.
 원효로1가에는 용산경찰서가 있으며, 원효로3가에는 조선시대 군자감(軍資監)의 강감(江監)이 있었다.
@@ -20914,11 +20793,12 @@
         </is>
       </c>
       <c r="M275" s="0">
-        <v>532</v>
+        <v>511</v>
       </c>
       <c r="N275" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">체신공무원교육원, 한국통신품질보증단, 용산전자상가가 있다.</t>
+          <t xml:space="preserve">구의 서쪽에 있는 1~4가의 동이다.
+체신공무원교육원, 한국통신품질보증단, 용산전자상가가 있다.</t>
         </is>
       </c>
     </row>
@@ -20980,8 +20860,7 @@
       </c>
       <c r="L276" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 서쪽에 있는 1~4가의 동이다.
-원효로를 중심으로 좌우로 길게 형성되었으며, 남쪽은 한강 건너 영등포구 여의도동, 동쪽은 한강로, 서쪽은 청파동 · 효창동 · 용문동 · 신창동 · 산천동 · 창암동, 북쪽은 남영동과 접해 있다.
+          <t xml:space="preserve">원효로를 중심으로 좌우로 길게 형성되었으며, 남쪽은 한강 건너 영등포구 여의도동, 동쪽은 한강로, 서쪽은 청파동 · 효창동 · 용문동 · 신창동 · 산천동 · 창암동, 북쪽은 남영동과 접해 있다.
 동명은 광복 직후 일제식 명칭을 고치고 우리 성현의 이름을 붙이면서 신라의 승려 원효대사(元曉大師)의 법호를 붙인 것이다.
 조선시대 한성부 성저십리(城底十里)지역이었고, 1911년에는 경기도 용산면에 속하였다가, 1914년 경성부 원정1·2·3·4정목이 되었고, 1946년 원효로1·2·3·4가로 바뀌었다.
 원효로1가에는 용산경찰서가 있으며, 원효로3가에는 조선시대 군자감(軍資監)의 강감(江監)이 있었다.
@@ -20991,11 +20870,12 @@
         </is>
       </c>
       <c r="M276" s="0">
-        <v>532</v>
+        <v>511</v>
       </c>
       <c r="N276" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">체신공무원교육원, 한국통신품질보증단, 용산전자상가가 있다.</t>
+          <t xml:space="preserve">구의 서쪽에 있는 1~4가의 동이다.
+체신공무원교육원, 한국통신품질보증단, 용산전자상가가 있다.</t>
         </is>
       </c>
     </row>
@@ -21057,8 +20937,7 @@
       </c>
       <c r="L277" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 서쪽에 있는 1~4가의 동이다.
-원효로를 중심으로 좌우로 길게 형성되었으며, 남쪽은 한강 건너 영등포구 여의도동, 동쪽은 한강로, 서쪽은 청파동 · 효창동 · 용문동 · 신창동 · 산천동 · 창암동, 북쪽은 남영동과 접해 있다.
+          <t xml:space="preserve">원효로를 중심으로 좌우로 길게 형성되었으며, 남쪽은 한강 건너 영등포구 여의도동, 동쪽은 한강로, 서쪽은 청파동 · 효창동 · 용문동 · 신창동 · 산천동 · 창암동, 북쪽은 남영동과 접해 있다.
 동명은 광복 직후 일제식 명칭을 고치고 우리 성현의 이름을 붙이면서 신라의 승려 원효대사(元曉大師)의 법호를 붙인 것이다.
 조선시대 한성부 성저십리(城底十里)지역이었고, 1911년에는 경기도 용산면에 속하였다가, 1914년 경성부 원정1·2·3·4정목이 되었고, 1946년 원효로1·2·3·4가로 바뀌었다.
 원효로1가에는 용산경찰서가 있으며, 원효로3가에는 조선시대 군자감(軍資監)의 강감(江監)이 있었다.
@@ -21068,11 +20947,12 @@
         </is>
       </c>
       <c r="M277" s="0">
-        <v>532</v>
+        <v>511</v>
       </c>
       <c r="N277" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">체신공무원교육원, 한국통신품질보증단, 용산전자상가가 있다.</t>
+          <t xml:space="preserve">구의 서쪽에 있는 1~4가의 동이다.
+체신공무원교육원, 한국통신품질보증단, 용산전자상가가 있다.</t>
         </is>
       </c>
     </row>
@@ -21135,8 +21015,7 @@
       </c>
       <c r="L278" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">용산구의 서남쪽에 있는 동이다.
-한강대교 북쪽 한강변에 있으며, 동쪽은 서빙고동, 서쪽은 원효로4가, 북쪽은 용산동5가 · 한강로3가동, 남쪽은 한강을 건너 동작구 노량진동 · 본동에 접해 있다.
+          <t xml:space="preserve">한강대교 북쪽 한강변에 있으며, 동쪽은 서빙고동, 서쪽은 원효로4가, 북쪽은 용산동5가 · 한강로3가동, 남쪽은 한강을 건너 동작구 노량진동 · 본동에 접해 있다.
 동명은 이 지역이 모래벌판이어서 여름에 장마가 지면 홍수를 피해 강변으로 옮겨가 살았으므로 마을을 떠난다는 의미의 이촌동(移村洞)으로 불리다가 한자가 변하여 이촌동(二村洞)이 되었다.
 조선시대 한성부 성저십리의 서부 용산방 사촌리계(沙村里契) · 신촌리계(新村里契) 지역이었다.
 1910년 10월 경성부 용산면(龍山面) 관할 지역이 되었다가, 1914년 이촌동, 1936년 이촌정이 되었고, 1943년 용산구에 속하였다가, 1946년에 이촌동으로 바뀌었다.
@@ -21149,11 +21028,12 @@
         </is>
       </c>
       <c r="M278" s="0">
-        <v>650</v>
+        <v>632</v>
       </c>
       <c r="N278" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">이촌제1동 지역을 동부이촌동이라 하는데, 이촌동길과 서빙고로가 동서로 지나고, 경원선 국철 이촌역과 지하철 4호선 이촌역이 있어 교통이 편리하다.</t>
+          <t xml:space="preserve">용산구의 서남쪽에 있는 동이다.
+이촌제1동 지역을 동부이촌동이라 하는데, 이촌동길과 서빙고로가 동서로 지나고, 경원선 국철 이촌역과 지하철 4호선 이촌역이 있어 교통이 편리하다.</t>
         </is>
       </c>
     </row>
@@ -21216,8 +21096,7 @@
       </c>
       <c r="L279" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">용산구의 중앙에 있는 동이다.
-동쪽은 한남동, 서쪽은 용산동2가, 남쪽은 동빙고동 · 보광동, 북쪽은 남산 능선을 경계로 중구 장충동2가와 접한다.
+          <t xml:space="preserve">동쪽은 한남동, 서쪽은 용산동2가, 남쪽은 동빙고동 · 보광동, 북쪽은 남산 능선을 경계로 중구 장충동2가와 접한다.
 동명은 조선시대 이곳에 있던 역원(驛院)인 이태원(梨泰院)에서 유래되었다.
 조선시대 한성부 성저십리의 남부 둔지방 이태원계였다.
 1914년 경기도 고양군 한지면 이태원리가 되었다가 1936년 경성부 이태원정이 되었다.
@@ -21230,11 +21109,12 @@
         </is>
       </c>
       <c r="M279" s="0">
-        <v>553</v>
+        <v>536</v>
       </c>
       <c r="N279" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">한국전쟁 후 미군이 용산 일대에 주둔하고 외국 공관이 많이 들어서면서 값싼 제품을 살 수 있는 2,000여 개의 상가로 구성된 쇼핑거리가 형성되었다.</t>
+          <t xml:space="preserve">용산구의 중앙에 있는 동이다.
+한국전쟁 후 미군이 용산 일대에 주둔하고 외국 공관이 많이 들어서면서 값싼 제품을 살 수 있는 2,000여 개의 상가로 구성된 쇼핑거리가 형성되었다.</t>
         </is>
       </c>
     </row>
@@ -21445,8 +21325,7 @@
       </c>
       <c r="L282" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 서쪽에 있는 1~3가의 동이다.
-동쪽은 경부선 철도를 경계로 동자동 · 갈월동 · 남영동, 서쪽은 효창동과 마포구 공덕동, 남쪽은 원효로1가, 북쪽의 서계동과 접해 있다.
+          <t xml:space="preserve">동쪽은 경부선 철도를 경계로 동자동 · 갈월동 · 남영동, 서쪽은 효창동과 마포구 공덕동, 남쪽은 원효로1가, 북쪽의 서계동과 접해 있다.
 동명은 용산 줄기를 따라 푸른 언덕이 많았기 때문이라는 것과 또 서울과 삼남 지방을 잇는 청파역이 있어 유래되었다는 설이 있다.
 배문중 · 고등학교가 자리한 지역에 연화봉(蓮花峰) · 목동산(牧童山) 등 작은 구릉과 옻나무골 등의 지명이 있어 청파의 동명을 연상할 수 있다.
 조선시대 한성부 성저십리에 속한 서부 용산방 청파계였다.
@@ -21456,11 +21335,12 @@
         </is>
       </c>
       <c r="M282" s="0">
-        <v>496</v>
+        <v>475</v>
       </c>
       <c r="N282" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">청파1동사무소에서 청파동1가와 서계동을, 청파2동사무소에서 청파동2·3가를 관할하고 있다.
+          <t xml:space="preserve">구의 서쪽에 있는 1~3가의 동이다.
+청파1동사무소에서 청파동1가와 서계동을, 청파2동사무소에서 청파동2·3가를 관할하고 있다.
 청파로와 경부선 · 한강로 등과 이어져 지하철 1·4호선의 남영역 · 숙대입구역이 설치되어 교통이 편리하다.</t>
         </is>
       </c>
@@ -21523,8 +21403,7 @@
       </c>
       <c r="L283" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 서쪽에 있는 1~3가의 동이다.
-동쪽은 경부선 철도를 경계로 동자동 · 갈월동 · 남영동, 서쪽은 효창동과 마포구 공덕동, 남쪽은 원효로1가, 북쪽의 서계동과 접해 있다.
+          <t xml:space="preserve">동쪽은 경부선 철도를 경계로 동자동 · 갈월동 · 남영동, 서쪽은 효창동과 마포구 공덕동, 남쪽은 원효로1가, 북쪽의 서계동과 접해 있다.
 동명은 용산 줄기를 따라 푸른 언덕이 많았기 때문이라는 것과 또 서울과 삼남 지방을 잇는 청파역이 있어 유래되었다는 설이 있다.
 배문중 · 고등학교가 자리한 지역에 연화봉(蓮花峰) · 목동산(牧童山) 등 작은 구릉과 옻나무골 등의 지명이 있어 청파의 동명을 연상할 수 있다.
 조선시대 한성부 성저십리에 속한 서부 용산방 청파계였다.
@@ -21534,11 +21413,12 @@
         </is>
       </c>
       <c r="M283" s="0">
-        <v>496</v>
+        <v>475</v>
       </c>
       <c r="N283" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">청파1동사무소에서 청파동1가와 서계동을, 청파2동사무소에서 청파동2·3가를 관할하고 있다.
+          <t xml:space="preserve">구의 서쪽에 있는 1~3가의 동이다.
+청파1동사무소에서 청파동1가와 서계동을, 청파2동사무소에서 청파동2·3가를 관할하고 있다.
 청파로와 경부선 · 한강로 등과 이어져 지하철 1·4호선의 남영역 · 숙대입구역이 설치되어 교통이 편리하다.</t>
         </is>
       </c>
@@ -21601,8 +21481,7 @@
       </c>
       <c r="L284" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 서쪽에 있는 1~3가의 동이다.
-동쪽은 경부선 철도를 경계로 동자동 · 갈월동 · 남영동, 서쪽은 효창동과 마포구 공덕동, 남쪽은 원효로1가, 북쪽의 서계동과 접해 있다.
+          <t xml:space="preserve">동쪽은 경부선 철도를 경계로 동자동 · 갈월동 · 남영동, 서쪽은 효창동과 마포구 공덕동, 남쪽은 원효로1가, 북쪽의 서계동과 접해 있다.
 동명은 용산 줄기를 따라 푸른 언덕이 많았기 때문이라는 것과 또 서울과 삼남 지방을 잇는 청파역이 있어 유래되었다는 설이 있다.
 배문중 · 고등학교가 자리한 지역에 연화봉(蓮花峰) · 목동산(牧童山) 등 작은 구릉과 옻나무골 등의 지명이 있어 청파의 동명을 연상할 수 있다.
 조선시대 한성부 성저십리에 속한 서부 용산방 청파계였다.
@@ -21612,11 +21491,12 @@
         </is>
       </c>
       <c r="M284" s="0">
-        <v>496</v>
+        <v>475</v>
       </c>
       <c r="N284" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">청파1동사무소에서 청파동1가와 서계동을, 청파2동사무소에서 청파동2·3가를 관할하고 있다.
+          <t xml:space="preserve">구의 서쪽에 있는 1~3가의 동이다.
+청파1동사무소에서 청파동1가와 서계동을, 청파2동사무소에서 청파동2·3가를 관할하고 있다.
 청파로와 경부선 · 한강로 등과 이어져 지하철 1·4호선의 남영역 · 숙대입구역이 설치되어 교통이 편리하다.</t>
         </is>
       </c>
@@ -21919,8 +21799,7 @@
       </c>
       <c r="L288" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">용산구의 동쪽에 있는 동이다.
-남산의 남동쪽 기슭에 있으며, 동쪽은 응봉 줄기를 따라 성동구 옥수동, 서쪽은 이태원동 · 보광동, 남쪽은 한강을 건너 강남구 신사동과 서초구 잠원동, 북쪽은 중구 장충동2가 · 신당동과 접해 있다.
+          <t xml:space="preserve">남산의 남동쪽 기슭에 있으며, 동쪽은 응봉 줄기를 따라 성동구 옥수동, 서쪽은 이태원동 · 보광동, 남쪽은 한강을 건너 강남구 신사동과 서초구 잠원동, 북쪽은 중구 장충동2가 · 신당동과 접해 있다.
 동명은 동의 경계가 되는 곳에 한강과 남산이 있어 한강의 ‘한’자와 남산의 ‘남’자를 따서 붙인 것이다.
 조선시대 한성부 성저십리의 남부 한강방 한강계였다.
 1914년 경기도 고양군 한지면 한강리(漢江里)에 속하였다가, 1936년 경성부 한남정(漢南町)이 되었다.
@@ -21933,11 +21812,12 @@
         </is>
       </c>
       <c r="M288" s="0">
-        <v>753</v>
+        <v>736</v>
       </c>
       <c r="N288" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">이태원로 · 소월길 · 독서당길 등이 지나고, 지하철 6호선이 지나 교통이 편리하다.</t>
+          <t xml:space="preserve">용산구의 동쪽에 있는 동이다.
+이태원로 · 소월길 · 독서당길 등이 지나고, 지하철 6호선이 지나 교통이 편리하다.</t>
         </is>
       </c>
     </row>
@@ -22000,8 +21880,7 @@
       </c>
       <c r="L289" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 서쪽에 있는 동이다.
-동쪽은 청파동, 서쪽의 마포구 신공덕동, 남쪽은 용문동, 북쪽의 공덕동과 접해 있으며, 동의 많은 부분이 효창공원으로 되어 있다.
+          <t xml:space="preserve">동쪽은 청파동, 서쪽의 마포구 신공덕동, 남쪽은 용문동, 북쪽의 공덕동과 접해 있으며, 동의 많은 부분이 효창공원으로 되어 있다.
 동명은 조선 정조의 문효세자(文孝世子)의 묘원(墓園)인 효창원(孝昌園)이 있었던 데서 유래되었다.
 조선시대 한성부 성저십리 용산방 만리창계 지역이었다.
 1914년 경성부 금정(錦町)이 되었다가 1943년 용산구에 편입되고, 1946년 효창동이 되었다.
@@ -22012,11 +21891,12 @@
         </is>
       </c>
       <c r="M289" s="0">
-        <v>522</v>
+        <v>507</v>
       </c>
       <c r="N289" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동의 남북으로 효창원길이 지나고, 남쪽으로는 백범로가 용산선과 평행하게 지나며, 지하철 6호선 효창공원앞역이 있어 교통이 편리하다.</t>
+          <t xml:space="preserve">구의 서쪽에 있는 동이다.
+동의 남북으로 효창원길이 지나고, 남쪽으로는 백범로가 용산선과 평행하게 지나며, 지하철 6호선 효창공원앞역이 있어 교통이 편리하다.</t>
         </is>
       </c>
     </row>
@@ -22078,8 +21958,7 @@
       </c>
       <c r="L290" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 북쪽에 있는 동이다.
-남산 정상의 서울성곽을 따라 중구와 경계를 이루며, 동쪽과 남쪽은 용산동2가, 서쪽은 동자동 · 갈월동과 접해 있다.
+          <t xml:space="preserve">남산 정상의 서울성곽을 따라 중구와 경계를 이루며, 동쪽과 남쪽은 용산동2가, 서쪽은 동자동 · 갈월동과 접해 있다.
 동명은 남산에 있는 두텁바위, 즉 둥글고 두터운 큰 바위가 있었던 데서 유래한다.
 조선시대 초기에는 한성부 성저십리 지역이었고, 1751년(영조 27)에 한성부 남부 둔지방 전생서내계 · 외계에 속하였다.
 1911년 경성부 한지면에 속하였고, 1914년 삼판통(三坂通)으로 되었다가 1943년 용산구에 편입되었다.
@@ -22093,11 +21972,11 @@
         </is>
       </c>
       <c r="M290" s="0">
-        <v>588</v>
+        <v>573</v>
       </c>
       <c r="N290" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 북쪽에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -22160,8 +22039,7 @@
       </c>
       <c r="L291" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 서쪽에 있는 동이다.
-동쪽은 박석고개를 사이에 두고 불광동, 남쪽은 구산동 · 대조동, 북쪽은 구파발동 · 진관외동, 서쪽은 봉산 능선을 경계로 경기도 고양시 용두동과 접해 있다.
+          <t xml:space="preserve">동쪽은 박석고개를 사이에 두고 불광동, 남쪽은 구산동 · 대조동, 북쪽은 구파발동 · 진관외동, 서쪽은 봉산 능선을 경계로 경기도 고양시 용두동과 접해 있다.
 동명은 이 일대에 칡이 많아서 칡고개 · 갈고개 · 가루게라 불렀던 것이 한자로 갈현이라 표현된 것이다.
 조선시대에는 한성부 성저십리 지역으로 북부 연은방 갈고개계(葛古介契) 또는 갈현계 지역이었다.
 1914년 경기도 고양군 은평면 갈현리에 속하였고, 1949년 서울특별시 서대문구에 편입되었다.
@@ -22171,11 +22049,12 @@
         </is>
       </c>
       <c r="M291" s="0">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="N291" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">갈현1동은 통일로와 연신내 전철역 주변 및 갈현시장을 중심으로 상권이 형성되었고, 갈현2동은 연서로 · 서오릉로 · 갈현동길에 접한 주거 및 상가지역으로 되어 있다.</t>
+          <t xml:space="preserve">구의 서쪽에 있는 동이다.
+갈현1동은 통일로와 연신내 전철역 주변 및 갈현시장을 중심으로 상권이 형성되었고, 갈현2동은 연서로 · 서오릉로 · 갈현동길에 접한 주거 및 상가지역으로 되어 있다.</t>
         </is>
       </c>
     </row>
@@ -22237,8 +22116,7 @@
       </c>
       <c r="L292" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 서쪽에 있는 동이다.
-동쪽과 남쪽은 역촌동, 북쪽은 갈현동, 서쪽의 봉산을 경계로 경기도 고양시 향동동과 접해 있다.
+          <t xml:space="preserve">동쪽과 남쪽은 역촌동, 북쪽은 갈현동, 서쪽의 봉산을 경계로 경기도 고양시 향동동과 접해 있다.
 동명은 고양시와 경계를 이루는 산세가 거북이 형상을 하고 있고, 산에 거북 받침의 인조별서유기비(仁祖別墅遺基碑)가 있는 데서 유래되었다.
 조선시대 한성부 성저십리 지역으로 북부 연은방 사계(私契) 지역이었다.
 1914년 노지동을 합하여 경기도 고양군 은평면 구산리라 하였고, 1949년 서대문구에 편입되었다.
@@ -22249,11 +22127,11 @@
         </is>
       </c>
       <c r="M292" s="0">
-        <v>472</v>
+        <v>457</v>
       </c>
       <c r="N292" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 서쪽에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -22315,8 +22193,7 @@
       </c>
       <c r="L293" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 동쪽에 있는 동이다.
-동쪽은 서대문구 홍은동, 서쪽은 역촌동 · 대조동, 남쪽은 응암동, 북쪽은 불광동과 접해 있다.
+          <t xml:space="preserve">동쪽은 서대문구 홍은동, 서쪽은 역촌동 · 대조동, 남쪽은 응암동, 북쪽은 불광동과 접해 있다.
 동명은 녹반(綠礬)이 많이 나는 고개라는 뜻의 녹번고개에서 유래되었다.
 조선시대에는 한성부 북부 연은방 지역이었다.
 1914년 경기도 고양군 녹번리에 속하였고, 1949년 서울특별시 서대문구에 편입되어 녹번리로 불렸다.
@@ -22328,11 +22205,11 @@
         </is>
       </c>
       <c r="M293" s="0">
-        <v>550</v>
+        <v>535</v>
       </c>
       <c r="N293" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 동쪽에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -22395,8 +22272,7 @@
       </c>
       <c r="L294" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 중앙에 있는 동이다.
-통일로를 사이에 두고 동쪽은 불광동, 서쪽은 갈현동, 북쪽은 갈현동 · 불광동, 남쪽은 녹번동 · 역촌동과 접해 있다.
+          <t xml:space="preserve">통일로를 사이에 두고 동쪽은 불광동, 서쪽은 갈현동, 북쪽은 갈현동 · 불광동, 남쪽은 녹번동 · 역촌동과 접해 있다.
 동명은 이 마을에 대추나무가 많았던 데서 유래되었다.
 조선시대 한성부 성저십리 북부 연은방 지역이었다.
 1914년 경기도 고양군 은평면 대조리에 속하였고, 1949년 서울특별시 서대문구에 편입되었다.
@@ -22405,11 +22281,12 @@
         </is>
       </c>
       <c r="M294" s="0">
-        <v>316</v>
+        <v>301</v>
       </c>
       <c r="N294" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">사방으로 통일로 · 연서로 · 진흥로 · 서오릉로 등 간선도로로 둘러싸여 있는 은평구 중심지역으로, 대조시장 등 상가가 밀집되어 있으며, 서부시외버스터미널이 있어 유동인구가 많다.</t>
+          <t xml:space="preserve">구의 중앙에 있는 동이다.
+사방으로 통일로 · 연서로 · 진흥로 · 서오릉로 등 간선도로로 둘러싸여 있는 은평구 중심지역으로, 대조시장 등 상가가 밀집되어 있으며, 서부시외버스터미널이 있어 유동인구가 많다.</t>
         </is>
       </c>
     </row>
@@ -22472,8 +22349,7 @@
       </c>
       <c r="L295" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 중앙과 동쪽에 있는 동이다.
-동쪽은 종로구 구기동, 서쪽은 대조동 · 갈현동, 남쪽은 녹번동, 북쪽은 진관외동과 접해 있다.
+          <t xml:space="preserve">동쪽은 종로구 구기동, 서쪽은 대조동 · 갈현동, 남쪽은 녹번동, 북쪽은 진관외동과 접해 있다.
 동명은 불광사에서 유래되었다.
 근처에 바위와 크고 작은 사찰이 많아 부처의 서광이 서려 있다 하여 붙여진 이름이다.
 조선시대에는 한성부 북부 연은방 지역이었다.
@@ -22488,11 +22364,11 @@
         </is>
       </c>
       <c r="M295" s="0">
-        <v>711</v>
+        <v>692</v>
       </c>
       <c r="N295" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 중앙과 동쪽에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -22554,8 +22430,7 @@
       </c>
       <c r="L296" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 남서쪽 끝에 있는 동이다.
-동쪽은 증산동, 서쪽은 경기도 고양시 향동동, 북쪽은 증산동 · 신사동, 남쪽은 마포구 상암동과 접해 있다.
+          <t xml:space="preserve">동쪽은 증산동, 서쪽은 경기도 고양시 향동동, 북쪽은 증산동 · 신사동, 남쪽은 마포구 상암동과 접해 있다.
 동명은 마을 앞 들판 건너편에 있는 물의 풍치가 좋다는 데서 유래되었다.
 이곳은 한강 하류로서 예로부터 물과 깊은 인연이 있어 수생리계(水生里契), 수색리계(水色里契), 수암리계(水岩里契), 학암리계(鶴岩里契) 등 여러 이름으로 불렸다.
 조선시대 한성부 성저십리 북부 연희방(延禧坊) 수생리계(水生里契), 수색리계(水色里契), 수암리계(水岩里契) 등으로 불린 지역이었다.
@@ -22567,11 +22442,11 @@
         </is>
       </c>
       <c r="M296" s="0">
-        <v>588</v>
+        <v>570</v>
       </c>
       <c r="N296" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 남서쪽 끝에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -22633,8 +22508,7 @@
       </c>
       <c r="L297" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 남서쪽에 있는 동이다.
-동쪽은 응암동, 남쪽은 증산동 · 수색동, 북쪽은 역촌동, 서쪽은 봉산 능선을 따라 경기도 고양시 향동동과 접해 있다.
+          <t xml:space="preserve">동쪽은 응암동, 남쪽은 증산동 · 수색동, 북쪽은 역촌동, 서쪽은 봉산 능선을 따라 경기도 고양시 향동동과 접해 있다.
 동명은 옛날 이 마을에 새 절[新寺]이 있었던 데서 유래되었다.
 조선시대 한성부 성저십리 북부 연은방 지역이었다.
 1914년에 경기도 고양군 은평면 신사리에 속했고 1949년 서울특별시 서대문구에 편입되었다.
@@ -22643,11 +22517,12 @@
         </is>
       </c>
       <c r="M297" s="0">
-        <v>351</v>
+        <v>335</v>
       </c>
       <c r="N297" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울기독대학교, 숭실중 · 고등학교, 신사종합사회복지관, 신흥시장, 공동묘지 등이 있다.</t>
+          <t xml:space="preserve">구의 남서쪽에 있는 동이다.
+서울기독대학교, 숭실중 · 고등학교, 신사종합사회복지관, 신흥시장, 공동묘지 등이 있다.</t>
         </is>
       </c>
     </row>
@@ -22708,8 +22583,7 @@
       </c>
       <c r="L298" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 중앙 서쪽에 있는 동이다.
-동쪽은 응암동 · 녹번동, 서쪽은 경기도 고양시 향동동, 남쪽은 신사동 · 응암동, 북쪽은 대조동 · 구산동 · 갈현동과 접해 있다.
+          <t xml:space="preserve">동쪽은 응암동 · 녹번동, 서쪽은 경기도 고양시 향동동, 남쪽은 신사동 · 응암동, 북쪽은 대조동 · 구산동 · 갈현동과 접해 있다.
 동명은 대조동과 경계되는 지역에 조선시대부터 연서역(延曙驛)이 있어서 마방촌 · 역말 · 역촌이라고 부른 데서 유래한다.
 또 지형이 돌로 곶이를 이루었으므로 돌곶이, 한자명으로 석관동(石串洞)이라고도 하였다.
 조선시대에는 한성부 성저십리 북부 연은방 역계(驛契) 지역이었다.
@@ -22718,11 +22592,11 @@
         </is>
       </c>
       <c r="M298" s="0">
-        <v>358</v>
+        <v>340</v>
       </c>
       <c r="N298" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 중앙 서쪽에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -22784,8 +22658,7 @@
       </c>
       <c r="L299" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 남쪽에 있는 동이다.
-동쪽은 백련산을 경계로 서대문구 홍은동, 서쪽은 신사동 · 증산동, 남쪽은 서대문구 남가좌동, 북쪽의 역촌동 · 녹번동과 접해 있다.
+          <t xml:space="preserve">동쪽은 백련산을 경계로 서대문구 홍은동, 서쪽은 신사동 · 증산동, 남쪽은 서대문구 남가좌동, 북쪽의 역촌동 · 녹번동과 접해 있다.
 동명은 마을 뒤 백련산 기슭에 매가 앉은 모습의 바위가 있는데서 유래되었다.
 또 왕의 일행이 궁중에서 나와 매사냥을 하던 큰 바위가 있었다 하여 붙여진 이름이라고도 한다.
 조선시대에는 한성부 성저십리 북부 연은방 지역이었다.
@@ -22795,11 +22668,12 @@
         </is>
       </c>
       <c r="M299" s="0">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="N299" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">따라서 서부경찰서 · 은평등기소 · 은평우체국 · 서부세무서 등의 공공기관이 자리하고 있으며, 대림시장을 비롯한 응암오거리 상권이 발달해 있다.</t>
+          <t xml:space="preserve">구의 남쪽에 있는 동이다.
+따라서 서부경찰서 · 은평등기소 · 은평우체국 · 서부세무서 등의 공공기관이 자리하고 있으며, 대림시장을 비롯한 응암오거리 상권이 발달해 있다.</t>
         </is>
       </c>
     </row>
@@ -22861,8 +22735,7 @@
       </c>
       <c r="L300" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 남쪽 끝에 있는 동이다.
-동쪽은 응암동과 서대문구 북가좌동, 서쪽은 수색동, 남쪽은 서대문구 북가좌동 · 중동, 북쪽은신사동과 접해 있다.
+          <t xml:space="preserve">동쪽은 응암동과 서대문구 북가좌동, 서쪽은 수색동, 남쪽은 서대문구 북가좌동 · 중동, 북쪽은신사동과 접해 있다.
 동명은 시루봉 아래에 있어 시루메라고 하였는데, 시루는 물이 새므로 좋지 않다 하여 시루 ‘증(甑)’ 자를 비단 ‘증(繒)’으로 바꾸어 붙인 데서 유래되었다.
 조선시대 한성부 성저십리 북부 연희방 지역이었다.
 1914년 경기도 고양군 연희면 증산리에 속하였고, 1949년 서대문구에 편입되었다.
@@ -22872,11 +22745,12 @@
         </is>
       </c>
       <c r="M300" s="0">
-        <v>416</v>
+        <v>399</v>
       </c>
       <c r="N300" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">증산종합시장과 서부농산물직판장이 있어 생필품 공급이 원활하다.</t>
+          <t xml:space="preserve">구의 남쪽 끝에 있는 동이다.
+증산종합시장과 서부농산물직판장이 있어 생필품 공급이 원활하다.</t>
         </is>
       </c>
     </row>
@@ -23004,8 +22878,7 @@
       </c>
       <c r="L302" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 중앙에 있는 동이다.
-북쪽은 삼청동, 동쪽은 계동, 남쪽은 재동, 서쪽은 화동 · 삼청동과 접해 있다.
+          <t xml:space="preserve">북쪽은 삼청동, 동쪽은 계동, 남쪽은 재동, 서쪽은 화동 · 삼청동과 접해 있다.
 동명은 조선시대의 명칭인 가회방(嘉會坊)에서 유래되었는데, 가회란 어진 신하가 어진 임금을 만나서 국운이 창성하는 좋은 만남을 뜻한다.
 조선시대 한성부 북부 가회방 지역이었으며, 1914년 맹현(孟峴) · 재동(齋洞) · 동곡(東谷) · 계동(桂洞) 일부를 합쳐 경성부 가회동이 되었다가, 1936년 가회정이 되었고, 1946년 다시 가회동이 되었다.
 가회동은 정독도서관과 중앙고등학교 사이, 응봉 남쪽 기슭의 경복궁과 창덕궁 사이에 있어 서울 북촌의 중심을 이루고 있다.
@@ -23015,11 +22888,12 @@
         </is>
       </c>
       <c r="M302" s="0">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="N302" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가회동은 행정동과 이름이 같으며, 법정동인 가회동 · 계동 · 재동 · 원서동을 관할하고 있다.</t>
+          <t xml:space="preserve">구의 중앙에 있는 동이다.
+가회동은 행정동과 이름이 같으며, 법정동인 가회동 · 계동 · 재동 · 원서동을 관할하고 있다.</t>
         </is>
       </c>
     </row>
@@ -23605,8 +23479,7 @@
       </c>
       <c r="L310" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 서남쪽 끝에 있는 동이다.
-동쪽은 평동, 서쪽은 서대문구 냉천동 · 옥천동 · 천연동, 남쪽은 서대문구 냉천동, 북쪽은 교북동 · 송월동과 접해 있다.
+          <t xml:space="preserve">동쪽은 평동, 서쪽은 서대문구 냉천동 · 옥천동 · 천연동, 남쪽은 서대문구 냉천동, 북쪽은 교북동 · 송월동과 접해 있다.
 동명은 만초천 상류인 교남지구대 앞에 있던 돌다리 남쪽 마을인데서 유래되었다.
 조선시대 한성부 서부 반송방(盤松坊)에 속하였으며, 1914년에는 경성부 교남동이 되었다가, 1936년 교남정(橋南町)으로 바뀌었다.
 1943년 구제 실시에 따라 서대문구에 편입되었고, 1946년 교남동이 되었으며, 1975년 종로구 관할이 되었다.
@@ -23614,11 +23487,12 @@
         </is>
       </c>
       <c r="M310" s="0">
-        <v>339</v>
+        <v>321</v>
       </c>
       <c r="N310" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">교남동은 행정동과 이름이 같으며, 법정동인 교남동 · 평동 · 송월동 · 홍파동 · 교북동 · 행촌동을 관할하고 있다.</t>
+          <t xml:space="preserve">구의 서남쪽 끝에 있는 동이다.
+교남동은 행정동과 이름이 같으며, 법정동인 교남동 · 평동 · 송월동 · 홍파동 · 교북동 · 행촌동을 관할하고 있다.</t>
         </is>
       </c>
     </row>
@@ -24643,8 +24517,7 @@
       </c>
       <c r="L324" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 북쪽에 있는 동이다.
-북쪽은 성북구 성북동, 동쪽은 혜화동, 서쪽은 와룡동, 남쪽은 연건동과 접해 있다.
+          <t xml:space="preserve">북쪽은 성북구 성북동, 동쪽은 혜화동, 서쪽은 와룡동, 남쪽은 연건동과 접해 있다.
 동명은 조선시대 인륜을 밝히는 교육기관인 성균관(成均館)이 있고, 그 맥을 이어 성균관대학교의 전신인 명륜학원(明倫學院)이 있었던 데서 유래되었다.
 조선시대 한성부 동부 숭교방(崇敎坊)에 속하였으며, 1914년 숭일동 · 숭이동 · 숭삼동 · 숭사동이 되었다.
 1936년 명륜정1·2·3·4정목이 되었다가, 1946년 명륜동1·2·3·4가가 되었다.
@@ -24656,11 +24529,12 @@
         </is>
       </c>
       <c r="M324" s="0">
-        <v>576</v>
+        <v>561</v>
       </c>
       <c r="N324" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">법정동인 명륜동1~4가 가운데 명륜동3가와 와룡동 1번지는 행정동 명륜3가동에서 행정을 담당하고 있으며, 명륜동1·2·4가는 혜화동에서 관할하고 있다.
+          <t xml:space="preserve">구의 북쪽에 있는 동이다.
+법정동인 명륜동1~4가 가운데 명륜동3가와 와룡동 1번지는 행정동 명륜3가동에서 행정을 담당하고 있으며, 명륜동1·2·4가는 혜화동에서 관할하고 있다.
 그리고 우석병원이 있던 곳은 아남아파트단지로 변하였다.</t>
         </is>
       </c>
@@ -24723,8 +24597,7 @@
       </c>
       <c r="L325" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 북쪽에 있는 동이다.
-북쪽은 성북구 성북동, 동쪽은 혜화동, 서쪽은 와룡동, 남쪽은 연건동과 접해 있다.
+          <t xml:space="preserve">북쪽은 성북구 성북동, 동쪽은 혜화동, 서쪽은 와룡동, 남쪽은 연건동과 접해 있다.
 동명은 조선시대 인륜을 밝히는 교육기관인 성균관(成均館)이 있고, 그 맥을 이어 성균관대학교의 전신인 명륜학원(明倫學院)이 있었던 데서 유래되었다.
 조선시대 한성부 동부 숭교방(崇敎坊)에 속하였으며, 1914년 숭일동 · 숭이동 · 숭삼동 · 숭사동이 되었다.
 1936년 명륜정1·2·3·4정목이 되었다가, 1946년 명륜동1·2·3·4가가 되었다.
@@ -24736,11 +24609,12 @@
         </is>
       </c>
       <c r="M325" s="0">
-        <v>576</v>
+        <v>561</v>
       </c>
       <c r="N325" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">법정동인 명륜동1~4가 가운데 명륜동3가와 와룡동 1번지는 행정동 명륜3가동에서 행정을 담당하고 있으며, 명륜동1·2·4가는 혜화동에서 관할하고 있다.
+          <t xml:space="preserve">구의 북쪽에 있는 동이다.
+법정동인 명륜동1~4가 가운데 명륜동3가와 와룡동 1번지는 행정동 명륜3가동에서 행정을 담당하고 있으며, 명륜동1·2·4가는 혜화동에서 관할하고 있다.
 그리고 우석병원이 있던 곳은 아남아파트단지로 변하였다.</t>
         </is>
       </c>
@@ -24803,8 +24677,7 @@
       </c>
       <c r="L326" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 북쪽에 있는 동이다.
-북쪽은 성북구 성북동, 동쪽은 혜화동, 서쪽은 와룡동, 남쪽은 연건동과 접해 있다.
+          <t xml:space="preserve">북쪽은 성북구 성북동, 동쪽은 혜화동, 서쪽은 와룡동, 남쪽은 연건동과 접해 있다.
 동명은 조선시대 인륜을 밝히는 교육기관인 성균관(成均館)이 있고, 그 맥을 이어 성균관대학교의 전신인 명륜학원(明倫學院)이 있었던 데서 유래되었다.
 조선시대 한성부 동부 숭교방(崇敎坊)에 속하였으며, 1914년 숭일동 · 숭이동 · 숭삼동 · 숭사동이 되었다.
 1936년 명륜정1·2·3·4정목이 되었다가, 1946년 명륜동1·2·3·4가가 되었다.
@@ -24816,11 +24689,12 @@
         </is>
       </c>
       <c r="M326" s="0">
-        <v>576</v>
+        <v>561</v>
       </c>
       <c r="N326" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">법정동인 명륜동1~4가 가운데 명륜동3가와 와룡동 1번지는 행정동 명륜3가동에서 행정을 담당하고 있으며, 명륜동1·2·4가는 혜화동에서 관할하고 있다.
+          <t xml:space="preserve">구의 북쪽에 있는 동이다.
+법정동인 명륜동1~4가 가운데 명륜동3가와 와룡동 1번지는 행정동 명륜3가동에서 행정을 담당하고 있으며, 명륜동1·2·4가는 혜화동에서 관할하고 있다.
 그리고 우석병원이 있던 곳은 아남아파트단지로 변하였다.</t>
         </is>
       </c>
@@ -24883,8 +24757,7 @@
       </c>
       <c r="L327" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 북쪽에 있는 동이다.
-북쪽은 성북구 성북동, 동쪽은 혜화동, 서쪽은 와룡동, 남쪽은 연건동과 접해 있다.
+          <t xml:space="preserve">북쪽은 성북구 성북동, 동쪽은 혜화동, 서쪽은 와룡동, 남쪽은 연건동과 접해 있다.
 동명은 조선시대 인륜을 밝히는 교육기관인 성균관(成均館)이 있고, 그 맥을 이어 성균관대학교의 전신인 명륜학원(明倫學院)이 있었던 데서 유래되었다.
 조선시대 한성부 동부 숭교방(崇敎坊)에 속하였으며, 1914년 숭일동 · 숭이동 · 숭삼동 · 숭사동이 되었다.
 1936년 명륜정1·2·3·4정목이 되었다가, 1946년 명륜동1·2·3·4가가 되었다.
@@ -24896,11 +24769,12 @@
         </is>
       </c>
       <c r="M327" s="0">
-        <v>576</v>
+        <v>561</v>
       </c>
       <c r="N327" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">법정동인 명륜동1~4가 가운데 명륜동3가와 와룡동 1번지는 행정동 명륜3가동에서 행정을 담당하고 있으며, 명륜동1·2·4가는 혜화동에서 관할하고 있다.
+          <t xml:space="preserve">구의 북쪽에 있는 동이다.
+법정동인 명륜동1~4가 가운데 명륜동3가와 와룡동 1번지는 행정동 명륜3가동에서 행정을 담당하고 있으며, 명륜동1·2·4가는 혜화동에서 관할하고 있다.
 그리고 우석병원이 있던 곳은 아남아파트단지로 변하였다.</t>
         </is>
       </c>
@@ -25039,8 +24913,7 @@
       </c>
       <c r="L329" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 서쪽 끝에 있는 동이다.
-인왕산 서쪽 기슭에 있으며, 동쪽은 사직동 · 누상동, 서쪽은 서대문구 현저동, 남쪽은 행촌동, 북쪽은 서대문구 홍제동과 접해 있다.
+          <t xml:space="preserve">인왕산 서쪽 기슭에 있으며, 동쪽은 사직동 · 누상동, 서쪽은 서대문구 현저동, 남쪽은 행촌동, 북쪽은 서대문구 홍제동과 접해 있다.
 동명은 1975년 서대문구 현저동 일부를 종로구에 편입할 때 무악고개가 있는 곳이라 하여 유래되었다.
 조선시대 한성부 서부 반송방(盤松坊)에 속하였으며, 1914년 경성부 현저동, 1936년 현저정(峴底町)에 속하였다.
 1943년 서대문구에 편입되었고, 1946년 현저동에 속하였다가, 1975년 종로구에 편입되면서 무악동이 되었다.
@@ -25050,11 +24923,11 @@
         </is>
       </c>
       <c r="M329" s="0">
-        <v>517</v>
+        <v>500</v>
       </c>
       <c r="N329" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 서쪽 끝에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -25188,19 +25061,18 @@
       </c>
       <c r="L331" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 서북쪽에 있는 동이다.
-인왕산 동북쪽 기슭과 백악산 서북쪽 기슭에 있으며, 동쪽은 삼청동, 서쪽은 홍지동과 서대문구 홍제동, 남쪽은 청운동 · 옥인동, 북쪽은 신영동 · 평창동과 접해 있다.
+          <t xml:space="preserve">인왕산 동북쪽 기슭과 백악산 서북쪽 기슭에 있으며, 동쪽은 삼청동, 서쪽은 홍지동과 서대문구 홍제동, 남쪽은 청운동 · 옥인동, 북쪽은 신영동 · 평창동과 접해 있다.
 동명은 이곳에 부침바위[付岩]가 있었던 데서 유래되었다.
 조선시대 한성부 북부 의통방(義通坊)에 속하였고, 1914년 고양군 은평면 부암리가 되었다가, 1936년 경성부 부암정(付岩町)이 되었다.
 1943년 구제 실시에 따라 서대문구에 속하였다가, 1946년 부암동으로 바뀌었으며, 1975년 종로구 관할이 되었다.</t>
         </is>
       </c>
       <c r="M331" s="0">
-        <v>286</v>
+        <v>270</v>
       </c>
       <c r="N331" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 서북쪽에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -25334,8 +25206,7 @@
       </c>
       <c r="L333" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 서쪽에 있는 동이다.
-동쪽은 필운동 · 내자동 · 내수동, 서쪽은 행촌동 · 무악동, 남쪽은 송월동 · 신문로 2가, 북쪽은 필운동 · 누상동과 접해 있다.
+          <t xml:space="preserve">동쪽은 필운동 · 내자동 · 내수동, 서쪽은 행촌동 · 무악동, 남쪽은 송월동 · 신문로 2가, 북쪽은 필운동 · 누상동과 접해 있다.
 동명은 조선시대에 설치된 사직단에서 유래되었다.
 조선시대 한성부 서부 인달방(仁達坊)에 속하였다.
 1914년 창평동 · 무덕문 · 사직동 · 박정동의 각 일부를 합쳐 사직동이 되었고, 1936년 사직정이 되었다.
@@ -25344,11 +25215,11 @@
         </is>
       </c>
       <c r="M333" s="0">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="N333" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 서쪽에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -25409,8 +25280,7 @@
       </c>
       <c r="L334" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 중앙 북쪽에 있는 동이다.
-동쪽은 명륜동, 서쪽은 청운동 · 부암동, 남쪽은 세종로동 · 팔판동 · 화동 · 가회동, 북쪽은 성북구 성북동과 접해 있다.
+          <t xml:space="preserve">동쪽은 명륜동, 서쪽은 청운동 · 부암동, 남쪽은 세종로동 · 팔판동 · 화동 · 가회동, 북쪽은 성북구 성북동과 접해 있다.
 동명은 조선시대 이곳에 도교의 태청(太淸) · 상청(上淸) · 옥청(玉淸)의 삼청전(三淸殿)이 있었던 데서 유래되었다.
 또 산과 물이 맑고, 인심 또한 맑고 좋다고 하여 삼청(三淸)이라고 하였다고도 한다.
 조선시대 한성부 북부 진장방(鎭長坊)에 속하였으며, 1914년 삼청동이 되었다가, 1936년 삼청정이 되었다.
@@ -25418,11 +25288,12 @@
         </is>
       </c>
       <c r="M334" s="0">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="N334" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">삼청동은 행정동과 이름이 같으며 법정동인 삼청동 · 팔판동 · 안국동 · 소격동 · 화동 · 사간동 · 송현동을 관할하고 있다.</t>
+          <t xml:space="preserve">구의 중앙 북쪽에 있는 동이다.
+삼청동은 행정동과 이름이 같으며 법정동인 삼청동 · 팔판동 · 안국동 · 소격동 · 화동 · 사간동 · 송현동을 관할하고 있다.</t>
         </is>
       </c>
     </row>
@@ -25938,8 +25809,7 @@
       </c>
       <c r="L341" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 동쪽 끝에 있는 동이다.
-북쪽은 성북구 보문동, 동쪽으로 동대문구 신설동, 서쪽은 창신동, 남쪽은 중구 황학동과 접해 있다.
+          <t xml:space="preserve">북쪽은 성북구 보문동, 동쪽으로 동대문구 신설동, 서쪽은 창신동, 남쪽은 중구 황학동과 접해 있다.
 동명은 옛 지명인 숭신방(崇信坊)과 인창방(仁昌坊)의 머리글자를 합한 데서 비롯되었다.
 조선시대 한성부 동부 숭신방과 인창방에 속하였으며, 1914년 경성부 숭인동이 되었다.
 1936년 숭인정이 되었다가, 1943년 동대문구에 편입되었고, 1946년 숭인동이 되었으며, 1975년 종로구 관할이 되었다.
@@ -25952,11 +25822,12 @@
         </is>
       </c>
       <c r="M341" s="0">
-        <v>577</v>
+        <v>560</v>
       </c>
       <c r="N341" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">현재 동묘 담장 밖에는 수많은 물품을 좌판을 벌려놓고 파는 풍물시장이 형성되어 있다.</t>
+          <t xml:space="preserve">구의 동쪽 끝에 있는 동이다.
+현재 동묘 담장 밖에는 수많은 물품을 좌판을 벌려놓고 파는 풍물시장이 형성되어 있다.</t>
         </is>
       </c>
     </row>
@@ -26092,19 +25963,18 @@
       </c>
       <c r="L343" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 남서쪽에 있는 동으로 가로명과 일치한다.
-동쪽은 세종로, 남쪽은 중구 정동, 북쪽은 당주동, 서쪽으로는 신문로2가와 접해 있다.
+          <t xml:space="preserve">동쪽은 세종로, 남쪽은 중구 정동, 북쪽은 당주동, 서쪽으로는 신문로2가와 접해 있다.
 조선시대 한성부 서부 적선방(積善坊)과 여경방(餘慶紡)에 속하였으며, 1914년 훈조동 · 야주현 · 염정동 · 송교 · 상방교 · 오궁동 · 정자동 · 중방교 · 동령동 · 원동 · 선공동의 일부를 합하여 서대문정 1정목이 되었고, 1943년 구제 실시로 종로구에 속하였다가, 1946년 신문로1가가 되었다.
 조선시대 비변사 · 선공감 · 훈련도감 등의 관아가 있었으며, 새문안교회 · 구세군대한본영 등 오랜 역사의 개신교회가 위치해 있다.
 최초의 국립극장인 원각사와 청계천에 놓여진 송기교(松杞橋)가 있어 여기서부터 청계천 본류가 시작되었다.</t>
         </is>
       </c>
       <c r="M343" s="0">
-        <v>380</v>
+        <v>354</v>
       </c>
       <c r="N343" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 남서쪽에 있는 동으로 가로명과 일치한다.</t>
         </is>
       </c>
     </row>
@@ -26165,17 +26035,16 @@
       </c>
       <c r="L344" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 남서쪽에 있는 동으로 가로명과 일치한다.
-동쪽은 내수동 · 당주동 · 신문로1가, 남쪽은 평동과 중구 정동과 충정로1가, 서쪽은 송월동 · 홍파동 · 행촌동, 북쪽은 사직동과 접해 있다.
+          <t xml:space="preserve">동쪽은 내수동 · 당주동 · 신문로1가, 남쪽은 평동과 중구 정동과 충정로1가, 서쪽은 송월동 · 홍파동 · 행촌동, 북쪽은 사직동과 접해 있다.
 조선 초기까지 한성부 서부 여경방에 속했으며, 1914년 자문동 · 함춘원 · 농포 · 방추동 · 오궁동 · 장생동의 일부를 합하여 서대문 2정목이 되었고, 1943년 구제 실시로 종로구에 속하였다가, 1946년 신문로2가가 되었다.</t>
         </is>
       </c>
       <c r="M344" s="0">
-        <v>238</v>
+        <v>212</v>
       </c>
       <c r="N344" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 남서쪽에 있는 동으로 가로명과 일치한다.</t>
         </is>
       </c>
     </row>
@@ -26848,8 +26717,7 @@
       </c>
       <c r="L353" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 동쪽에 있는 동으로 동명은 창경원의 남쪽에 있는 데서 유래되었다고 하는데, 함춘원 남쪽으로도 볼 수 있다.
-조선시대 한성부 동부 연화방(蓮化坊)에 속하였으며, 1914년 승문동(承文洞), 신민동(新民洞), 감정동(甘井洞), 호동(壺洞), 상사동(相思洞), 순라동(巡邏洞), 마전정동(麻田井洞), 함춘동(含春洞), 연지동을 통합하여 원남동이 되었다.
+          <t xml:space="preserve">조선시대 한성부 동부 연화방(蓮化坊)에 속하였으며, 1914년 승문동(承文洞), 신민동(新民洞), 감정동(甘井洞), 호동(壺洞), 상사동(相思洞), 순라동(巡邏洞), 마전정동(麻田井洞), 함춘동(含春洞), 연지동을 통합하여 원남동이 되었다.
 1936년 원남정이 되었으며, 1946년 원남동이 되었다.
 조선 중기 이항복이 살았다.
 일제강점기 때 종로4가에서 창경궁까지 이어지는 전차로가 있었다.
@@ -26857,11 +26725,11 @@
         </is>
       </c>
       <c r="M353" s="0">
-        <v>318</v>
+        <v>255</v>
       </c>
       <c r="N353" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">구의 동쪽에 있는 동으로 동명은 창경원의 남쪽에 있는 데서 유래되었다고 하는데, 함춘원 남쪽으로도 볼 수 있다.</t>
         </is>
       </c>
     </row>
@@ -26998,8 +26866,7 @@
       </c>
       <c r="L355" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 동쪽에 있는 동이다.
-낙산(駱山) 서쪽 기슭에 있으며, 동쪽은 창신동, 서쪽으로 연지동, 남쪽은 충신동, 북쪽의 동숭동과 접해 있다.
+          <t xml:space="preserve">낙산(駱山) 서쪽 기슭에 있으며, 동쪽은 창신동, 서쪽으로 연지동, 남쪽은 충신동, 북쪽의 동숭동과 접해 있다.
 동명은 조선 전기 김일손이 살던 이화정(梨花亭)이라는 정자에서 유래되었다.
 조선시대 한성부 동부 숭신방(崇信坊)에 속하였으며, 1914년 이화동이 되었다.
 1936년 이화정이 되었다가, 1943년 구제 실시로 종로구에 편입되었고, 1946년 이화동이 되었다.
@@ -27012,11 +26879,12 @@
         </is>
       </c>
       <c r="M355" s="0">
-        <v>643</v>
+        <v>628</v>
       </c>
       <c r="N355" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">이화동은 행정동과 이름이 같으며 법정동인 이화동 · 연건동 · 동숭동을 관할하고 있다.</t>
+          <t xml:space="preserve">구의 동쪽에 있는 동이다.
+이화동은 행정동과 이름이 같으며 법정동인 이화동 · 연건동 · 동숭동을 관할하고 있다.</t>
         </is>
       </c>
     </row>
@@ -28192,8 +28060,7 @@
       </c>
       <c r="L370" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 동쪽에 있는 동이다.
-북쪽은 성북구 삼선동2가, 동쪽은 숭인동, 서쪽은 혜화동 · 이화동 · 충신동 · 종로6가, 남쪽은 중구 흥인동과 접해 있다.
+          <t xml:space="preserve">북쪽은 성북구 삼선동2가, 동쪽은 숭인동, 서쪽은 혜화동 · 이화동 · 충신동 · 종로6가, 남쪽은 중구 흥인동과 접해 있다.
 동명은 옛 지명인 인창방(仁昌坊)과 숭신방(崇信坊)의 가운데 글자를 합성한 데서 유래되었다.
 조선시대 한성부 동부 인창방과 숭신방에 속하였으며, 1914년 창신동이 되었다.
 1936년 창신정이 되었다가, 1943년 동대문구에 편입되었고, 1946년 창신동이 되었으며, 1975년 종로구 관할이 되었다.
@@ -28206,11 +28073,12 @@
         </is>
       </c>
       <c r="M370" s="0">
-        <v>725</v>
+        <v>710</v>
       </c>
       <c r="N370" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동문시장 · 청계상가 · 동대문신발도매상가와 삼우텍스프라자 등이 있다.</t>
+          <t xml:space="preserve">구의 동쪽에 있는 동이다.
+동문시장 · 청계상가 · 동대문신발도매상가와 삼우텍스프라자 등이 있다.</t>
         </is>
       </c>
     </row>
@@ -28272,8 +28140,7 @@
       </c>
       <c r="L371" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 서쪽에 있는 동이다.
-북악산 서남쪽 기슭에 있으며, 동쪽은 세종로 · 삼청동, 서쪽과 북쪽은 부암동, 남쪽은 옥인동 · 신교동 · 궁정동과 접해 있다.
+          <t xml:space="preserve">북악산 서남쪽 기슭에 있으며, 동쪽은 세종로 · 삼청동, 서쪽과 북쪽은 부암동, 남쪽은 옥인동 · 신교동 · 궁정동과 접해 있다.
 동명은 인왕산 청풍계(淸風溪)라는 계곡과 백악산 백운동(白雲洞) 계곡의 머리글자를 합성한 데서 유래되었다.
 조선시대 한성부 북부 순화방(順化坊) 지역이었으며, 1914년 경성부 북부 백운동 · 청풍동 · 박정동 · 신교의 각 일부를 합쳐 청운동이라고 하였고, 1936년 청운정이 되었다.
 1943년 종로구에 편입되었고, 1946년 청운동이 되었다.
@@ -28283,11 +28150,12 @@
         </is>
       </c>
       <c r="M371" s="0">
-        <v>462</v>
+        <v>447</v>
       </c>
       <c r="N371" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">청운동은 행정동 이름과 같으며, 법정동인 청운동 · 신교동 · 궁정동 · 세종로 1번지를 관할하고 있다.</t>
+          <t xml:space="preserve">구의 서쪽에 있는 동이다.
+청운동은 행정동 이름과 같으며, 법정동인 청운동 · 신교동 · 궁정동 · 세종로 1번지를 관할하고 있다.</t>
         </is>
       </c>
     </row>
@@ -28875,8 +28743,7 @@
       </c>
       <c r="L379" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 북쪽에 있는 동이다.
-동쪽과 북쪽은 성북구 정릉동, 서쪽으로 구기동, 남쪽은 부암동 · 삼청동과 접해 있다.
+          <t xml:space="preserve">동쪽과 북쪽은 성북구 정릉동, 서쪽으로 구기동, 남쪽은 부암동 · 삼청동과 접해 있다.
 동명은 조선시대에 선혜청(宣惠廳)의 평창이 있었던 것에서 유래되었다.
 조선시대 한성부 북부 의통방(義通坊)에 속하였으며, 갑오개혁 때 북서 상평방(성외) 평창이었다.
 1914년 경기도 고양군 은평면(恩平面) 평창리(平倉里)가 되었다가, 1949년 서울특별시 서대문구에 편입되어 1950년 평창동이 되었으며, 1975년 종로구 관할이 되었다.
@@ -28887,11 +28754,12 @@
         </is>
       </c>
       <c r="M379" s="0">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="N379" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">평창동은 행정동과 이름이 같으며 법정동인 평창동 · 구기동을 관할하고 있다.</t>
+          <t xml:space="preserve">구의 북쪽에 있는 동이다.
+평창동은 행정동과 이름이 같으며 법정동인 평창동 · 구기동을 관할하고 있다.</t>
         </is>
       </c>
     </row>
@@ -29104,8 +28972,7 @@
       </c>
       <c r="L382" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 북동쪽에 있는 동이다.
-북쪽은 성북구 성북동, 동쪽은 성북구 동소문동 · 성북동, 남쪽은 동숭동, 서쪽으로 명륜동과 접해 있다.
+          <t xml:space="preserve">북쪽은 성북구 성북동, 동쪽은 성북구 동소문동 · 성북동, 남쪽은 동숭동, 서쪽으로 명륜동과 접해 있다.
 동명은 서울성곽 4소문의 하나인 혜화문(惠化門)이 있는 데서 유래되었다.
 조선시대 한성부 동부 숭신방(崇信坊)에 속하였으며, 1914년에 송동 · 상토교 · 하토교 · 상백동을 합하여 혜화동이 되었다.
 1936년 혜화정이 되었다가, 1943년 종로구에 편입되었고, 1946년에 혜화동이 되었다.
@@ -29114,11 +28981,12 @@
         </is>
       </c>
       <c r="M382" s="0">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="N382" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">혜화동은 행정동과 이름이 같으며, 법정동인 혜화동과 명륜동1·2·4가를 관할하고 있다.</t>
+          <t xml:space="preserve">구의 북동쪽에 있는 동이다.
+혜화동은 행정동과 이름이 같으며, 법정동인 혜화동과 명륜동1·2·4가를 관할하고 있다.</t>
         </is>
       </c>
     </row>
@@ -29402,8 +29270,7 @@
       </c>
       <c r="L386" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구의 서쪽에 있는 동이다.
-동쪽은 세종로(경복궁), 서쪽은 옥인동, 남쪽은 창성동, 북쪽은 궁정동과 접해 있다.
+          <t xml:space="preserve">동쪽은 세종로(경복궁), 서쪽은 옥인동, 남쪽은 창성동, 북쪽은 궁정동과 접해 있다.
 동명은 효자로 이름난 조선 중기의 문신 조원의 아들로 임진왜란 때 어머니를 구하기 위해 목숨을 바친 희정 · 희철 형제가 살았던 곳인 데서 유래되었다.
 조선시대 한성부 북부 순화방(順化坊) 지역이었으며, 1914년에는 경성부 북부 효곡 · 백구동 · 동곡 · 육상궁동 · 장동 · 온정동 · 신교의 각 일부를 합쳐 효자동이라고 하였고, 1936년 경성부 효자정이 되었다.
 1943년 구제 실시로 종로구에 속하였고, 1946년 효자동이 되었다.
@@ -29411,11 +29278,12 @@
         </is>
       </c>
       <c r="M386" s="0">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="N386" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">효자동은 행정동과 이름이 같으며 법정동인 효자동 · 창성동 · 통인동 · 누상동 · 누하동 · 옥인동을 관할하고 있다.</t>
+          <t xml:space="preserve">구의 서쪽에 있는 동이다.
+효자동은 행정동과 이름이 같으며 법정동인 효자동 · 창성동 · 통인동 · 누상동 · 누하동 · 옥인동을 관할하고 있다.</t>
         </is>
       </c>
     </row>
@@ -35085,19 +34953,18 @@
       </c>
       <c r="L463" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">중랑구의 중앙 동쪽에 있는 동이다.
-동쪽은 망우산 능선을 경계로 경기도 구리시 교문동, 서쪽은 상봉동, 남쪽은 면목동, 북서쪽은 신내동과 접해 있다.
+          <t xml:space="preserve">동쪽은 망우산 능선을 경계로 경기도 구리시 교문동, 서쪽은 상봉동, 남쪽은 면목동, 북서쪽은 신내동과 접해 있다.
 서울특별시와 경기도 구리시의 경계가 되는 망우고개에서 동명이 유래되었다.
 양주군 망우리면, 양주군 구리면 망우리였다가 1963년 서울특별시 동대문구에 편입되면서 망우동이 되었고, 1988년 중랑구 신설로 이에 속하게 되었다.
 망우동의 많은 부분이 공원묘지로 되어 있는데, 이곳에는 방정환(方定煥) · 오세창(吳世昌) · 한용운(韓龍雲) · 조봉암(曺奉岩) · 문일평(文一平) · 지석영(池錫永) 등의 묘역이 있다.</t>
         </is>
       </c>
       <c r="M463" s="0">
-        <v>315</v>
+        <v>295</v>
       </c>
       <c r="N463" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">중랑구의 중앙 동쪽에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -35159,8 +35026,7 @@
       </c>
       <c r="L464" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">중랑구의 남쪽 일대에 있는 동이다.
-동의 서쪽에는 중랑천 건너 동대문구 휘경동 · 장안동, 남쪽에는 아차산을 경계로 구리시 아천동, 동쪽에는 용마산을 경계로 구리시 교문동, 북쪽은 상봉동 · 망우동과 접해 있다.
+          <t xml:space="preserve">동의 서쪽에는 중랑천 건너 동대문구 휘경동 · 장안동, 남쪽에는 아차산을 경계로 구리시 아천동, 동쪽에는 용마산을 경계로 구리시 교문동, 북쪽은 상봉동 · 망우동과 접해 있다.
 조선시대 국립 목마장(牧馬場)이 앞쪽에 있어 동명이 유래되었다.
 양주군 고양주면, 고양군 뚝도면 면목리였다가, 1949년 서울특별시 성동구 면목동이 되었다.
 1963년 동대문구에 편입되었고, 1988년 중랑구 신설로 이에 속하게 되었다.
@@ -35171,11 +35037,11 @@
         </is>
       </c>
       <c r="M464" s="0">
-        <v>447</v>
+        <v>427</v>
       </c>
       <c r="N464" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">중랑구의 남쪽 일대에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -35237,8 +35103,7 @@
       </c>
       <c r="L465" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">중랑구의 서북쪽에 있는 동이다.
-동쪽은 신내동, 서쪽은 성북구 석관동, 남쪽은 중화동, 북쪽의 도봉구 공릉동과 접해 있다.
+          <t xml:space="preserve">동쪽은 신내동, 서쪽은 성북구 석관동, 남쪽은 중화동, 북쪽의 도봉구 공릉동과 접해 있다.
 문방사우(文房四友)의 하나인 먹을 이곳에서 제조하여 먹골이라 부르던 데서 동명이 유래되었다.
 양주군 망우리면(忘憂里面) 묵동리(墨洞里), 구리면(九里面) 묵동리였다가, 1963년 서울특별시 동대문구에 편입되면서 묵동이 되었고, 1988년 중랑구 신설로 이에 속하게 되었다.
 서쪽에 중랑천, 북쪽에 묵동천이 있고, 남동쪽에 봉화산이 있어 낮은 구릉산 아래 하천변에 발달된 마을이다.
@@ -35249,11 +35114,11 @@
         </is>
       </c>
       <c r="M465" s="0">
-        <v>473</v>
+        <v>455</v>
       </c>
       <c r="N465" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">중랑구의 서북쪽에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -35315,8 +35180,7 @@
       </c>
       <c r="L466" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">중랑구의 중앙에 있는 동이다.
-동의 동쪽은 망우동, 서쪽은 중화동, 남쪽은 면목동, 북쪽은 봉화산을 경계로 신내동과 접해 있다.
+          <t xml:space="preserve">동의 동쪽은 망우동, 서쪽은 중화동, 남쪽은 면목동, 북쪽은 봉화산을 경계로 신내동과 접해 있다.
 이 마을의 옛 지명인 상리(上里)와 봉황리(鳳凰里)의 첫 글자를 따서 동명이 유래되었다.
 양주군 망우리면, 양주군 구리면(九里面) 상봉리(上鳳里)가 되었다가, 1963년 서울특별시 동대문구로 편입되어 상봉동이 되었고, 1988년에 중랑구 신설로 이에 속하게 되었다.
 서울 동부지역의 대표적 재래시장인 동부중앙시장과 상봉시장 등이 있어 중랑구 상권의 중심지로 발전하였으며, 망우로의 확장과 상봉터미널이 서울 북부지역의 관문 역할을 하게 되면서 가전종합백화점 · 대형마트 등이 들어서 중심상권을 유지하고 있다.
@@ -35326,11 +35190,11 @@
         </is>
       </c>
       <c r="M466" s="0">
-        <v>486</v>
+        <v>469</v>
       </c>
       <c r="N466" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">중랑구의 중앙에 있는 동이다.</t>
         </is>
       </c>
     </row>
@@ -35390,8 +35254,7 @@
       </c>
       <c r="L467" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">중랑구의 북동쪽에 있는 동이다.
-동쪽은 구릉산(검암산) 능선을 경계로 경기도 구리시, 서쪽의 봉화산 능선을 따라 상봉동 · 묵동, 남쪽은 망우동, 북쪽의 도봉구 공릉동과 접해 있다.
+          <t xml:space="preserve">동쪽은 구릉산(검암산) 능선을 경계로 경기도 구리시, 서쪽의 봉화산 능선을 따라 상봉동 · 묵동, 남쪽은 망우동, 북쪽의 도봉구 공릉동과 접해 있다.
 이곳에 있던 마을 가운데 새고개마을인 신현(新峴)과 안마을인 내곡(內谷)의 첫 글자를 따서 붙인 데서 동명이 유래되었다.
 양주군 망우리면, 양주군 구리면 신내리(新內里)였다가, 1963년 동대문구에 편입되면서 신내동이 되었다가.
 1988년부터 중랑구 신설로 이에 속하게 되었다.
@@ -35403,11 +35266,12 @@
         </is>
       </c>
       <c r="M467" s="0">
-        <v>550</v>
+        <v>532</v>
       </c>
       <c r="N467" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">신내길이 북부간선도로와 이어져 교통이 편리해졌으며, 봉화산 동쪽에 대규모 아파트단지가 들어서고 중랑구청과 구의회 건물이 들어서 새로운 주택지로 각광받고 있다.</t>
+          <t xml:space="preserve">중랑구의 북동쪽에 있는 동이다.
+신내길이 북부간선도로와 이어져 교통이 편리해졌으며, 봉화산 동쪽에 대규모 아파트단지가 들어서고 중랑구청과 구의회 건물이 들어서 새로운 주택지로 각광받고 있다.</t>
         </is>
       </c>
     </row>
@@ -35469,8 +35333,7 @@
       </c>
       <c r="L468" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">중랑구의 중앙 서쪽에 있는 동이다.
-서쪽은 중랑천을 건너 동대문구 이문동 · 휘경동, 동쪽의 상봉동, 남쪽은 면목동, 북쪽은 묵동과 접해 있다.
+          <t xml:space="preserve">서쪽은 중랑천을 건너 동대문구 이문동 · 휘경동, 동쪽의 상봉동, 남쪽은 면목동, 북쪽은 묵동과 접해 있다.
 자연마을인 가운뎃마을과 아랫마을을 합하여 동명을 한자로 표기하여 중하리(中下里)라 하였던 것이 주민의 건의에 따라 중화리(中和里)로 개칭되었다.
 양주군 남면(南面) 길완리(吉完里) 지역이었으며, 구리면(九里面) 중하리가 되었다가, 1963년 동대문구에 편입되면서 중화동이 되었고, 1988년 중랑구 신설로 이에 속하게 되었다.
 마을의 동북쪽에 봉화산이 있으며, 도시계획에 의해 가로망이 잘 발달되어 있다.
@@ -35480,11 +35343,12 @@
         </is>
       </c>
       <c r="M468" s="0">
-        <v>442</v>
+        <v>422</v>
       </c>
       <c r="N468" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동부간선도로 · 동일로와 더불어 지하철 7호선이 지나 교통이 편리하다.</t>
+          <t xml:space="preserve">중랑구의 중앙 서쪽에 있는 동이다.
+동부간선도로 · 동일로와 더불어 지하철 7호선이 지나 교통이 편리하다.</t>
         </is>
       </c>
     </row>
